--- a/AAII_Financials/Quarterly/QFIN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QFIN_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="92">
   <si>
     <t>QFIN</t>
   </si>
@@ -656,391 +656,403 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>591100</v>
+        <v>625000</v>
       </c>
       <c r="E8" s="3">
-        <v>540500</v>
+        <v>595100</v>
       </c>
       <c r="F8" s="3">
-        <v>497000</v>
+        <v>544200</v>
       </c>
       <c r="G8" s="3">
-        <v>539400</v>
+        <v>500400</v>
       </c>
       <c r="H8" s="3">
-        <v>572200</v>
+        <v>543100</v>
       </c>
       <c r="I8" s="3">
-        <v>577600</v>
+        <v>576100</v>
       </c>
       <c r="J8" s="3">
+        <v>581500</v>
+      </c>
+      <c r="K8" s="3">
         <v>596500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>609300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>655700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>574700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>501000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>464600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>545700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>492200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>502100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>369700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>403000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>347400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>306900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>444600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>89900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>62300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>86000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>64400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>52500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>88300</v>
+        <v>101700</v>
       </c>
       <c r="E9" s="3">
-        <v>89500</v>
+        <v>88900</v>
       </c>
       <c r="F9" s="3">
-        <v>88400</v>
+        <v>90100</v>
       </c>
       <c r="G9" s="3">
-        <v>80900</v>
+        <v>89000</v>
       </c>
       <c r="H9" s="3">
-        <v>85200</v>
+        <v>81400</v>
       </c>
       <c r="I9" s="3">
-        <v>76700</v>
+        <v>85800</v>
       </c>
       <c r="J9" s="3">
+        <v>77200</v>
+      </c>
+      <c r="K9" s="3">
         <v>84900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>81200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>89200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>80100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>66500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>61900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>60200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>58900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>54800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>27200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>58400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>47400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>34800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>32800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>24500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>32900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>14300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>8800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>11400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>502800</v>
+        <v>523200</v>
       </c>
       <c r="E10" s="3">
-        <v>451000</v>
+        <v>506200</v>
       </c>
       <c r="F10" s="3">
-        <v>408600</v>
+        <v>454100</v>
       </c>
       <c r="G10" s="3">
-        <v>458600</v>
+        <v>411300</v>
       </c>
       <c r="H10" s="3">
-        <v>487000</v>
+        <v>461700</v>
       </c>
       <c r="I10" s="3">
-        <v>500900</v>
+        <v>490300</v>
       </c>
       <c r="J10" s="3">
+        <v>504300</v>
+      </c>
+      <c r="K10" s="3">
         <v>511600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>528100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>566600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>494600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>434500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>402700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>485500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>433300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>447300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>342400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>344600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>300000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>272100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>411900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>65500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>29500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>71700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>55600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>41100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1071,8 +1083,9 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1157,8 +1170,11 @@
       <c r="AD12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1243,8 +1259,11 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1329,8 +1348,11 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1376,8 +1398,8 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>8</v>
+      <c r="R15" s="3">
+        <v>0</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>8</v>
@@ -1394,29 +1416,32 @@
       <c r="W15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X15" s="3">
+      <c r="X15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y15" s="3">
         <v>100</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA15" s="3">
-        <v>100</v>
+      <c r="AA15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB15" s="3">
         <v>100</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>8</v>
+      <c r="AC15" s="3">
+        <v>100</v>
       </c>
       <c r="AD15" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1444,180 +1469,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>399300</v>
+        <v>447100</v>
       </c>
       <c r="E17" s="3">
-        <v>377300</v>
+        <v>402100</v>
       </c>
       <c r="F17" s="3">
-        <v>357900</v>
+        <v>379900</v>
       </c>
       <c r="G17" s="3">
-        <v>409100</v>
+        <v>360400</v>
       </c>
       <c r="H17" s="3">
-        <v>412300</v>
+        <v>411900</v>
       </c>
       <c r="I17" s="3">
-        <v>438000</v>
+        <v>415100</v>
       </c>
       <c r="J17" s="3">
+        <v>441000</v>
+      </c>
+      <c r="K17" s="3">
         <v>408800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>405100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>386500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>308600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>284200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>291800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>343700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>345800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>473100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>329300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>256000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>218000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>175600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>139100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>68400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>141500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>55400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>36100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>49600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>9900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>191800</v>
+        <v>177900</v>
       </c>
       <c r="E18" s="3">
-        <v>163100</v>
+        <v>193100</v>
       </c>
       <c r="F18" s="3">
-        <v>139100</v>
+        <v>164200</v>
       </c>
       <c r="G18" s="3">
-        <v>130300</v>
+        <v>140000</v>
       </c>
       <c r="H18" s="3">
-        <v>159900</v>
+        <v>131200</v>
       </c>
       <c r="I18" s="3">
-        <v>139600</v>
+        <v>161000</v>
       </c>
       <c r="J18" s="3">
+        <v>140500</v>
+      </c>
+      <c r="K18" s="3">
         <v>187700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>204100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>269200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>266100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>216800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>172800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>202100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>146400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>29100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>40400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>147000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>129400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>131300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>305500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>21500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-79200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>30600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>28400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-8200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-5600</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1648,94 +1680,98 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>12300</v>
+        <v>7100</v>
       </c>
       <c r="E20" s="3">
-        <v>25500</v>
+        <v>12400</v>
       </c>
       <c r="F20" s="3">
-        <v>13100</v>
+        <v>25700</v>
       </c>
       <c r="G20" s="3">
+        <v>13200</v>
+      </c>
+      <c r="H20" s="3">
         <v>11200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1800</v>
       </c>
-      <c r="I20" s="3">
-        <v>19900</v>
-      </c>
       <c r="J20" s="3">
+        <v>20100</v>
+      </c>
+      <c r="K20" s="3">
         <v>4400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>8300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>4100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>14400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>6600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>15400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>12900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>7300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>6900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>13600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-5200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>8800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>800</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>400</v>
       </c>
       <c r="Z20" s="3">
         <v>400</v>
       </c>
       <c r="AA20" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AB20" s="3">
         <v>200</v>
       </c>
       <c r="AC20" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD20" s="3">
         <v>100</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1796,32 +1832,35 @@
       <c r="V21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X21" s="3">
         <v>306600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>22700</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AA21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC21" s="3">
         <v>3200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-8000</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1852,8 +1891,8 @@
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>8</v>
+      <c r="M22" s="3">
+        <v>0</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>8</v>
@@ -1870,18 +1909,18 @@
       <c r="R22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S22" s="3">
+      <c r="S22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T22" s="3">
         <v>2200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>4000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>800</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W22" s="3" t="s">
         <v>8</v>
       </c>
@@ -1894,8 +1933,8 @@
       <c r="Z22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA22" s="3">
-        <v>0</v>
+      <c r="AA22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
@@ -1906,180 +1945,189 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>204100</v>
+        <v>185000</v>
       </c>
       <c r="E23" s="3">
-        <v>188700</v>
+        <v>205500</v>
       </c>
       <c r="F23" s="3">
-        <v>152200</v>
+        <v>189900</v>
       </c>
       <c r="G23" s="3">
-        <v>141500</v>
+        <v>153200</v>
       </c>
       <c r="H23" s="3">
-        <v>161800</v>
+        <v>142500</v>
       </c>
       <c r="I23" s="3">
-        <v>159500</v>
+        <v>162900</v>
       </c>
       <c r="J23" s="3">
+        <v>160600</v>
+      </c>
+      <c r="K23" s="3">
         <v>192000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>212400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>273300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>280500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>223500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>188200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>215000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>153700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>36000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>51800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>143900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>123400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>140100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>306100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>22300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-78800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>31000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>28500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>3100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-8000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-5600</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>47000</v>
+        <v>31000</v>
       </c>
       <c r="E24" s="3">
-        <v>37700</v>
+        <v>47300</v>
       </c>
       <c r="F24" s="3">
-        <v>23800</v>
+        <v>37900</v>
       </c>
       <c r="G24" s="3">
-        <v>21700</v>
+        <v>24000</v>
       </c>
       <c r="H24" s="3">
-        <v>25300</v>
+        <v>21800</v>
       </c>
       <c r="I24" s="3">
-        <v>24900</v>
+        <v>25500</v>
       </c>
       <c r="J24" s="3">
+        <v>25100</v>
+      </c>
+      <c r="K24" s="3">
         <v>29900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>32500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>51000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>58200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>35900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>20500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>33500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>24500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>7100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-14300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>29500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>27000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>30100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>64600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>7900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-4600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>7500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>6400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2164,8 +2212,11 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2173,85 +2224,88 @@
         <v>8</v>
       </c>
       <c r="E26" s="3">
-        <v>151000</v>
+        <v>158200</v>
       </c>
       <c r="F26" s="3">
-        <v>128400</v>
+        <v>152000</v>
       </c>
       <c r="G26" s="3">
-        <v>119800</v>
+        <v>129300</v>
       </c>
       <c r="H26" s="3">
-        <v>136500</v>
+        <v>120700</v>
       </c>
       <c r="I26" s="3">
-        <v>134600</v>
+        <v>137400</v>
       </c>
       <c r="J26" s="3">
+        <v>135500</v>
+      </c>
+      <c r="K26" s="3">
         <v>162200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>179800</v>
-      </c>
-      <c r="L26" s="3">
-        <v>222300</v>
       </c>
       <c r="M26" s="3">
         <v>222300</v>
       </c>
       <c r="N26" s="3">
+        <v>222300</v>
+      </c>
+      <c r="O26" s="3">
         <v>187500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>167600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>181500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>129200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>28900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>66200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>114400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>96400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>110000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>241500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>14400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-74200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>23500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>22100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-5900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2259,85 +2313,88 @@
         <v>8</v>
       </c>
       <c r="E27" s="3">
-        <v>151500</v>
+        <v>158800</v>
       </c>
       <c r="F27" s="3">
-        <v>129000</v>
+        <v>152600</v>
       </c>
       <c r="G27" s="3">
-        <v>120400</v>
+        <v>129900</v>
       </c>
       <c r="H27" s="3">
-        <v>137100</v>
+        <v>121200</v>
       </c>
       <c r="I27" s="3">
-        <v>135300</v>
+        <v>138000</v>
       </c>
       <c r="J27" s="3">
+        <v>136200</v>
+      </c>
+      <c r="K27" s="3">
         <v>162900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>182200</v>
-      </c>
-      <c r="L27" s="3">
-        <v>222300</v>
       </c>
       <c r="M27" s="3">
         <v>222300</v>
       </c>
       <c r="N27" s="3">
+        <v>222300</v>
+      </c>
+      <c r="O27" s="3">
         <v>187600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>167700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>181500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>129200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>28900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>66200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>114400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>96400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>110000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>241500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-419200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-74200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>23500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>22100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-5900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2422,8 +2479,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2508,8 +2568,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2594,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2680,94 +2746,100 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-12300</v>
+        <v>-7100</v>
       </c>
       <c r="E32" s="3">
-        <v>-25500</v>
+        <v>-12400</v>
       </c>
       <c r="F32" s="3">
-        <v>-13100</v>
+        <v>-25700</v>
       </c>
       <c r="G32" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="H32" s="3">
         <v>-11200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1800</v>
       </c>
-      <c r="I32" s="3">
-        <v>-19900</v>
-      </c>
       <c r="J32" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="K32" s="3">
         <v>-4400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-8300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-4100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-14400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-6600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-15400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-12900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-7300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-6900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-13600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>5200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-8800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-800</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-400</v>
       </c>
       <c r="Z32" s="3">
         <v>-400</v>
       </c>
       <c r="AA32" s="3">
-        <v>-200</v>
+        <v>-400</v>
       </c>
       <c r="AB32" s="3">
         <v>-200</v>
       </c>
       <c r="AC32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-100</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2775,85 +2847,88 @@
         <v>8</v>
       </c>
       <c r="E33" s="3">
-        <v>151500</v>
+        <v>158800</v>
       </c>
       <c r="F33" s="3">
-        <v>129000</v>
+        <v>152600</v>
       </c>
       <c r="G33" s="3">
-        <v>120400</v>
+        <v>129900</v>
       </c>
       <c r="H33" s="3">
-        <v>137100</v>
+        <v>121200</v>
       </c>
       <c r="I33" s="3">
-        <v>135300</v>
+        <v>138000</v>
       </c>
       <c r="J33" s="3">
+        <v>136200</v>
+      </c>
+      <c r="K33" s="3">
         <v>162900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>182200</v>
-      </c>
-      <c r="L33" s="3">
-        <v>222300</v>
       </c>
       <c r="M33" s="3">
         <v>222300</v>
       </c>
       <c r="N33" s="3">
+        <v>222300</v>
+      </c>
+      <c r="O33" s="3">
         <v>187600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>167700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>181500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>129200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>28900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>66200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>114400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>96400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>110000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>241500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-419200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-74200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>23500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>22100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-5900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2938,8 +3013,11 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2947,176 +3025,182 @@
         <v>8</v>
       </c>
       <c r="E35" s="3">
-        <v>151500</v>
+        <v>158800</v>
       </c>
       <c r="F35" s="3">
-        <v>129000</v>
+        <v>152600</v>
       </c>
       <c r="G35" s="3">
-        <v>120400</v>
+        <v>129900</v>
       </c>
       <c r="H35" s="3">
-        <v>137100</v>
+        <v>121200</v>
       </c>
       <c r="I35" s="3">
-        <v>135300</v>
+        <v>138000</v>
       </c>
       <c r="J35" s="3">
+        <v>136200</v>
+      </c>
+      <c r="K35" s="3">
         <v>162900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>182200</v>
-      </c>
-      <c r="L35" s="3">
-        <v>222300</v>
       </c>
       <c r="M35" s="3">
         <v>222300</v>
       </c>
       <c r="N35" s="3">
+        <v>222300</v>
+      </c>
+      <c r="O35" s="3">
         <v>187600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>167700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>181500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>129200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>28900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>66200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>114400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>96400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>110000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>241500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-419200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-74200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>23500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>22100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-5900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3147,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3179,80 +3264,81 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>681900</v>
+        <v>580800</v>
       </c>
       <c r="E41" s="3">
-        <v>725800</v>
+        <v>686500</v>
       </c>
       <c r="F41" s="3">
-        <v>708100</v>
+        <v>730700</v>
       </c>
       <c r="G41" s="3">
-        <v>989400</v>
+        <v>712900</v>
       </c>
       <c r="H41" s="3">
-        <v>996900</v>
+        <v>996200</v>
       </c>
       <c r="I41" s="3">
-        <v>961800</v>
+        <v>1003700</v>
       </c>
       <c r="J41" s="3">
+        <v>968300</v>
+      </c>
+      <c r="K41" s="3">
         <v>852800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>842700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>600500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>745700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>831600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>615000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>710400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>563400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>570500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>324600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>287700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>285100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>195700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>210000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>281100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>65600</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3265,28 +3351,31 @@
       <c r="AD41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="E42" s="3">
-        <v>34200</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>32600</v>
+        <v>34400</v>
       </c>
       <c r="G42" s="3">
+        <v>32800</v>
+      </c>
+      <c r="H42" s="3">
         <v>7900</v>
       </c>
-      <c r="H42" s="3">
-        <v>4100</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>8</v>
+      <c r="I42" s="3">
+        <v>4200</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>8</v>
@@ -3300,8 +3389,8 @@
       <c r="M42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
+      <c r="N42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
@@ -3351,80 +3440,83 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4247300</v>
+        <v>4404900</v>
       </c>
       <c r="E43" s="3">
-        <v>3915400</v>
+        <v>4276200</v>
       </c>
       <c r="F43" s="3">
-        <v>3506000</v>
+        <v>3942100</v>
       </c>
       <c r="G43" s="3">
-        <v>3141600</v>
+        <v>3529900</v>
       </c>
       <c r="H43" s="3">
-        <v>3028700</v>
+        <v>3163000</v>
       </c>
       <c r="I43" s="3">
-        <v>2625500</v>
+        <v>3049300</v>
       </c>
       <c r="J43" s="3">
+        <v>2643400</v>
+      </c>
+      <c r="K43" s="3">
         <v>2653400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2444000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2516000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2232800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1947600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1918900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2034700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2097200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2153800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2168400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2094600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1663200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1050200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>642500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>177700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>272300</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3437,8 +3529,11 @@
       <c r="AD43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3523,80 +3618,83 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>595300</v>
+        <v>544700</v>
       </c>
       <c r="E45" s="3">
-        <v>510600</v>
+        <v>599400</v>
       </c>
       <c r="F45" s="3">
-        <v>588600</v>
+        <v>514000</v>
       </c>
       <c r="G45" s="3">
-        <v>569300</v>
+        <v>592600</v>
       </c>
       <c r="H45" s="3">
-        <v>565200</v>
+        <v>573200</v>
       </c>
       <c r="I45" s="3">
-        <v>666700</v>
+        <v>569100</v>
       </c>
       <c r="J45" s="3">
+        <v>671200</v>
+      </c>
+      <c r="K45" s="3">
         <v>555600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>537700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>521500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>563400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>511100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>511200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>517600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>606800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>597700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>510200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>498200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>427100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>354900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>213900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>156100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>102600</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3609,80 +3707,83 @@
       <c r="AD45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>5524600</v>
+        <v>5532400</v>
       </c>
       <c r="E46" s="3">
-        <v>5186000</v>
+        <v>5562200</v>
       </c>
       <c r="F46" s="3">
-        <v>4835400</v>
+        <v>5221300</v>
       </c>
       <c r="G46" s="3">
-        <v>4708200</v>
+        <v>4868300</v>
       </c>
       <c r="H46" s="3">
-        <v>4595000</v>
+        <v>4740200</v>
       </c>
       <c r="I46" s="3">
-        <v>4253900</v>
+        <v>4626300</v>
       </c>
       <c r="J46" s="3">
+        <v>4282900</v>
+      </c>
+      <c r="K46" s="3">
         <v>4061900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3824400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3638000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3541900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3290300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3045100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3262700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3267400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3322000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3003100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2880600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2375500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1600800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1066300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>615000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>440500</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA46" s="3" t="s">
         <v>8</v>
       </c>
@@ -3695,68 +3796,71 @@
       <c r="AD46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>498300</v>
+        <v>506800</v>
       </c>
       <c r="E47" s="3">
-        <v>495500</v>
+        <v>501700</v>
       </c>
       <c r="F47" s="3">
-        <v>496600</v>
+        <v>498900</v>
       </c>
       <c r="G47" s="3">
-        <v>568900</v>
+        <v>500000</v>
       </c>
       <c r="H47" s="3">
-        <v>609700</v>
+        <v>572800</v>
       </c>
       <c r="I47" s="3">
-        <v>647300</v>
+        <v>613900</v>
       </c>
       <c r="J47" s="3">
+        <v>651700</v>
+      </c>
+      <c r="K47" s="3">
         <v>607100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>526500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>579600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>358000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>201600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>144900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>127700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>99300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>55100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>12100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>100</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W47" s="3" t="s">
         <v>8</v>
       </c>
@@ -3769,8 +3873,8 @@
       <c r="Z47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA47" s="3">
-        <v>0</v>
+      <c r="AA47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB47" s="3">
         <v>0</v>
@@ -3781,67 +3885,70 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>27800</v>
+        <v>38500</v>
       </c>
       <c r="E48" s="3">
-        <v>22900</v>
+        <v>28000</v>
       </c>
       <c r="F48" s="3">
-        <v>19500</v>
+        <v>23000</v>
       </c>
       <c r="G48" s="3">
-        <v>14300</v>
+        <v>19600</v>
       </c>
       <c r="H48" s="3">
-        <v>12400</v>
+        <v>14400</v>
       </c>
       <c r="I48" s="3">
-        <v>13300</v>
+        <v>12500</v>
       </c>
       <c r="J48" s="3">
+        <v>13400</v>
+      </c>
+      <c r="K48" s="3">
         <v>13100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>11100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>11600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>11200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2200</v>
-      </c>
-      <c r="V48" s="3">
-        <v>1000</v>
       </c>
       <c r="W48" s="3">
         <v>1000</v>
@@ -3852,8 +3959,8 @@
       <c r="Y48" s="3">
         <v>1000</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>8</v>
+      <c r="Z48" s="3">
+        <v>1000</v>
       </c>
       <c r="AA48" s="3" t="s">
         <v>8</v>
@@ -3867,22 +3974,25 @@
       <c r="AD48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>143200</v>
+        <v>137800</v>
       </c>
       <c r="E49" s="3">
-        <v>700</v>
+        <v>7600</v>
       </c>
       <c r="F49" s="3">
         <v>700</v>
       </c>
       <c r="G49" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="H49" s="3">
         <v>700</v>
@@ -3891,19 +4001,19 @@
         <v>700</v>
       </c>
       <c r="J49" s="3">
+        <v>700</v>
+      </c>
+      <c r="K49" s="3">
         <v>800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>141100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>700</v>
-      </c>
-      <c r="N49" s="3">
-        <v>500</v>
       </c>
       <c r="O49" s="3">
         <v>500</v>
@@ -3912,22 +4022,22 @@
         <v>500</v>
       </c>
       <c r="Q49" s="3">
+        <v>500</v>
+      </c>
+      <c r="R49" s="3">
         <v>400</v>
-      </c>
-      <c r="R49" s="3">
-        <v>500</v>
       </c>
       <c r="S49" s="3">
         <v>500</v>
       </c>
       <c r="T49" s="3">
+        <v>500</v>
+      </c>
+      <c r="U49" s="3">
         <v>600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>300</v>
-      </c>
-      <c r="V49" s="3">
-        <v>100</v>
       </c>
       <c r="W49" s="3">
         <v>100</v>
@@ -3938,8 +4048,8 @@
       <c r="Y49" s="3">
         <v>100</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>8</v>
+      <c r="Z49" s="3">
+        <v>100</v>
       </c>
       <c r="AA49" s="3" t="s">
         <v>8</v>
@@ -3953,8 +4063,11 @@
       <c r="AD49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4039,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4125,80 +4241,83 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>163100</v>
+        <v>148400</v>
       </c>
       <c r="E52" s="3">
-        <v>287900</v>
+        <v>300900</v>
       </c>
       <c r="F52" s="3">
-        <v>292400</v>
+        <v>289900</v>
       </c>
       <c r="G52" s="3">
-        <v>278600</v>
+        <v>294400</v>
       </c>
       <c r="H52" s="3">
-        <v>300200</v>
+        <v>280500</v>
       </c>
       <c r="I52" s="3">
-        <v>285600</v>
+        <v>302200</v>
       </c>
       <c r="J52" s="3">
+        <v>287600</v>
+      </c>
+      <c r="K52" s="3">
         <v>267100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>115000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>164800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>147500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>207100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>194700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>169500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>154500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>212000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>107400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>25500</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W52" s="3">
-        <v>0</v>
+      <c r="W52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
         <v>86800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>67400</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4211,8 +4330,11 @@
       <c r="AD52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4297,80 +4419,83 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>6357100</v>
+        <v>6369700</v>
       </c>
       <c r="E54" s="3">
-        <v>5993000</v>
+        <v>6400400</v>
       </c>
       <c r="F54" s="3">
-        <v>5644600</v>
+        <v>6033800</v>
       </c>
       <c r="G54" s="3">
-        <v>5570600</v>
+        <v>5683000</v>
       </c>
       <c r="H54" s="3">
-        <v>5518000</v>
+        <v>5608500</v>
       </c>
       <c r="I54" s="3">
-        <v>5200900</v>
+        <v>5555600</v>
       </c>
       <c r="J54" s="3">
+        <v>5236300</v>
+      </c>
+      <c r="K54" s="3">
         <v>4950100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4616300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4390300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4056700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3707600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3394700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3571600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3533800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3601200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3134400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2913900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2378000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1601900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1067400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>702900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>509000</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>8</v>
       </c>
@@ -4383,8 +4508,11 @@
       <c r="AD54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4415,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4447,8 +4576,9 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4533,68 +4663,71 @@
       <c r="AD57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>104400</v>
+        <v>111000</v>
       </c>
       <c r="E58" s="3">
-        <v>35900</v>
+        <v>105100</v>
       </c>
       <c r="F58" s="3">
-        <v>20700</v>
+        <v>36100</v>
       </c>
       <c r="G58" s="3">
-        <v>20700</v>
+        <v>20900</v>
       </c>
       <c r="H58" s="3">
-        <v>88300</v>
+        <v>20900</v>
       </c>
       <c r="I58" s="3">
-        <v>84400</v>
+        <v>88900</v>
       </c>
       <c r="J58" s="3">
+        <v>85000</v>
+      </c>
+      <c r="K58" s="3">
         <v>81000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>54800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>47700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>48300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>32300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>26000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>27200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>27700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>68600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>30800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>239500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>223900</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>8</v>
       </c>
@@ -4607,8 +4740,8 @@
       <c r="Z58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
+      <c r="AA58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB58" s="3">
         <v>0</v>
@@ -4619,80 +4752,83 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2518500</v>
+        <v>2655400</v>
       </c>
       <c r="E59" s="3">
-        <v>2199100</v>
+        <v>2535700</v>
       </c>
       <c r="F59" s="3">
-        <v>2489100</v>
+        <v>2214100</v>
       </c>
       <c r="G59" s="3">
-        <v>2292100</v>
+        <v>2506100</v>
       </c>
       <c r="H59" s="3">
-        <v>2389200</v>
+        <v>2307700</v>
       </c>
       <c r="I59" s="3">
-        <v>2238600</v>
+        <v>2405500</v>
       </c>
       <c r="J59" s="3">
+        <v>2253800</v>
+      </c>
+      <c r="K59" s="3">
         <v>1939500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1893900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1870500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1877300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1841500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1837100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1863800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1930800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2084600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1457800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1280000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1109500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>754700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>420300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>413100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>452200</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>8</v>
       </c>
@@ -4705,80 +4841,83 @@
       <c r="AD59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2623000</v>
+        <v>2766400</v>
       </c>
       <c r="E60" s="3">
-        <v>2235000</v>
+        <v>2640800</v>
       </c>
       <c r="F60" s="3">
-        <v>2509800</v>
+        <v>2250200</v>
       </c>
       <c r="G60" s="3">
-        <v>2312800</v>
+        <v>2526900</v>
       </c>
       <c r="H60" s="3">
-        <v>2477600</v>
+        <v>2328600</v>
       </c>
       <c r="I60" s="3">
-        <v>2323000</v>
+        <v>2494400</v>
       </c>
       <c r="J60" s="3">
+        <v>2338800</v>
+      </c>
+      <c r="K60" s="3">
         <v>2020400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1948600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1918300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1925600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1873800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1863100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1891000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1958600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2153300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1488600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1519500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1333300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>754700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>420300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>413100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>452200</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA60" s="3" t="s">
         <v>8</v>
       </c>
@@ -4791,8 +4930,11 @@
       <c r="AD60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4877,74 +5019,77 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>816500</v>
+        <v>543400</v>
       </c>
       <c r="E62" s="3">
-        <v>874100</v>
+        <v>822100</v>
       </c>
       <c r="F62" s="3">
-        <v>410800</v>
+        <v>880000</v>
       </c>
       <c r="G62" s="3">
-        <v>643700</v>
+        <v>413600</v>
       </c>
       <c r="H62" s="3">
-        <v>556500</v>
+        <v>648100</v>
       </c>
       <c r="I62" s="3">
-        <v>527700</v>
+        <v>560200</v>
       </c>
       <c r="J62" s="3">
+        <v>531300</v>
+      </c>
+      <c r="K62" s="3">
         <v>695500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>571100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>465300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>337600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>317300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>211800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>467700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>542400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>490300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>534900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>342300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>121400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>54400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2300</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>8</v>
       </c>
@@ -4963,8 +5108,11 @@
       <c r="AD62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5049,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5135,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5221,80 +5375,83 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3450000</v>
+        <v>3319900</v>
       </c>
       <c r="E66" s="3">
-        <v>3119600</v>
+        <v>3473500</v>
       </c>
       <c r="F66" s="3">
-        <v>2931700</v>
+        <v>3140800</v>
       </c>
       <c r="G66" s="3">
-        <v>2968200</v>
+        <v>2951700</v>
       </c>
       <c r="H66" s="3">
-        <v>3046200</v>
+        <v>2988400</v>
       </c>
       <c r="I66" s="3">
-        <v>2851100</v>
+        <v>3066900</v>
       </c>
       <c r="J66" s="3">
+        <v>2870500</v>
+      </c>
+      <c r="K66" s="3">
         <v>2717000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2521500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2383600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2263300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2191200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2075000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2358900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2501200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2643700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2023600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1862000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1454700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>809100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>422600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>413100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>452200</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>8</v>
       </c>
@@ -5307,8 +5464,11 @@
       <c r="AD66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5339,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5425,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5511,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5577,11 +5744,11 @@
         <v>0</v>
       </c>
       <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
         <v>628600</v>
       </c>
-      <c r="Y70" s="3">
-        <v>0</v>
-      </c>
       <c r="Z70" s="3">
         <v>0</v>
       </c>
@@ -5597,8 +5764,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5683,8 +5853,11 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -5697,11 +5870,11 @@
       <c r="F72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G72" s="3">
-        <v>1767900</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>8</v>
+      <c r="G72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H72" s="3">
+        <v>1780000</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>8</v>
@@ -5709,54 +5882,54 @@
       <c r="J72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L72" s="3">
         <v>1328500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1222000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1010000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>763500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>575900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>432200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>250600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>130000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>318900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>256100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>141600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>44300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-62500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-339400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-109100</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>8</v>
       </c>
@@ -5769,8 +5942,11 @@
       <c r="AD72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5855,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5941,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6027,80 +6209,83 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2907000</v>
+        <v>3049700</v>
       </c>
       <c r="E76" s="3">
-        <v>2873400</v>
+        <v>2926800</v>
       </c>
       <c r="F76" s="3">
-        <v>2712900</v>
+        <v>2893000</v>
       </c>
       <c r="G76" s="3">
-        <v>2602400</v>
+        <v>2731400</v>
       </c>
       <c r="H76" s="3">
-        <v>2471800</v>
+        <v>2620100</v>
       </c>
       <c r="I76" s="3">
-        <v>2349900</v>
+        <v>2488600</v>
       </c>
       <c r="J76" s="3">
+        <v>2365900</v>
+      </c>
+      <c r="K76" s="3">
         <v>2233100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2094800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2006700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1793300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1516400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1319700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1212800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1032600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>957400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1110700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1051900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>923300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>792800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>644800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-338900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>56800</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>8</v>
       </c>
@@ -6113,8 +6298,11 @@
       <c r="AD76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6199,99 +6387,105 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6299,85 +6493,88 @@
         <v>8</v>
       </c>
       <c r="E81" s="3">
-        <v>151500</v>
+        <v>158800</v>
       </c>
       <c r="F81" s="3">
-        <v>129000</v>
+        <v>152600</v>
       </c>
       <c r="G81" s="3">
-        <v>120400</v>
+        <v>129900</v>
       </c>
       <c r="H81" s="3">
-        <v>137100</v>
+        <v>121200</v>
       </c>
       <c r="I81" s="3">
-        <v>135300</v>
+        <v>138000</v>
       </c>
       <c r="J81" s="3">
+        <v>136200</v>
+      </c>
+      <c r="K81" s="3">
         <v>162900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>182200</v>
-      </c>
-      <c r="L81" s="3">
-        <v>222300</v>
       </c>
       <c r="M81" s="3">
         <v>222300</v>
       </c>
       <c r="N81" s="3">
+        <v>222300</v>
+      </c>
+      <c r="O81" s="3">
         <v>187600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>167700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>181500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>129200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>28900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>66200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>114400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>96400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>110000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>241500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-419200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-74200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>23500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>22100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-5900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6408,8 +6605,9 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6476,8 +6674,8 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>8</v>
+      <c r="Y83" s="3">
+        <v>0</v>
       </c>
       <c r="Z83" s="3" t="s">
         <v>8</v>
@@ -6494,8 +6692,11 @@
       <c r="AD83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6580,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6666,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6752,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6838,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6924,47 +7137,50 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>171800</v>
+      <c r="D89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E89" s="3">
-        <v>243200</v>
+        <v>172900</v>
       </c>
       <c r="F89" s="3">
-        <v>243200</v>
+        <v>489700</v>
       </c>
       <c r="G89" s="3">
-        <v>247500</v>
+        <v>-578500</v>
       </c>
       <c r="H89" s="3">
-        <v>219800</v>
+        <v>249200</v>
       </c>
       <c r="I89" s="3">
-        <v>154400</v>
+        <v>221300</v>
       </c>
       <c r="J89" s="3">
+        <v>352800</v>
+      </c>
+      <c r="K89" s="3">
         <v>196000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>132800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>252600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>186200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>244000</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>8</v>
       </c>
@@ -6977,8 +7193,8 @@
       <c r="S89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
+      <c r="T89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U89" s="3">
         <v>0</v>
@@ -6992,8 +7208,8 @@
       <c r="X89" s="3">
         <v>0</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>8</v>
+      <c r="Y89" s="3">
+        <v>0</v>
       </c>
       <c r="Z89" s="3" t="s">
         <v>8</v>
@@ -7010,8 +7226,11 @@
       <c r="AD89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7042,8 +7261,9 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7110,8 +7330,8 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>8</v>
+      <c r="Y91" s="3">
+        <v>0</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>8</v>
@@ -7128,8 +7348,11 @@
       <c r="AD91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7214,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7300,47 +7526,50 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>-312200</v>
+      <c r="D94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E94" s="3">
-        <v>-474600</v>
+        <v>-314300</v>
       </c>
       <c r="F94" s="3">
-        <v>-492100</v>
+        <v>-973300</v>
       </c>
       <c r="G94" s="3">
-        <v>-232000</v>
+        <v>527100</v>
       </c>
       <c r="H94" s="3">
-        <v>-411600</v>
+        <v>-233600</v>
       </c>
       <c r="I94" s="3">
-        <v>-34900</v>
+        <v>-414400</v>
       </c>
       <c r="J94" s="3">
+        <v>-374600</v>
+      </c>
+      <c r="K94" s="3">
         <v>-337100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>10100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-487700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-323400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-63400</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>8</v>
       </c>
@@ -7353,8 +7582,8 @@
       <c r="S94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
+      <c r="T94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
@@ -7368,8 +7597,8 @@
       <c r="X94" s="3">
         <v>0</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>8</v>
+      <c r="Y94" s="3">
+        <v>0</v>
       </c>
       <c r="Z94" s="3" t="s">
         <v>8</v>
@@ -7386,8 +7615,11 @@
       <c r="AD94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7418,8 +7650,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7504,8 +7737,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7590,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7676,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7762,47 +8004,50 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>97100</v>
+      <c r="D100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E100" s="3">
-        <v>170700</v>
+        <v>97700</v>
       </c>
       <c r="F100" s="3">
-        <v>5400</v>
+        <v>177300</v>
       </c>
       <c r="G100" s="3">
-        <v>26800</v>
+        <v>-440000</v>
       </c>
       <c r="H100" s="3">
-        <v>121700</v>
+        <v>26900</v>
       </c>
       <c r="I100" s="3">
-        <v>145300</v>
+        <v>122500</v>
       </c>
       <c r="J100" s="3">
+        <v>296000</v>
+      </c>
+      <c r="K100" s="3">
         <v>148700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>149600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>64700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>77300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>25700</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>8</v>
       </c>
@@ -7815,8 +8060,8 @@
       <c r="S100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
+      <c r="T100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U100" s="3">
         <v>0</v>
@@ -7830,8 +8075,8 @@
       <c r="X100" s="3">
         <v>0</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>8</v>
+      <c r="Y100" s="3">
+        <v>0</v>
       </c>
       <c r="Z100" s="3" t="s">
         <v>8</v>
@@ -7848,46 +8093,49 @@
       <c r="AD100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3">
         <v>700</v>
       </c>
-      <c r="E101" s="3">
-        <v>1200</v>
-      </c>
       <c r="F101" s="3">
-        <v>-400</v>
+        <v>800</v>
       </c>
       <c r="G101" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H101" s="3">
         <v>-3200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1000</v>
       </c>
-      <c r="I101" s="3">
-        <v>200</v>
-      </c>
       <c r="J101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K101" s="3">
         <v>-500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="N101" s="3">
         <v>-200</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>8</v>
+      <c r="O101" s="3">
+        <v>-200</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>8</v>
@@ -7901,8 +8149,8 @@
       <c r="S101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
+      <c r="T101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
@@ -7916,8 +8164,8 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>8</v>
+      <c r="Y101" s="3">
+        <v>0</v>
       </c>
       <c r="Z101" s="3" t="s">
         <v>8</v>
@@ -7934,47 +8182,50 @@
       <c r="AD101" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>-42700</v>
+      <c r="D102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E102" s="3">
-        <v>-59500</v>
+        <v>-43000</v>
       </c>
       <c r="F102" s="3">
-        <v>-244000</v>
+        <v>-305500</v>
       </c>
       <c r="G102" s="3">
-        <v>39100</v>
+        <v>-489300</v>
       </c>
       <c r="H102" s="3">
-        <v>-69200</v>
+        <v>39300</v>
       </c>
       <c r="I102" s="3">
-        <v>265000</v>
+        <v>-69600</v>
       </c>
       <c r="J102" s="3">
+        <v>273900</v>
+      </c>
+      <c r="K102" s="3">
         <v>7100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>292400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-170400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-60100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>206100</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>8</v>
       </c>
@@ -7987,8 +8238,8 @@
       <c r="S102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
+      <c r="T102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U102" s="3">
         <v>0</v>
@@ -8002,8 +8253,8 @@
       <c r="X102" s="3">
         <v>0</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>8</v>
+      <c r="Y102" s="3">
+        <v>0</v>
       </c>
       <c r="Z102" s="3" t="s">
         <v>8</v>
@@ -8018,6 +8269,9 @@
         <v>8</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/QFIN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QFIN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="92">
   <si>
     <t>QFIN</t>
   </si>
@@ -656,225 +656,232 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>625000</v>
+        <v>573800</v>
       </c>
       <c r="E8" s="3">
-        <v>595100</v>
+        <v>621100</v>
       </c>
       <c r="F8" s="3">
-        <v>544200</v>
+        <v>591500</v>
       </c>
       <c r="G8" s="3">
-        <v>500400</v>
+        <v>540800</v>
       </c>
       <c r="H8" s="3">
-        <v>543100</v>
+        <v>497300</v>
       </c>
       <c r="I8" s="3">
-        <v>576100</v>
+        <v>539700</v>
       </c>
       <c r="J8" s="3">
+        <v>572500</v>
+      </c>
+      <c r="K8" s="3">
         <v>581500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>596500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>609300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>655700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>574700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>501000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>464600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>545700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>492200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>502100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>369700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>403000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>347400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>306900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>444600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>89900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>62300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>86000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>64400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>52500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -882,177 +889,183 @@
         <v>101700</v>
       </c>
       <c r="E9" s="3">
-        <v>88900</v>
+        <v>101100</v>
       </c>
       <c r="F9" s="3">
-        <v>90100</v>
+        <v>88400</v>
       </c>
       <c r="G9" s="3">
-        <v>89000</v>
+        <v>89500</v>
       </c>
       <c r="H9" s="3">
-        <v>81400</v>
+        <v>88500</v>
       </c>
       <c r="I9" s="3">
-        <v>85800</v>
+        <v>80900</v>
       </c>
       <c r="J9" s="3">
+        <v>85300</v>
+      </c>
+      <c r="K9" s="3">
         <v>77200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>84900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>81200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>89200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>80100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>66500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>61900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>60200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>58900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>54800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>27200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>58400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>47400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>34800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>32800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>24500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>32900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>14300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>8800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>11400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>523200</v>
+        <v>472100</v>
       </c>
       <c r="E10" s="3">
-        <v>506200</v>
+        <v>520000</v>
       </c>
       <c r="F10" s="3">
-        <v>454100</v>
+        <v>503100</v>
       </c>
       <c r="G10" s="3">
-        <v>411300</v>
+        <v>451300</v>
       </c>
       <c r="H10" s="3">
-        <v>461700</v>
+        <v>408800</v>
       </c>
       <c r="I10" s="3">
-        <v>490300</v>
+        <v>458800</v>
       </c>
       <c r="J10" s="3">
+        <v>487300</v>
+      </c>
+      <c r="K10" s="3">
         <v>504300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>511600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>528100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>566600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>494600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>434500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>402700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>485500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>433300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>447300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>342400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>344600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>300000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>272100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>411900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>65500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>29500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>71700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>55600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>41100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1084,8 +1097,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1173,8 +1187,11 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,8 +1279,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1351,8 +1371,11 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1401,8 +1424,8 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>8</v>
+      <c r="S15" s="3">
+        <v>0</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>8</v>
@@ -1419,29 +1442,32 @@
       <c r="X15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Y15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z15" s="3">
         <v>100</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB15" s="3">
-        <v>100</v>
+      <c r="AB15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC15" s="3">
         <v>100</v>
       </c>
-      <c r="AD15" s="3" t="s">
-        <v>8</v>
+      <c r="AD15" s="3">
+        <v>100</v>
       </c>
       <c r="AE15" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,186 +1496,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>447100</v>
+        <v>385300</v>
       </c>
       <c r="E17" s="3">
-        <v>402100</v>
+        <v>444300</v>
       </c>
       <c r="F17" s="3">
-        <v>379900</v>
+        <v>399600</v>
       </c>
       <c r="G17" s="3">
-        <v>360400</v>
+        <v>377600</v>
       </c>
       <c r="H17" s="3">
-        <v>411900</v>
+        <v>358100</v>
       </c>
       <c r="I17" s="3">
-        <v>415100</v>
+        <v>409300</v>
       </c>
       <c r="J17" s="3">
+        <v>412500</v>
+      </c>
+      <c r="K17" s="3">
         <v>441000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>408800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>405100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>386500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>308600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>284200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>291800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>343700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>345800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>473100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>329300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>256000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>218000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>175600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>139100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>68400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>141500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>55400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>36100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>49600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>9900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>177900</v>
+        <v>188500</v>
       </c>
       <c r="E18" s="3">
-        <v>193100</v>
+        <v>176800</v>
       </c>
       <c r="F18" s="3">
-        <v>164200</v>
+        <v>191900</v>
       </c>
       <c r="G18" s="3">
-        <v>140000</v>
+        <v>163200</v>
       </c>
       <c r="H18" s="3">
-        <v>131200</v>
+        <v>139100</v>
       </c>
       <c r="I18" s="3">
-        <v>161000</v>
+        <v>130400</v>
       </c>
       <c r="J18" s="3">
+        <v>160000</v>
+      </c>
+      <c r="K18" s="3">
         <v>140500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>187700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>204100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>269200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>266100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>216800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>172800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>202100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>146400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>29100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>40400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>147000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>129400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>131300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>305500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>21500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-79200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>30600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>28400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-8200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-5600</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,97 +1714,101 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E20" s="3">
         <v>7100</v>
       </c>
-      <c r="E20" s="3">
-        <v>12400</v>
-      </c>
       <c r="F20" s="3">
-        <v>25700</v>
+        <v>12300</v>
       </c>
       <c r="G20" s="3">
-        <v>13200</v>
+        <v>25500</v>
       </c>
       <c r="H20" s="3">
+        <v>13100</v>
+      </c>
+      <c r="I20" s="3">
         <v>11200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>20100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>8300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>4100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>14400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>6600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>15400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>12900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>7300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>6900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>13600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-5200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>8800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>800</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>400</v>
       </c>
       <c r="AA20" s="3">
         <v>400</v>
       </c>
       <c r="AB20" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AC20" s="3">
         <v>200</v>
       </c>
       <c r="AD20" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE20" s="3">
         <v>100</v>
       </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1835,32 +1872,35 @@
       <c r="W21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y21" s="3">
         <v>306600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>22700</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AB21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD21" s="3">
         <v>3200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-8000</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1894,8 +1934,8 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>8</v>
+      <c r="N22" s="3">
+        <v>0</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>8</v>
@@ -1912,18 +1952,18 @@
       <c r="S22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T22" s="3">
+      <c r="T22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U22" s="3">
         <v>2200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>4000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>800</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X22" s="3" t="s">
         <v>8</v>
       </c>
@@ -1936,8 +1976,8 @@
       <c r="AA22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
+      <c r="AB22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC22" s="3">
         <v>0</v>
@@ -1948,186 +1988,195 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>185000</v>
+        <v>210900</v>
       </c>
       <c r="E23" s="3">
-        <v>205500</v>
+        <v>183900</v>
       </c>
       <c r="F23" s="3">
-        <v>189900</v>
+        <v>204200</v>
       </c>
       <c r="G23" s="3">
-        <v>153200</v>
+        <v>188800</v>
       </c>
       <c r="H23" s="3">
-        <v>142500</v>
+        <v>152300</v>
       </c>
       <c r="I23" s="3">
-        <v>162900</v>
+        <v>141600</v>
       </c>
       <c r="J23" s="3">
+        <v>161900</v>
+      </c>
+      <c r="K23" s="3">
         <v>160600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>192000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>212400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>273300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>280500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>223500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>188200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>215000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>153700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>36000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>51800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>143900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>123400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>140100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>306100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>22300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-78800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>31000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>28500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>3100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-8000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-5600</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>31000</v>
+        <v>50600</v>
       </c>
       <c r="E24" s="3">
-        <v>47300</v>
+        <v>30800</v>
       </c>
       <c r="F24" s="3">
-        <v>37900</v>
+        <v>47000</v>
       </c>
       <c r="G24" s="3">
-        <v>24000</v>
+        <v>37700</v>
       </c>
       <c r="H24" s="3">
-        <v>21800</v>
+        <v>23800</v>
       </c>
       <c r="I24" s="3">
-        <v>25500</v>
+        <v>21700</v>
       </c>
       <c r="J24" s="3">
+        <v>25300</v>
+      </c>
+      <c r="K24" s="3">
         <v>25100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>29900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>32500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>51000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>58200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>35900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>20500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>33500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>24500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>7100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-14300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>29500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>27000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>30100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>64600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>7900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-4600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>7500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>6400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>8</v>
+      <c r="D26" s="3">
+        <v>160300</v>
       </c>
       <c r="E26" s="3">
-        <v>158200</v>
+        <v>153000</v>
       </c>
       <c r="F26" s="3">
-        <v>152000</v>
+        <v>157200</v>
       </c>
       <c r="G26" s="3">
-        <v>129300</v>
+        <v>151100</v>
       </c>
       <c r="H26" s="3">
-        <v>120700</v>
+        <v>128500</v>
       </c>
       <c r="I26" s="3">
-        <v>137400</v>
+        <v>119900</v>
       </c>
       <c r="J26" s="3">
+        <v>136600</v>
+      </c>
+      <c r="K26" s="3">
         <v>135500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>162200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>179800</v>
-      </c>
-      <c r="M26" s="3">
-        <v>222300</v>
       </c>
       <c r="N26" s="3">
         <v>222300</v>
       </c>
       <c r="O26" s="3">
+        <v>222300</v>
+      </c>
+      <c r="P26" s="3">
         <v>187500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>167600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>181500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>129200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>28900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>66200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>114400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>96400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>110000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>241500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>14400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-74200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>23500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>22100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-5900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>8</v>
+      <c r="D27" s="3">
+        <v>160900</v>
       </c>
       <c r="E27" s="3">
-        <v>158800</v>
+        <v>153600</v>
       </c>
       <c r="F27" s="3">
-        <v>152600</v>
+        <v>157800</v>
       </c>
       <c r="G27" s="3">
-        <v>129900</v>
+        <v>151600</v>
       </c>
       <c r="H27" s="3">
-        <v>121200</v>
+        <v>129100</v>
       </c>
       <c r="I27" s="3">
-        <v>138000</v>
+        <v>120500</v>
       </c>
       <c r="J27" s="3">
+        <v>137200</v>
+      </c>
+      <c r="K27" s="3">
         <v>136200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>162900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>182200</v>
-      </c>
-      <c r="M27" s="3">
-        <v>222300</v>
       </c>
       <c r="N27" s="3">
         <v>222300</v>
       </c>
       <c r="O27" s="3">
+        <v>222300</v>
+      </c>
+      <c r="P27" s="3">
         <v>187600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>167700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>181500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>129200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>28900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>66200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>114400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>96400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>110000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>241500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-419200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-74200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>23500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>22100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-5900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2571,8 +2632,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,186 +2816,195 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-22400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-7100</v>
       </c>
-      <c r="E32" s="3">
-        <v>-12400</v>
-      </c>
       <c r="F32" s="3">
-        <v>-25700</v>
+        <v>-12300</v>
       </c>
       <c r="G32" s="3">
-        <v>-13200</v>
+        <v>-25500</v>
       </c>
       <c r="H32" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="I32" s="3">
         <v>-11200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-20100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-8300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-4100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-14400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-6600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-15400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-12900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-7300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-6900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-13600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>5200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-8800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-800</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-400</v>
       </c>
       <c r="AA32" s="3">
         <v>-400</v>
       </c>
       <c r="AB32" s="3">
-        <v>-200</v>
+        <v>-400</v>
       </c>
       <c r="AC32" s="3">
         <v>-200</v>
       </c>
       <c r="AD32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-100</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>8</v>
+      <c r="D33" s="3">
+        <v>160900</v>
       </c>
       <c r="E33" s="3">
-        <v>158800</v>
+        <v>153600</v>
       </c>
       <c r="F33" s="3">
-        <v>152600</v>
+        <v>157800</v>
       </c>
       <c r="G33" s="3">
-        <v>129900</v>
+        <v>151600</v>
       </c>
       <c r="H33" s="3">
-        <v>121200</v>
+        <v>129100</v>
       </c>
       <c r="I33" s="3">
-        <v>138000</v>
+        <v>120500</v>
       </c>
       <c r="J33" s="3">
+        <v>137200</v>
+      </c>
+      <c r="K33" s="3">
         <v>136200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>162900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>182200</v>
-      </c>
-      <c r="M33" s="3">
-        <v>222300</v>
       </c>
       <c r="N33" s="3">
         <v>222300</v>
       </c>
       <c r="O33" s="3">
+        <v>222300</v>
+      </c>
+      <c r="P33" s="3">
         <v>187600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>167700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>181500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>129200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>28900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>66200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>114400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>96400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>110000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>241500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-419200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-74200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>23500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>22100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-5900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>8</v>
+      <c r="D35" s="3">
+        <v>160900</v>
       </c>
       <c r="E35" s="3">
-        <v>158800</v>
+        <v>153600</v>
       </c>
       <c r="F35" s="3">
-        <v>152600</v>
+        <v>157800</v>
       </c>
       <c r="G35" s="3">
-        <v>129900</v>
+        <v>151600</v>
       </c>
       <c r="H35" s="3">
-        <v>121200</v>
+        <v>129100</v>
       </c>
       <c r="I35" s="3">
-        <v>138000</v>
+        <v>120500</v>
       </c>
       <c r="J35" s="3">
+        <v>137200</v>
+      </c>
+      <c r="K35" s="3">
         <v>136200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>162900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>182200</v>
-      </c>
-      <c r="M35" s="3">
-        <v>222300</v>
       </c>
       <c r="N35" s="3">
         <v>222300</v>
       </c>
       <c r="O35" s="3">
+        <v>222300</v>
+      </c>
+      <c r="P35" s="3">
         <v>187600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>167700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>181500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>129200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>28900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>66200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>114400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>96400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>110000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>241500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-419200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-74200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>23500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>22100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-5900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,83 +3351,84 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>580800</v>
+        <v>732400</v>
       </c>
       <c r="E41" s="3">
-        <v>686500</v>
+        <v>577200</v>
       </c>
       <c r="F41" s="3">
-        <v>730700</v>
+        <v>682300</v>
       </c>
       <c r="G41" s="3">
-        <v>712900</v>
+        <v>726200</v>
       </c>
       <c r="H41" s="3">
-        <v>996200</v>
+        <v>708500</v>
       </c>
       <c r="I41" s="3">
-        <v>1003700</v>
+        <v>990000</v>
       </c>
       <c r="J41" s="3">
+        <v>997500</v>
+      </c>
+      <c r="K41" s="3">
         <v>968300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>852800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>842700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>600500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>745700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>831600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>615000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>710400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>563400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>570500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>324600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>287700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>285100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>195700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>210000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>281100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>65600</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3354,8 +3441,11 @@
       <c r="AE41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3363,22 +3453,22 @@
         <v>2100</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="F42" s="3">
-        <v>34400</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>32800</v>
+        <v>34200</v>
       </c>
       <c r="H42" s="3">
+        <v>32600</v>
+      </c>
+      <c r="I42" s="3">
         <v>7900</v>
       </c>
-      <c r="I42" s="3">
-        <v>4200</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>8</v>
+      <c r="J42" s="3">
+        <v>4100</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>8</v>
@@ -3392,8 +3482,8 @@
       <c r="N42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
+      <c r="O42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
@@ -3443,83 +3533,86 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4404900</v>
+        <v>4555500</v>
       </c>
       <c r="E43" s="3">
-        <v>4276200</v>
+        <v>4377600</v>
       </c>
       <c r="F43" s="3">
-        <v>3942100</v>
+        <v>4249800</v>
       </c>
       <c r="G43" s="3">
-        <v>3529900</v>
+        <v>3917700</v>
       </c>
       <c r="H43" s="3">
-        <v>3163000</v>
+        <v>3508100</v>
       </c>
       <c r="I43" s="3">
-        <v>3049300</v>
+        <v>3143400</v>
       </c>
       <c r="J43" s="3">
+        <v>3030500</v>
+      </c>
+      <c r="K43" s="3">
         <v>2643400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2653400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2444000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2516000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2232800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1947600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1918900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2034700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2097200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2153800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2168400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2094600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1663200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1050200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>642500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>177700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>272300</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3532,8 +3625,11 @@
       <c r="AE43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3621,83 +3717,86 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>544700</v>
+        <v>487400</v>
       </c>
       <c r="E45" s="3">
-        <v>599400</v>
+        <v>541300</v>
       </c>
       <c r="F45" s="3">
-        <v>514000</v>
+        <v>595700</v>
       </c>
       <c r="G45" s="3">
-        <v>592600</v>
+        <v>510800</v>
       </c>
       <c r="H45" s="3">
-        <v>573200</v>
+        <v>589000</v>
       </c>
       <c r="I45" s="3">
-        <v>569100</v>
+        <v>569600</v>
       </c>
       <c r="J45" s="3">
+        <v>565600</v>
+      </c>
+      <c r="K45" s="3">
         <v>671200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>555600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>537700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>521500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>563400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>511100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>511200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>517600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>606800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>597700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>510200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>498200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>427100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>354900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>213900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>156100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>102600</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3710,83 +3809,86 @@
       <c r="AE45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>5532400</v>
+        <v>5777300</v>
       </c>
       <c r="E46" s="3">
-        <v>5562200</v>
+        <v>5498200</v>
       </c>
       <c r="F46" s="3">
-        <v>5221300</v>
+        <v>5527800</v>
       </c>
       <c r="G46" s="3">
-        <v>4868300</v>
+        <v>5189000</v>
       </c>
       <c r="H46" s="3">
-        <v>4740200</v>
+        <v>4838200</v>
       </c>
       <c r="I46" s="3">
-        <v>4626300</v>
+        <v>4710900</v>
       </c>
       <c r="J46" s="3">
+        <v>4597700</v>
+      </c>
+      <c r="K46" s="3">
         <v>4282900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4061900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3824400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3638000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3541900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3290300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3045100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3262700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3267400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3322000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3003100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2880600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2375500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1600800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1066300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>615000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>440500</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>8</v>
       </c>
@@ -3799,71 +3901,74 @@
       <c r="AE46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>506800</v>
+        <v>437200</v>
       </c>
       <c r="E47" s="3">
-        <v>501700</v>
+        <v>503700</v>
       </c>
       <c r="F47" s="3">
-        <v>498900</v>
+        <v>498600</v>
       </c>
       <c r="G47" s="3">
-        <v>500000</v>
+        <v>495800</v>
       </c>
       <c r="H47" s="3">
-        <v>572800</v>
+        <v>496900</v>
       </c>
       <c r="I47" s="3">
-        <v>613900</v>
+        <v>569300</v>
       </c>
       <c r="J47" s="3">
+        <v>610100</v>
+      </c>
+      <c r="K47" s="3">
         <v>651700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>607100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>526500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>579600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>358000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>201600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>144900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>127700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>99300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>55100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>12100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>100</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>8</v>
       </c>
@@ -3876,8 +3981,8 @@
       <c r="AA47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB47" s="3">
-        <v>0</v>
+      <c r="AB47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC47" s="3">
         <v>0</v>
@@ -3888,70 +3993,73 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>38500</v>
+        <v>43300</v>
       </c>
       <c r="E48" s="3">
-        <v>28000</v>
+        <v>38300</v>
       </c>
       <c r="F48" s="3">
-        <v>23000</v>
+        <v>27800</v>
       </c>
       <c r="G48" s="3">
-        <v>19600</v>
+        <v>22900</v>
       </c>
       <c r="H48" s="3">
-        <v>14400</v>
+        <v>19500</v>
       </c>
       <c r="I48" s="3">
-        <v>12500</v>
+        <v>14300</v>
       </c>
       <c r="J48" s="3">
+        <v>12400</v>
+      </c>
+      <c r="K48" s="3">
         <v>13400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>11100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>12200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>11600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>11200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2200</v>
-      </c>
-      <c r="W48" s="3">
-        <v>1000</v>
       </c>
       <c r="X48" s="3">
         <v>1000</v>
@@ -3962,8 +4070,8 @@
       <c r="Z48" s="3">
         <v>1000</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>8</v>
+      <c r="AA48" s="3">
+        <v>1000</v>
       </c>
       <c r="AB48" s="3" t="s">
         <v>8</v>
@@ -3977,19 +4085,22 @@
       <c r="AE48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>137800</v>
+        <v>7500</v>
       </c>
       <c r="E49" s="3">
         <v>7600</v>
       </c>
       <c r="F49" s="3">
-        <v>700</v>
+        <v>7600</v>
       </c>
       <c r="G49" s="3">
         <v>700</v>
@@ -3998,25 +4109,25 @@
         <v>700</v>
       </c>
       <c r="I49" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="J49" s="3">
         <v>700</v>
       </c>
       <c r="K49" s="3">
+        <v>700</v>
+      </c>
+      <c r="L49" s="3">
         <v>800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>141100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>700</v>
-      </c>
-      <c r="O49" s="3">
-        <v>500</v>
       </c>
       <c r="P49" s="3">
         <v>500</v>
@@ -4025,22 +4136,22 @@
         <v>500</v>
       </c>
       <c r="R49" s="3">
+        <v>500</v>
+      </c>
+      <c r="S49" s="3">
         <v>400</v>
-      </c>
-      <c r="S49" s="3">
-        <v>500</v>
       </c>
       <c r="T49" s="3">
         <v>500</v>
       </c>
       <c r="U49" s="3">
+        <v>500</v>
+      </c>
+      <c r="V49" s="3">
         <v>600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>300</v>
-      </c>
-      <c r="W49" s="3">
-        <v>100</v>
       </c>
       <c r="X49" s="3">
         <v>100</v>
@@ -4051,8 +4162,8 @@
       <c r="Z49" s="3">
         <v>100</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>8</v>
+      <c r="AA49" s="3">
+        <v>100</v>
       </c>
       <c r="AB49" s="3" t="s">
         <v>8</v>
@@ -4066,8 +4177,11 @@
       <c r="AE49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,83 +4361,86 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>148400</v>
+        <v>287200</v>
       </c>
       <c r="E52" s="3">
-        <v>300900</v>
+        <v>282600</v>
       </c>
       <c r="F52" s="3">
-        <v>289900</v>
+        <v>299000</v>
       </c>
       <c r="G52" s="3">
-        <v>294400</v>
+        <v>288100</v>
       </c>
       <c r="H52" s="3">
-        <v>280500</v>
+        <v>292600</v>
       </c>
       <c r="I52" s="3">
-        <v>302200</v>
+        <v>278700</v>
       </c>
       <c r="J52" s="3">
+        <v>300400</v>
+      </c>
+      <c r="K52" s="3">
         <v>287600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>267100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>115000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>164800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>147500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>207100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>194700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>169500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>154500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>212000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>107400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>25500</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X52" s="3">
-        <v>0</v>
+      <c r="X52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="3">
         <v>86800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>67400</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4333,8 +4453,11 @@
       <c r="AE52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,83 +4545,86 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>6369700</v>
+        <v>6552400</v>
       </c>
       <c r="E54" s="3">
-        <v>6400400</v>
+        <v>6330300</v>
       </c>
       <c r="F54" s="3">
-        <v>6033800</v>
+        <v>6360800</v>
       </c>
       <c r="G54" s="3">
-        <v>5683000</v>
+        <v>5996400</v>
       </c>
       <c r="H54" s="3">
-        <v>5608500</v>
+        <v>5647900</v>
       </c>
       <c r="I54" s="3">
-        <v>5555600</v>
+        <v>5573800</v>
       </c>
       <c r="J54" s="3">
+        <v>5521200</v>
+      </c>
+      <c r="K54" s="3">
         <v>5236300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4950100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4616300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4390300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4056700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3707600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3394700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3571600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3533800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3601200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3134400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2913900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2378000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1601900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1067400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>702900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>509000</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>8</v>
       </c>
@@ -4511,8 +4637,11 @@
       <c r="AE54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,8 +4707,9 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4666,71 +4797,74 @@
       <c r="AE57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>111000</v>
+        <v>94500</v>
       </c>
       <c r="E58" s="3">
-        <v>105100</v>
+        <v>110300</v>
       </c>
       <c r="F58" s="3">
-        <v>36100</v>
+        <v>104500</v>
       </c>
       <c r="G58" s="3">
-        <v>20900</v>
+        <v>35900</v>
       </c>
       <c r="H58" s="3">
-        <v>20900</v>
+        <v>20700</v>
       </c>
       <c r="I58" s="3">
-        <v>88900</v>
+        <v>20700</v>
       </c>
       <c r="J58" s="3">
+        <v>88400</v>
+      </c>
+      <c r="K58" s="3">
         <v>85000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>81000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>54800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>47700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>48300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>32300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>26000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>27200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>27700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>68600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>30800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>239500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>223900</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>8</v>
       </c>
@@ -4743,8 +4877,8 @@
       <c r="AA58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB58" s="3">
-        <v>0</v>
+      <c r="AB58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC58" s="3">
         <v>0</v>
@@ -4755,83 +4889,86 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2655400</v>
+        <v>2636400</v>
       </c>
       <c r="E59" s="3">
-        <v>2535700</v>
+        <v>2639000</v>
       </c>
       <c r="F59" s="3">
-        <v>2214100</v>
+        <v>2520000</v>
       </c>
       <c r="G59" s="3">
-        <v>2506100</v>
+        <v>2200400</v>
       </c>
       <c r="H59" s="3">
-        <v>2307700</v>
+        <v>2490600</v>
       </c>
       <c r="I59" s="3">
-        <v>2405500</v>
+        <v>2293400</v>
       </c>
       <c r="J59" s="3">
+        <v>2390600</v>
+      </c>
+      <c r="K59" s="3">
         <v>2253800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1939500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1893900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1870500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1877300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1841500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1837100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1863800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1930800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2084600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1457800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1280000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1109500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>754700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>420300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>413100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>452200</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>8</v>
       </c>
@@ -4844,83 +4981,86 @@
       <c r="AE59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2766400</v>
+        <v>2730800</v>
       </c>
       <c r="E60" s="3">
-        <v>2640800</v>
+        <v>2749300</v>
       </c>
       <c r="F60" s="3">
-        <v>2250200</v>
+        <v>2624500</v>
       </c>
       <c r="G60" s="3">
-        <v>2526900</v>
+        <v>2236300</v>
       </c>
       <c r="H60" s="3">
-        <v>2328600</v>
+        <v>2511300</v>
       </c>
       <c r="I60" s="3">
-        <v>2494400</v>
+        <v>2314200</v>
       </c>
       <c r="J60" s="3">
+        <v>2479000</v>
+      </c>
+      <c r="K60" s="3">
         <v>2338800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2020400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1948600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1918300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1925600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1873800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1863100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1891000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1958600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2153300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1488600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1519500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1333300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>754700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>420300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>413100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>452200</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>8</v>
       </c>
@@ -4933,8 +5073,11 @@
       <c r="AE60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5022,77 +5165,80 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>543400</v>
+        <v>762600</v>
       </c>
       <c r="E62" s="3">
-        <v>822100</v>
+        <v>540100</v>
       </c>
       <c r="F62" s="3">
-        <v>880000</v>
+        <v>817000</v>
       </c>
       <c r="G62" s="3">
-        <v>413600</v>
+        <v>874600</v>
       </c>
       <c r="H62" s="3">
-        <v>648100</v>
+        <v>411100</v>
       </c>
       <c r="I62" s="3">
-        <v>560200</v>
+        <v>644100</v>
       </c>
       <c r="J62" s="3">
+        <v>556800</v>
+      </c>
+      <c r="K62" s="3">
         <v>531300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>695500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>571100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>465300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>337600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>317300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>211800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>467700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>542400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>490300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>534900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>342300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>121400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>54400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2300</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5111,8 +5257,11 @@
       <c r="AE62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,83 +5533,86 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3319900</v>
+        <v>3502800</v>
       </c>
       <c r="E66" s="3">
-        <v>3473500</v>
+        <v>3299400</v>
       </c>
       <c r="F66" s="3">
-        <v>3140800</v>
+        <v>3452000</v>
       </c>
       <c r="G66" s="3">
-        <v>2951700</v>
+        <v>3121400</v>
       </c>
       <c r="H66" s="3">
-        <v>2988400</v>
+        <v>2933400</v>
       </c>
       <c r="I66" s="3">
-        <v>3066900</v>
+        <v>2969900</v>
       </c>
       <c r="J66" s="3">
+        <v>3048000</v>
+      </c>
+      <c r="K66" s="3">
         <v>2870500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2717000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2521500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2383600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2263300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2191200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2075000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2358900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2501200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2643700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2023600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1862000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1454700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>809100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>422600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>413100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>452200</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>8</v>
       </c>
@@ -5467,8 +5625,11 @@
       <c r="AE66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5747,11 +5915,11 @@
         <v>0</v>
       </c>
       <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
         <v>628600</v>
       </c>
-      <c r="Z70" s="3">
-        <v>0</v>
-      </c>
       <c r="AA70" s="3">
         <v>0</v>
       </c>
@@ -5767,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,16 +6027,19 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>8</v>
+      <c r="E72" s="3">
+        <v>2251600</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>8</v>
@@ -5873,11 +6047,11 @@
       <c r="G72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H72" s="3">
-        <v>1780000</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>8</v>
+      <c r="H72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I72" s="3">
+        <v>1769000</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>8</v>
@@ -5885,54 +6059,54 @@
       <c r="K72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M72" s="3">
         <v>1328500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1222000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1010000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>763500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>575900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>432200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>250600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>130000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>318900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>256100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>141600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>44300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-62500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-339400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-109100</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>8</v>
       </c>
@@ -5945,8 +6119,11 @@
       <c r="AE72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,83 +6395,86 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>3049700</v>
+        <v>3049600</v>
       </c>
       <c r="E76" s="3">
-        <v>2926800</v>
+        <v>3030900</v>
       </c>
       <c r="F76" s="3">
-        <v>2893000</v>
+        <v>2908700</v>
       </c>
       <c r="G76" s="3">
-        <v>2731400</v>
+        <v>2875100</v>
       </c>
       <c r="H76" s="3">
-        <v>2620100</v>
+        <v>2714500</v>
       </c>
       <c r="I76" s="3">
-        <v>2488600</v>
+        <v>2603900</v>
       </c>
       <c r="J76" s="3">
+        <v>2473200</v>
+      </c>
+      <c r="K76" s="3">
         <v>2365900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2233100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2094800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2006700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1793300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1516400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1319700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1212800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1032600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>957400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1110700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1051900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>923300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>792800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>644800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-338900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>56800</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>8</v>
       </c>
@@ -6301,8 +6487,11 @@
       <c r="AE76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>8</v>
+      <c r="D81" s="3">
+        <v>160900</v>
       </c>
       <c r="E81" s="3">
-        <v>158800</v>
+        <v>153600</v>
       </c>
       <c r="F81" s="3">
-        <v>152600</v>
+        <v>157800</v>
       </c>
       <c r="G81" s="3">
-        <v>129900</v>
+        <v>151600</v>
       </c>
       <c r="H81" s="3">
-        <v>121200</v>
+        <v>129100</v>
       </c>
       <c r="I81" s="3">
-        <v>138000</v>
+        <v>120500</v>
       </c>
       <c r="J81" s="3">
+        <v>137200</v>
+      </c>
+      <c r="K81" s="3">
         <v>136200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>162900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>182200</v>
-      </c>
-      <c r="M81" s="3">
-        <v>222300</v>
       </c>
       <c r="N81" s="3">
         <v>222300</v>
       </c>
       <c r="O81" s="3">
+        <v>222300</v>
+      </c>
+      <c r="P81" s="3">
         <v>187600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>167700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>181500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>129200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>28900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>66200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>114400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>96400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>110000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>241500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-419200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-74200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>23500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>22100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-5900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +6804,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6677,8 +6876,8 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>8</v>
+      <c r="Z83" s="3">
+        <v>0</v>
       </c>
       <c r="AA83" s="3" t="s">
         <v>8</v>
@@ -6695,8 +6894,11 @@
       <c r="AE83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,50 +7354,53 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>8</v>
+      <c r="D89" s="3">
+        <v>270600</v>
       </c>
       <c r="E89" s="3">
-        <v>172900</v>
+        <v>324900</v>
       </c>
       <c r="F89" s="3">
-        <v>489700</v>
+        <v>171900</v>
       </c>
       <c r="G89" s="3">
-        <v>-578500</v>
+        <v>243400</v>
       </c>
       <c r="H89" s="3">
-        <v>249200</v>
+        <v>243300</v>
       </c>
       <c r="I89" s="3">
-        <v>221300</v>
+        <v>247600</v>
       </c>
       <c r="J89" s="3">
+        <v>220000</v>
+      </c>
+      <c r="K89" s="3">
         <v>352800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>196000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>132800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>252600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>186200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>244000</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>8</v>
       </c>
@@ -7196,8 +7413,8 @@
       <c r="T89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
+      <c r="U89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V89" s="3">
         <v>0</v>
@@ -7211,8 +7428,8 @@
       <c r="Y89" s="3">
         <v>0</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>8</v>
+      <c r="Z89" s="3">
+        <v>0</v>
       </c>
       <c r="AA89" s="3" t="s">
         <v>8</v>
@@ -7229,8 +7446,11 @@
       <c r="AE89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,8 +7482,9 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7333,8 +7554,8 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>8</v>
+      <c r="Z91" s="3">
+        <v>0</v>
       </c>
       <c r="AA91" s="3" t="s">
         <v>8</v>
@@ -7351,8 +7572,11 @@
       <c r="AE91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,50 +7756,53 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>8</v>
+      <c r="D94" s="3">
+        <v>-433600</v>
       </c>
       <c r="E94" s="3">
-        <v>-314300</v>
+        <v>-260500</v>
       </c>
       <c r="F94" s="3">
-        <v>-973300</v>
+        <v>-312400</v>
       </c>
       <c r="G94" s="3">
-        <v>527100</v>
+        <v>-474900</v>
       </c>
       <c r="H94" s="3">
-        <v>-233600</v>
+        <v>-492400</v>
       </c>
       <c r="I94" s="3">
-        <v>-414400</v>
+        <v>-232200</v>
       </c>
       <c r="J94" s="3">
+        <v>-411900</v>
+      </c>
+      <c r="K94" s="3">
         <v>-374600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-337100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>10100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-487700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-323400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-63400</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>8</v>
       </c>
@@ -7585,8 +7815,8 @@
       <c r="T94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
@@ -7600,8 +7830,8 @@
       <c r="Y94" s="3">
         <v>0</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>8</v>
+      <c r="Z94" s="3">
+        <v>0</v>
       </c>
       <c r="AA94" s="3" t="s">
         <v>8</v>
@@ -7618,8 +7848,11 @@
       <c r="AE94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7740,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,50 +8250,53 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>8</v>
+      <c r="D100" s="3">
+        <v>245300</v>
       </c>
       <c r="E100" s="3">
-        <v>97700</v>
+        <v>-125900</v>
       </c>
       <c r="F100" s="3">
-        <v>177300</v>
+        <v>97100</v>
       </c>
       <c r="G100" s="3">
-        <v>-440000</v>
+        <v>170800</v>
       </c>
       <c r="H100" s="3">
-        <v>26900</v>
+        <v>5400</v>
       </c>
       <c r="I100" s="3">
-        <v>122500</v>
+        <v>26800</v>
       </c>
       <c r="J100" s="3">
+        <v>121700</v>
+      </c>
+      <c r="K100" s="3">
         <v>296000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>148700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>149600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>64700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>77300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>25700</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>8</v>
       </c>
@@ -8063,8 +8309,8 @@
       <c r="T100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
+      <c r="U100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V100" s="3">
         <v>0</v>
@@ -8078,8 +8324,8 @@
       <c r="Y100" s="3">
         <v>0</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>8</v>
+      <c r="Z100" s="3">
+        <v>0</v>
       </c>
       <c r="AA100" s="3" t="s">
         <v>8</v>
@@ -8096,49 +8342,52 @@
       <c r="AE100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>8</v>
+      <c r="D101" s="3">
+        <v>300</v>
       </c>
       <c r="E101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F101" s="3">
         <v>700</v>
       </c>
-      <c r="F101" s="3">
-        <v>800</v>
-      </c>
       <c r="G101" s="3">
-        <v>2100</v>
+        <v>1200</v>
       </c>
       <c r="H101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I101" s="3">
         <v>-3200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="O101" s="3">
         <v>-200</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>8</v>
+      <c r="P101" s="3">
+        <v>-200</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>8</v>
@@ -8152,8 +8401,8 @@
       <c r="T101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
+      <c r="U101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V101" s="3">
         <v>0</v>
@@ -8167,8 +8416,8 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>8</v>
+      <c r="Z101" s="3">
+        <v>0</v>
       </c>
       <c r="AA101" s="3" t="s">
         <v>8</v>
@@ -8185,50 +8434,53 @@
       <c r="AE101" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>8</v>
+      <c r="D102" s="3">
+        <v>82600</v>
       </c>
       <c r="E102" s="3">
-        <v>-43000</v>
+        <v>-61700</v>
       </c>
       <c r="F102" s="3">
-        <v>-305500</v>
+        <v>-42700</v>
       </c>
       <c r="G102" s="3">
-        <v>-489300</v>
+        <v>-59500</v>
       </c>
       <c r="H102" s="3">
-        <v>39300</v>
+        <v>-244100</v>
       </c>
       <c r="I102" s="3">
-        <v>-69600</v>
+        <v>39100</v>
       </c>
       <c r="J102" s="3">
+        <v>-69200</v>
+      </c>
+      <c r="K102" s="3">
         <v>273900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>7100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>292400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-170400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-60100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>206100</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>8</v>
       </c>
@@ -8241,8 +8493,8 @@
       <c r="T102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
+      <c r="U102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V102" s="3">
         <v>0</v>
@@ -8256,8 +8508,8 @@
       <c r="Y102" s="3">
         <v>0</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>8</v>
+      <c r="Z102" s="3">
+        <v>0</v>
       </c>
       <c r="AA102" s="3" t="s">
         <v>8</v>
@@ -8272,6 +8524,9 @@
         <v>8</v>
       </c>
       <c r="AE102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/QFIN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QFIN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="92">
   <si>
     <t>QFIN</t>
   </si>
@@ -656,416 +656,429 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>573800</v>
+        <v>586500</v>
       </c>
       <c r="E8" s="3">
-        <v>621100</v>
+        <v>585500</v>
       </c>
       <c r="F8" s="3">
-        <v>591500</v>
+        <v>633800</v>
       </c>
       <c r="G8" s="3">
-        <v>540800</v>
+        <v>603500</v>
       </c>
       <c r="H8" s="3">
-        <v>497300</v>
+        <v>551800</v>
       </c>
       <c r="I8" s="3">
-        <v>539700</v>
+        <v>507400</v>
       </c>
       <c r="J8" s="3">
+        <v>550800</v>
+      </c>
+      <c r="K8" s="3">
         <v>572500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>581500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>596500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>609300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>655700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>574700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>501000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>464600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>545700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>492200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>502100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>369700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>403000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>347400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>306900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>444600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>89900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>62300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>86000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>64400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>52500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>101700</v>
+        <v>101800</v>
       </c>
       <c r="E9" s="3">
-        <v>101100</v>
+        <v>103800</v>
       </c>
       <c r="F9" s="3">
-        <v>88400</v>
+        <v>103200</v>
       </c>
       <c r="G9" s="3">
-        <v>89500</v>
+        <v>90200</v>
       </c>
       <c r="H9" s="3">
-        <v>88500</v>
+        <v>91400</v>
       </c>
       <c r="I9" s="3">
-        <v>80900</v>
+        <v>90300</v>
       </c>
       <c r="J9" s="3">
+        <v>82600</v>
+      </c>
+      <c r="K9" s="3">
         <v>85300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>77200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>84900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>81200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>89200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>80100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>66500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>61900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>60200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>58900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>54800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>27200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>58400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>47400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>34800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>32800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>24500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>32900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>14300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>8800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>11400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>472100</v>
+        <v>484700</v>
       </c>
       <c r="E10" s="3">
-        <v>520000</v>
+        <v>481800</v>
       </c>
       <c r="F10" s="3">
-        <v>503100</v>
+        <v>530600</v>
       </c>
       <c r="G10" s="3">
-        <v>451300</v>
+        <v>513300</v>
       </c>
       <c r="H10" s="3">
-        <v>408800</v>
+        <v>460500</v>
       </c>
       <c r="I10" s="3">
-        <v>458800</v>
+        <v>417100</v>
       </c>
       <c r="J10" s="3">
+        <v>468200</v>
+      </c>
+      <c r="K10" s="3">
         <v>487300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>504300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>511600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>528100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>566600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>494600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>434500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>402700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>485500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>433300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>447300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>342400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>344600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>300000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>272100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>411900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>65500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>29500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>71700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>55600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>41100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1111,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1190,8 +1204,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1299,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1374,8 +1394,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1427,8 +1450,8 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>8</v>
+      <c r="T15" s="3">
+        <v>0</v>
       </c>
       <c r="U15" s="3" t="s">
         <v>8</v>
@@ -1445,29 +1468,32 @@
       <c r="Y15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="Z15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA15" s="3">
         <v>100</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC15" s="3">
-        <v>100</v>
+      <c r="AC15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD15" s="3">
         <v>100</v>
       </c>
-      <c r="AE15" s="3" t="s">
-        <v>8</v>
+      <c r="AE15" s="3">
+        <v>100</v>
       </c>
       <c r="AF15" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1523,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>306600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>393200</v>
+      </c>
+      <c r="F17" s="3">
+        <v>453400</v>
+      </c>
+      <c r="G17" s="3">
+        <v>407700</v>
+      </c>
+      <c r="H17" s="3">
         <v>385300</v>
       </c>
-      <c r="E17" s="3">
-        <v>444300</v>
-      </c>
-      <c r="F17" s="3">
-        <v>399600</v>
-      </c>
-      <c r="G17" s="3">
-        <v>377600</v>
-      </c>
-      <c r="H17" s="3">
-        <v>358100</v>
-      </c>
       <c r="I17" s="3">
-        <v>409300</v>
+        <v>365400</v>
       </c>
       <c r="J17" s="3">
+        <v>417700</v>
+      </c>
+      <c r="K17" s="3">
         <v>412500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>441000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>408800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>405100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>386500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>308600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>284200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>291800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>343700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>345800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>473100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>329300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>256000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>218000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>175600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>139100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>68400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>141500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>55400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>36100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>49600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>9900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>188500</v>
+        <v>279800</v>
       </c>
       <c r="E18" s="3">
-        <v>176800</v>
+        <v>192300</v>
       </c>
       <c r="F18" s="3">
-        <v>191900</v>
+        <v>180400</v>
       </c>
       <c r="G18" s="3">
-        <v>163200</v>
+        <v>195800</v>
       </c>
       <c r="H18" s="3">
-        <v>139100</v>
+        <v>166600</v>
       </c>
       <c r="I18" s="3">
-        <v>130400</v>
+        <v>142000</v>
       </c>
       <c r="J18" s="3">
+        <v>133100</v>
+      </c>
+      <c r="K18" s="3">
         <v>160000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>140500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>187700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>204100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>269200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>266100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>216800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>172800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>202100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>146400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>29100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>40400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>147000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>129400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>131300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>305500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>21500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-79200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>30600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>28400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-8200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-5600</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,100 +1748,104 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>22400</v>
+        <v>12900</v>
       </c>
       <c r="E20" s="3">
-        <v>7100</v>
+        <v>22900</v>
       </c>
       <c r="F20" s="3">
-        <v>12300</v>
+        <v>7200</v>
       </c>
       <c r="G20" s="3">
-        <v>25500</v>
+        <v>12600</v>
       </c>
       <c r="H20" s="3">
-        <v>13100</v>
+        <v>26100</v>
       </c>
       <c r="I20" s="3">
-        <v>11200</v>
+        <v>13400</v>
       </c>
       <c r="J20" s="3">
+        <v>11400</v>
+      </c>
+      <c r="K20" s="3">
         <v>1800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>20100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>4400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>8300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>4100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>14400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>6600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>15400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>12900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>7300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>6900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>13600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-5200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>8800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>800</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>400</v>
       </c>
       <c r="AB20" s="3">
         <v>400</v>
       </c>
       <c r="AC20" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AD20" s="3">
         <v>200</v>
       </c>
       <c r="AE20" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF20" s="3">
         <v>100</v>
       </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1875,32 +1912,35 @@
       <c r="X21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z21" s="3">
         <v>306600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>22700</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AC21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE21" s="3">
         <v>3200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-8000</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1937,8 +1977,8 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>8</v>
+      <c r="O22" s="3">
+        <v>0</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>8</v>
@@ -1955,18 +1995,18 @@
       <c r="T22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U22" s="3">
+      <c r="U22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V22" s="3">
         <v>2200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>4000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>800</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y22" s="3" t="s">
         <v>8</v>
       </c>
@@ -1979,8 +2019,8 @@
       <c r="AB22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC22" s="3">
-        <v>0</v>
+      <c r="AC22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD22" s="3">
         <v>0</v>
@@ -1991,192 +2031,201 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>210900</v>
+        <v>292800</v>
       </c>
       <c r="E23" s="3">
-        <v>183900</v>
+        <v>215200</v>
       </c>
       <c r="F23" s="3">
-        <v>204200</v>
+        <v>187600</v>
       </c>
       <c r="G23" s="3">
-        <v>188800</v>
+        <v>208400</v>
       </c>
       <c r="H23" s="3">
-        <v>152300</v>
+        <v>192600</v>
       </c>
       <c r="I23" s="3">
-        <v>141600</v>
+        <v>155400</v>
       </c>
       <c r="J23" s="3">
+        <v>144500</v>
+      </c>
+      <c r="K23" s="3">
         <v>161900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>160600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>192000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>212400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>273300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>280500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>223500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>188200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>215000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>153700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>36000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>51800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>143900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>123400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>140100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>306100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>22300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-78800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>31000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>28500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>3100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-8000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-5600</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>50600</v>
+        <v>98700</v>
       </c>
       <c r="E24" s="3">
-        <v>30800</v>
+        <v>51600</v>
       </c>
       <c r="F24" s="3">
-        <v>47000</v>
+        <v>31500</v>
       </c>
       <c r="G24" s="3">
-        <v>37700</v>
+        <v>48000</v>
       </c>
       <c r="H24" s="3">
-        <v>23800</v>
+        <v>38500</v>
       </c>
       <c r="I24" s="3">
-        <v>21700</v>
+        <v>24300</v>
       </c>
       <c r="J24" s="3">
+        <v>22100</v>
+      </c>
+      <c r="K24" s="3">
         <v>25300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>25100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>29900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>32500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>51000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>58200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>35900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>20500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>33500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>24500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>7100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-14300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>29500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>27000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>30100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>64600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>7900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-4600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>7500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>6400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2316,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>160300</v>
+        <v>194100</v>
       </c>
       <c r="E26" s="3">
-        <v>153000</v>
+        <v>163600</v>
       </c>
       <c r="F26" s="3">
-        <v>157200</v>
+        <v>156200</v>
       </c>
       <c r="G26" s="3">
-        <v>151100</v>
+        <v>160400</v>
       </c>
       <c r="H26" s="3">
-        <v>128500</v>
+        <v>154100</v>
       </c>
       <c r="I26" s="3">
-        <v>119900</v>
+        <v>131100</v>
       </c>
       <c r="J26" s="3">
+        <v>122400</v>
+      </c>
+      <c r="K26" s="3">
         <v>136600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>135500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>162200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>179800</v>
-      </c>
-      <c r="N26" s="3">
-        <v>222300</v>
       </c>
       <c r="O26" s="3">
         <v>222300</v>
       </c>
       <c r="P26" s="3">
+        <v>222300</v>
+      </c>
+      <c r="Q26" s="3">
         <v>187500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>167600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>181500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>129200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>28900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>66200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>114400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>96400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>110000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>241500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>14400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-74200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>23500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>22100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-5900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>160900</v>
+        <v>194600</v>
       </c>
       <c r="E27" s="3">
-        <v>153600</v>
+        <v>164100</v>
       </c>
       <c r="F27" s="3">
-        <v>157800</v>
+        <v>156700</v>
       </c>
       <c r="G27" s="3">
-        <v>151600</v>
+        <v>161000</v>
       </c>
       <c r="H27" s="3">
-        <v>129100</v>
+        <v>154700</v>
       </c>
       <c r="I27" s="3">
-        <v>120500</v>
+        <v>131700</v>
       </c>
       <c r="J27" s="3">
+        <v>122900</v>
+      </c>
+      <c r="K27" s="3">
         <v>137200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>136200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>162900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>182200</v>
-      </c>
-      <c r="N27" s="3">
-        <v>222300</v>
       </c>
       <c r="O27" s="3">
         <v>222300</v>
       </c>
       <c r="P27" s="3">
+        <v>222300</v>
+      </c>
+      <c r="Q27" s="3">
         <v>187600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>167700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>181500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>129200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>28900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>66200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>114400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>96400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>110000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>241500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-419200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-74200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>23500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>22100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-5900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2696,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2886,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-22400</v>
+        <v>-12900</v>
       </c>
       <c r="E32" s="3">
-        <v>-7100</v>
+        <v>-22900</v>
       </c>
       <c r="F32" s="3">
-        <v>-12300</v>
+        <v>-7200</v>
       </c>
       <c r="G32" s="3">
-        <v>-25500</v>
+        <v>-12600</v>
       </c>
       <c r="H32" s="3">
-        <v>-13100</v>
+        <v>-26100</v>
       </c>
       <c r="I32" s="3">
-        <v>-11200</v>
+        <v>-13400</v>
       </c>
       <c r="J32" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="K32" s="3">
         <v>-1800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-20100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-4400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-8300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-4100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-14400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-15400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-12900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-7300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-6900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-13600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>5200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-8800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-800</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>-400</v>
       </c>
       <c r="AB32" s="3">
         <v>-400</v>
       </c>
       <c r="AC32" s="3">
-        <v>-200</v>
+        <v>-400</v>
       </c>
       <c r="AD32" s="3">
         <v>-200</v>
       </c>
       <c r="AE32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-100</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>160900</v>
+        <v>194600</v>
       </c>
       <c r="E33" s="3">
-        <v>153600</v>
+        <v>164100</v>
       </c>
       <c r="F33" s="3">
-        <v>157800</v>
+        <v>156700</v>
       </c>
       <c r="G33" s="3">
-        <v>151600</v>
+        <v>161000</v>
       </c>
       <c r="H33" s="3">
-        <v>129100</v>
+        <v>154700</v>
       </c>
       <c r="I33" s="3">
-        <v>120500</v>
+        <v>131700</v>
       </c>
       <c r="J33" s="3">
+        <v>122900</v>
+      </c>
+      <c r="K33" s="3">
         <v>137200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>136200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>162900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>182200</v>
-      </c>
-      <c r="N33" s="3">
-        <v>222300</v>
       </c>
       <c r="O33" s="3">
         <v>222300</v>
       </c>
       <c r="P33" s="3">
+        <v>222300</v>
+      </c>
+      <c r="Q33" s="3">
         <v>187600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>167700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>181500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>129200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>28900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>66200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>114400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>96400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>110000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>241500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-419200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-74200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>23500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>22100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-5900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3171,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>160900</v>
+        <v>194600</v>
       </c>
       <c r="E35" s="3">
-        <v>153600</v>
+        <v>164100</v>
       </c>
       <c r="F35" s="3">
-        <v>157800</v>
+        <v>156700</v>
       </c>
       <c r="G35" s="3">
-        <v>151600</v>
+        <v>161000</v>
       </c>
       <c r="H35" s="3">
-        <v>129100</v>
+        <v>154700</v>
       </c>
       <c r="I35" s="3">
-        <v>120500</v>
+        <v>131700</v>
       </c>
       <c r="J35" s="3">
+        <v>122900</v>
+      </c>
+      <c r="K35" s="3">
         <v>137200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>136200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>162900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>182200</v>
-      </c>
-      <c r="N35" s="3">
-        <v>222300</v>
       </c>
       <c r="O35" s="3">
         <v>222300</v>
       </c>
       <c r="P35" s="3">
+        <v>222300</v>
+      </c>
+      <c r="Q35" s="3">
         <v>187600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>167700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>181500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>129200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>28900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>66200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>114400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>96400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>110000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>241500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-419200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-74200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>23500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>22100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-5900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,86 +3438,87 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>732400</v>
+        <v>893400</v>
       </c>
       <c r="E41" s="3">
-        <v>577200</v>
+        <v>747400</v>
       </c>
       <c r="F41" s="3">
-        <v>682300</v>
+        <v>589000</v>
       </c>
       <c r="G41" s="3">
-        <v>726200</v>
+        <v>696200</v>
       </c>
       <c r="H41" s="3">
-        <v>708500</v>
+        <v>741000</v>
       </c>
       <c r="I41" s="3">
-        <v>990000</v>
+        <v>723000</v>
       </c>
       <c r="J41" s="3">
+        <v>1010200</v>
+      </c>
+      <c r="K41" s="3">
         <v>997500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>968300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>852800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>842700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>600500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>745700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>831600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>615000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>710400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>563400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>570500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>324600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>287700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>285100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>195700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>210000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>281100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>65600</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3444,35 +3531,38 @@
       <c r="AF41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2100</v>
+        <v>41000</v>
       </c>
       <c r="E42" s="3">
         <v>2100</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="G42" s="3">
-        <v>34200</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>32600</v>
+        <v>34900</v>
       </c>
       <c r="I42" s="3">
-        <v>7900</v>
+        <v>33300</v>
       </c>
       <c r="J42" s="3">
+        <v>8000</v>
+      </c>
+      <c r="K42" s="3">
         <v>4100</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>8</v>
       </c>
@@ -3485,8 +3575,8 @@
       <c r="O42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
+      <c r="P42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q42" s="3">
         <v>0</v>
@@ -3536,86 +3626,89 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4555500</v>
+        <v>4533100</v>
       </c>
       <c r="E43" s="3">
-        <v>4377600</v>
+        <v>4648500</v>
       </c>
       <c r="F43" s="3">
-        <v>4249800</v>
+        <v>4467000</v>
       </c>
       <c r="G43" s="3">
-        <v>3917700</v>
+        <v>4336500</v>
       </c>
       <c r="H43" s="3">
-        <v>3508100</v>
+        <v>3997700</v>
       </c>
       <c r="I43" s="3">
-        <v>3143400</v>
+        <v>3579700</v>
       </c>
       <c r="J43" s="3">
+        <v>3207600</v>
+      </c>
+      <c r="K43" s="3">
         <v>3030500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2643400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2653400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2444000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2516000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2232800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1947600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1918900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2034700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2097200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2153800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2168400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2094600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1663200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1050200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>642500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>177700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>272300</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3628,8 +3721,11 @@
       <c r="AF43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,86 +3816,89 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>487400</v>
+        <v>371300</v>
       </c>
       <c r="E45" s="3">
-        <v>541300</v>
+        <v>497300</v>
       </c>
       <c r="F45" s="3">
-        <v>595700</v>
+        <v>552400</v>
       </c>
       <c r="G45" s="3">
-        <v>510800</v>
+        <v>607800</v>
       </c>
       <c r="H45" s="3">
-        <v>589000</v>
+        <v>521300</v>
       </c>
       <c r="I45" s="3">
-        <v>569600</v>
+        <v>601000</v>
       </c>
       <c r="J45" s="3">
+        <v>581200</v>
+      </c>
+      <c r="K45" s="3">
         <v>565600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>671200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>555600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>537700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>521500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>563400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>511100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>511200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>517600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>606800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>597700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>510200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>498200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>427100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>354900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>213900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>156100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>102600</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3812,86 +3911,89 @@
       <c r="AF45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>5777300</v>
+        <v>5838800</v>
       </c>
       <c r="E46" s="3">
-        <v>5498200</v>
+        <v>5895300</v>
       </c>
       <c r="F46" s="3">
-        <v>5527800</v>
+        <v>5610400</v>
       </c>
       <c r="G46" s="3">
-        <v>5189000</v>
+        <v>5640600</v>
       </c>
       <c r="H46" s="3">
-        <v>4838200</v>
+        <v>5294900</v>
       </c>
       <c r="I46" s="3">
-        <v>4710900</v>
+        <v>4936900</v>
       </c>
       <c r="J46" s="3">
+        <v>4807100</v>
+      </c>
+      <c r="K46" s="3">
         <v>4597700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4282900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4061900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3824400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3638000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3541900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3290300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3045100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3262700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3267400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3322000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3003100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2880600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2375500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1600800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1066300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>615000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>440500</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>8</v>
       </c>
@@ -3904,74 +4006,77 @@
       <c r="AF46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>437200</v>
+        <v>443300</v>
       </c>
       <c r="E47" s="3">
-        <v>503700</v>
+        <v>446100</v>
       </c>
       <c r="F47" s="3">
-        <v>498600</v>
+        <v>514000</v>
       </c>
       <c r="G47" s="3">
-        <v>495800</v>
+        <v>508800</v>
       </c>
       <c r="H47" s="3">
-        <v>496900</v>
+        <v>505900</v>
       </c>
       <c r="I47" s="3">
-        <v>569300</v>
+        <v>507000</v>
       </c>
       <c r="J47" s="3">
+        <v>580900</v>
+      </c>
+      <c r="K47" s="3">
         <v>610100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>651700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>607100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>526500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>579600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>358000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>201600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>144900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>127700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>99300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>55100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>12100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>100</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y47" s="3" t="s">
         <v>8</v>
       </c>
@@ -3984,8 +4089,8 @@
       <c r="AB47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC47" s="3">
-        <v>0</v>
+      <c r="AC47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD47" s="3">
         <v>0</v>
@@ -3996,73 +4101,76 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>43300</v>
+        <v>49600</v>
       </c>
       <c r="E48" s="3">
-        <v>38300</v>
+        <v>44200</v>
       </c>
       <c r="F48" s="3">
-        <v>27800</v>
+        <v>39100</v>
       </c>
       <c r="G48" s="3">
-        <v>22900</v>
+        <v>28400</v>
       </c>
       <c r="H48" s="3">
-        <v>19500</v>
+        <v>23400</v>
       </c>
       <c r="I48" s="3">
-        <v>14300</v>
+        <v>19900</v>
       </c>
       <c r="J48" s="3">
+        <v>14600</v>
+      </c>
+      <c r="K48" s="3">
         <v>12400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>11100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>12200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>11600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>11200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2200</v>
-      </c>
-      <c r="X48" s="3">
-        <v>1000</v>
       </c>
       <c r="Y48" s="3">
         <v>1000</v>
@@ -4073,8 +4181,8 @@
       <c r="AA48" s="3">
         <v>1000</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>8</v>
+      <c r="AB48" s="3">
+        <v>1000</v>
       </c>
       <c r="AC48" s="3" t="s">
         <v>8</v>
@@ -4088,8 +4196,11 @@
       <c r="AF48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4100,16 +4211,16 @@
         <v>7600</v>
       </c>
       <c r="F49" s="3">
-        <v>7600</v>
+        <v>7700</v>
       </c>
       <c r="G49" s="3">
-        <v>700</v>
+        <v>7700</v>
       </c>
       <c r="H49" s="3">
         <v>700</v>
       </c>
       <c r="I49" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="J49" s="3">
         <v>700</v>
@@ -4118,19 +4229,19 @@
         <v>700</v>
       </c>
       <c r="L49" s="3">
+        <v>700</v>
+      </c>
+      <c r="M49" s="3">
         <v>800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>141100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>700</v>
-      </c>
-      <c r="P49" s="3">
-        <v>500</v>
       </c>
       <c r="Q49" s="3">
         <v>500</v>
@@ -4139,22 +4250,22 @@
         <v>500</v>
       </c>
       <c r="S49" s="3">
+        <v>500</v>
+      </c>
+      <c r="T49" s="3">
         <v>400</v>
-      </c>
-      <c r="T49" s="3">
-        <v>500</v>
       </c>
       <c r="U49" s="3">
         <v>500</v>
       </c>
       <c r="V49" s="3">
+        <v>500</v>
+      </c>
+      <c r="W49" s="3">
         <v>600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>300</v>
-      </c>
-      <c r="X49" s="3">
-        <v>100</v>
       </c>
       <c r="Y49" s="3">
         <v>100</v>
@@ -4165,8 +4276,8 @@
       <c r="AA49" s="3">
         <v>100</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>8</v>
+      <c r="AB49" s="3">
+        <v>100</v>
       </c>
       <c r="AC49" s="3" t="s">
         <v>8</v>
@@ -4180,8 +4291,11 @@
       <c r="AF49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,86 +4481,89 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>287200</v>
+        <v>284400</v>
       </c>
       <c r="E52" s="3">
-        <v>282600</v>
+        <v>293000</v>
       </c>
       <c r="F52" s="3">
-        <v>299000</v>
+        <v>288300</v>
       </c>
       <c r="G52" s="3">
-        <v>288100</v>
+        <v>305100</v>
       </c>
       <c r="H52" s="3">
-        <v>292600</v>
+        <v>294000</v>
       </c>
       <c r="I52" s="3">
-        <v>278700</v>
+        <v>298600</v>
       </c>
       <c r="J52" s="3">
+        <v>284400</v>
+      </c>
+      <c r="K52" s="3">
         <v>300400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>287600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>267100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>115000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>164800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>147500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>207100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>194700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>169500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>154500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>212000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>107400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>25500</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y52" s="3">
-        <v>0</v>
+      <c r="Y52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="3">
         <v>86800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>67400</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4456,8 +4576,11 @@
       <c r="AF52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,86 +4671,89 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>6552400</v>
+        <v>6623700</v>
       </c>
       <c r="E54" s="3">
-        <v>6330300</v>
+        <v>6686200</v>
       </c>
       <c r="F54" s="3">
-        <v>6360800</v>
+        <v>6459500</v>
       </c>
       <c r="G54" s="3">
-        <v>5996400</v>
+        <v>6490600</v>
       </c>
       <c r="H54" s="3">
-        <v>5647900</v>
+        <v>6118800</v>
       </c>
       <c r="I54" s="3">
-        <v>5573800</v>
+        <v>5763200</v>
       </c>
       <c r="J54" s="3">
+        <v>5687600</v>
+      </c>
+      <c r="K54" s="3">
         <v>5521200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5236300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4950100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4616300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4390300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4056700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3707600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3394700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3571600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3533800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3601200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3134400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2913900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2378000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1601900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1067400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>702900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>509000</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>8</v>
       </c>
@@ -4640,8 +4766,11 @@
       <c r="AF54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,8 +4838,9 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4800,74 +4931,77 @@
       <c r="AF57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>94500</v>
+        <v>149200</v>
       </c>
       <c r="E58" s="3">
-        <v>110300</v>
+        <v>96400</v>
       </c>
       <c r="F58" s="3">
-        <v>104500</v>
+        <v>112600</v>
       </c>
       <c r="G58" s="3">
-        <v>35900</v>
+        <v>106600</v>
       </c>
       <c r="H58" s="3">
-        <v>20700</v>
+        <v>36700</v>
       </c>
       <c r="I58" s="3">
-        <v>20700</v>
+        <v>21100</v>
       </c>
       <c r="J58" s="3">
+        <v>21100</v>
+      </c>
+      <c r="K58" s="3">
         <v>88400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>85000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>81000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>54800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>47700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>48300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>32300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>26000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>27200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>27700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>68600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>30800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>239500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>223900</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>8</v>
       </c>
@@ -4880,8 +5014,8 @@
       <c r="AB58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC58" s="3">
-        <v>0</v>
+      <c r="AC58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD58" s="3">
         <v>0</v>
@@ -4892,86 +5026,89 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2636400</v>
+        <v>2231000</v>
       </c>
       <c r="E59" s="3">
-        <v>2639000</v>
+        <v>2690200</v>
       </c>
       <c r="F59" s="3">
-        <v>2520000</v>
+        <v>2692900</v>
       </c>
       <c r="G59" s="3">
-        <v>2200400</v>
+        <v>2571400</v>
       </c>
       <c r="H59" s="3">
-        <v>2490600</v>
+        <v>2245300</v>
       </c>
       <c r="I59" s="3">
-        <v>2293400</v>
+        <v>2541400</v>
       </c>
       <c r="J59" s="3">
+        <v>2340300</v>
+      </c>
+      <c r="K59" s="3">
         <v>2390600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2253800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1939500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1893900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1870500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1877300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1841500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1837100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1863800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1930800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2084600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1457800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1280000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1109500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>754700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>420300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>413100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>452200</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>8</v>
       </c>
@@ -4984,86 +5121,89 @@
       <c r="AF59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2730800</v>
+        <v>2380300</v>
       </c>
       <c r="E60" s="3">
-        <v>2749300</v>
+        <v>2786600</v>
       </c>
       <c r="F60" s="3">
-        <v>2624500</v>
+        <v>2805400</v>
       </c>
       <c r="G60" s="3">
-        <v>2236300</v>
+        <v>2678100</v>
       </c>
       <c r="H60" s="3">
-        <v>2511300</v>
+        <v>2281900</v>
       </c>
       <c r="I60" s="3">
-        <v>2314200</v>
+        <v>2562600</v>
       </c>
       <c r="J60" s="3">
+        <v>2361400</v>
+      </c>
+      <c r="K60" s="3">
         <v>2479000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2338800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2020400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1948600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1918300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1925600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1873800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1863100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1891000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1958600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2153300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1488600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1519500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1333300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>754700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>420300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>413100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>452200</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>8</v>
       </c>
@@ -5076,8 +5216,11 @@
       <c r="AF60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5168,80 +5311,83 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>762600</v>
+        <v>1052600</v>
       </c>
       <c r="E62" s="3">
-        <v>540100</v>
+        <v>778200</v>
       </c>
       <c r="F62" s="3">
-        <v>817000</v>
+        <v>551100</v>
       </c>
       <c r="G62" s="3">
-        <v>874600</v>
+        <v>833700</v>
       </c>
       <c r="H62" s="3">
-        <v>411100</v>
+        <v>892400</v>
       </c>
       <c r="I62" s="3">
-        <v>644100</v>
+        <v>419500</v>
       </c>
       <c r="J62" s="3">
+        <v>657200</v>
+      </c>
+      <c r="K62" s="3">
         <v>556800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>531300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>695500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>571100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>465300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>337600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>317300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>211800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>467700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>542400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>490300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>534900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>342300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>121400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>54400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2300</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5260,8 +5406,11 @@
       <c r="AF62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,86 +5691,89 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3502800</v>
+        <v>3441900</v>
       </c>
       <c r="E66" s="3">
-        <v>3299400</v>
+        <v>3574300</v>
       </c>
       <c r="F66" s="3">
-        <v>3452000</v>
+        <v>3366800</v>
       </c>
       <c r="G66" s="3">
-        <v>3121400</v>
+        <v>3522500</v>
       </c>
       <c r="H66" s="3">
-        <v>2933400</v>
+        <v>3185100</v>
       </c>
       <c r="I66" s="3">
-        <v>2969900</v>
+        <v>2993300</v>
       </c>
       <c r="J66" s="3">
+        <v>3030500</v>
+      </c>
+      <c r="K66" s="3">
         <v>3048000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2870500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2717000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2521500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2383600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2263300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2191200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2075000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2358900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2501200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2643700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2023600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1862000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1454700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>809100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>422600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>413100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>452200</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>8</v>
       </c>
@@ -5628,8 +5786,11 @@
       <c r="AF66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5918,11 +6086,11 @@
         <v>0</v>
       </c>
       <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
         <v>628600</v>
       </c>
-      <c r="AA70" s="3">
-        <v>0</v>
-      </c>
       <c r="AB70" s="3">
         <v>0</v>
       </c>
@@ -5938,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,19 +6201,22 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E72" s="3">
-        <v>2251600</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>8</v>
+      <c r="E72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F72" s="3">
+        <v>2297600</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>8</v>
@@ -6050,11 +6224,11 @@
       <c r="H72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I72" s="3">
-        <v>1769000</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>8</v>
+      <c r="I72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J72" s="3">
+        <v>1805100</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>8</v>
@@ -6062,54 +6236,54 @@
       <c r="L72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N72" s="3">
         <v>1328500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1222000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1010000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>763500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>575900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>432200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>250600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>130000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>318900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>256100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>141600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>44300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-62500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-339400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-109100</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>8</v>
       </c>
@@ -6122,8 +6296,11 @@
       <c r="AF72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,86 +6581,89 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>3049600</v>
+        <v>3181700</v>
       </c>
       <c r="E76" s="3">
-        <v>3030900</v>
+        <v>3111800</v>
       </c>
       <c r="F76" s="3">
-        <v>2908700</v>
+        <v>3092700</v>
       </c>
       <c r="G76" s="3">
-        <v>2875100</v>
+        <v>2968100</v>
       </c>
       <c r="H76" s="3">
-        <v>2714500</v>
+        <v>2933800</v>
       </c>
       <c r="I76" s="3">
-        <v>2603900</v>
+        <v>2769900</v>
       </c>
       <c r="J76" s="3">
+        <v>2657100</v>
+      </c>
+      <c r="K76" s="3">
         <v>2473200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2365900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2233100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2094800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2006700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1793300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1516400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1319700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1212800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1032600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>957400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1110700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1051900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>923300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>792800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>644800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-338900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>56800</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>8</v>
       </c>
@@ -6490,8 +6676,11 @@
       <c r="AF76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6771,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>160900</v>
+        <v>194600</v>
       </c>
       <c r="E81" s="3">
-        <v>153600</v>
+        <v>164100</v>
       </c>
       <c r="F81" s="3">
-        <v>157800</v>
+        <v>156700</v>
       </c>
       <c r="G81" s="3">
-        <v>151600</v>
+        <v>161000</v>
       </c>
       <c r="H81" s="3">
-        <v>129100</v>
+        <v>154700</v>
       </c>
       <c r="I81" s="3">
-        <v>120500</v>
+        <v>131700</v>
       </c>
       <c r="J81" s="3">
+        <v>122900</v>
+      </c>
+      <c r="K81" s="3">
         <v>137200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>136200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>162900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>182200</v>
-      </c>
-      <c r="N81" s="3">
-        <v>222300</v>
       </c>
       <c r="O81" s="3">
         <v>222300</v>
       </c>
       <c r="P81" s="3">
+        <v>222300</v>
+      </c>
+      <c r="Q81" s="3">
         <v>187600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>167700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>181500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>129200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>28900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>66200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>114400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>96400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>110000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>241500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-419200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-74200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>23500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>22100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-5900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7003,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6879,8 +7078,8 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>8</v>
+      <c r="AA83" s="3">
+        <v>0</v>
       </c>
       <c r="AB83" s="3" t="s">
         <v>8</v>
@@ -6897,8 +7096,11 @@
       <c r="AF83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,53 +7571,56 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>270600</v>
+        <v>276500</v>
       </c>
       <c r="E89" s="3">
-        <v>324900</v>
+        <v>276100</v>
       </c>
       <c r="F89" s="3">
-        <v>171900</v>
+        <v>331600</v>
       </c>
       <c r="G89" s="3">
-        <v>243400</v>
+        <v>175400</v>
       </c>
       <c r="H89" s="3">
-        <v>243300</v>
+        <v>248300</v>
       </c>
       <c r="I89" s="3">
-        <v>247600</v>
+        <v>248300</v>
       </c>
       <c r="J89" s="3">
+        <v>252700</v>
+      </c>
+      <c r="K89" s="3">
         <v>220000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>352800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>196000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>132800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>252600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>186200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>244000</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>8</v>
       </c>
@@ -7416,8 +7633,8 @@
       <c r="U89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
+      <c r="V89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W89" s="3">
         <v>0</v>
@@ -7431,8 +7648,8 @@
       <c r="Z89" s="3">
         <v>0</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>8</v>
+      <c r="AA89" s="3">
+        <v>0</v>
       </c>
       <c r="AB89" s="3" t="s">
         <v>8</v>
@@ -7449,8 +7666,11 @@
       <c r="AF89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7703,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7557,8 +7778,8 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>8</v>
+      <c r="AA91" s="3">
+        <v>0</v>
       </c>
       <c r="AB91" s="3" t="s">
         <v>8</v>
@@ -7575,8 +7796,11 @@
       <c r="AF91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,53 +7986,56 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-433600</v>
+        <v>-138200</v>
       </c>
       <c r="E94" s="3">
-        <v>-260500</v>
+        <v>-442400</v>
       </c>
       <c r="F94" s="3">
-        <v>-312400</v>
+        <v>-265800</v>
       </c>
       <c r="G94" s="3">
-        <v>-474900</v>
+        <v>-318700</v>
       </c>
       <c r="H94" s="3">
-        <v>-492400</v>
+        <v>-484500</v>
       </c>
       <c r="I94" s="3">
-        <v>-232200</v>
+        <v>-502500</v>
       </c>
       <c r="J94" s="3">
+        <v>-236900</v>
+      </c>
+      <c r="K94" s="3">
         <v>-411900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-374600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-337100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>10100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-487700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-323400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-63400</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>8</v>
       </c>
@@ -7818,8 +8048,8 @@
       <c r="U94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
+      <c r="V94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W94" s="3">
         <v>0</v>
@@ -7833,8 +8063,8 @@
       <c r="Z94" s="3">
         <v>0</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>8</v>
+      <c r="AA94" s="3">
+        <v>0</v>
       </c>
       <c r="AB94" s="3" t="s">
         <v>8</v>
@@ -7851,8 +8081,11 @@
       <c r="AF94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8118,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8211,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,53 +8496,56 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>245300</v>
+        <v>-108200</v>
       </c>
       <c r="E100" s="3">
-        <v>-125900</v>
+        <v>250300</v>
       </c>
       <c r="F100" s="3">
-        <v>97100</v>
+        <v>-128500</v>
       </c>
       <c r="G100" s="3">
-        <v>170800</v>
+        <v>99100</v>
       </c>
       <c r="H100" s="3">
-        <v>5400</v>
+        <v>174300</v>
       </c>
       <c r="I100" s="3">
-        <v>26800</v>
+        <v>5500</v>
       </c>
       <c r="J100" s="3">
+        <v>27300</v>
+      </c>
+      <c r="K100" s="3">
         <v>121700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>296000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>148700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>149600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>64700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>77300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>25700</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>8</v>
       </c>
@@ -8312,8 +8558,8 @@
       <c r="U100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
+      <c r="V100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W100" s="3">
         <v>0</v>
@@ -8327,8 +8573,8 @@
       <c r="Z100" s="3">
         <v>0</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>8</v>
+      <c r="AA100" s="3">
+        <v>0</v>
       </c>
       <c r="AB100" s="3" t="s">
         <v>8</v>
@@ -8345,8 +8591,11 @@
       <c r="AF100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8354,43 +8603,43 @@
         <v>300</v>
       </c>
       <c r="E101" s="3">
+        <v>300</v>
+      </c>
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-3200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="P101" s="3">
         <v>-200</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>8</v>
+      <c r="Q101" s="3">
+        <v>-200</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>8</v>
@@ -8404,8 +8653,8 @@
       <c r="U101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
+      <c r="V101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W101" s="3">
         <v>0</v>
@@ -8419,8 +8668,8 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-      <c r="AA101" s="3" t="s">
-        <v>8</v>
+      <c r="AA101" s="3">
+        <v>0</v>
       </c>
       <c r="AB101" s="3" t="s">
         <v>8</v>
@@ -8437,53 +8686,56 @@
       <c r="AF101" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>82600</v>
+        <v>30400</v>
       </c>
       <c r="E102" s="3">
-        <v>-61700</v>
+        <v>84200</v>
       </c>
       <c r="F102" s="3">
-        <v>-42700</v>
+        <v>-62900</v>
       </c>
       <c r="G102" s="3">
-        <v>-59500</v>
+        <v>-43600</v>
       </c>
       <c r="H102" s="3">
-        <v>-244100</v>
+        <v>-60700</v>
       </c>
       <c r="I102" s="3">
-        <v>39100</v>
+        <v>-249100</v>
       </c>
       <c r="J102" s="3">
+        <v>39900</v>
+      </c>
+      <c r="K102" s="3">
         <v>-69200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>273900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>7100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>292400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-170400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-60100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>206100</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>8</v>
       </c>
@@ -8496,8 +8748,8 @@
       <c r="U102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
+      <c r="V102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W102" s="3">
         <v>0</v>
@@ -8511,8 +8763,8 @@
       <c r="Z102" s="3">
         <v>0</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>8</v>
+      <c r="AA102" s="3">
+        <v>0</v>
       </c>
       <c r="AB102" s="3" t="s">
         <v>8</v>
@@ -8527,6 +8779,9 @@
         <v>8</v>
       </c>
       <c r="AF102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/QFIN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QFIN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="92">
   <si>
     <t>QFIN</t>
   </si>
@@ -656,429 +656,442 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>586500</v>
+        <v>623000</v>
       </c>
       <c r="E8" s="3">
-        <v>585500</v>
+        <v>572500</v>
       </c>
       <c r="F8" s="3">
-        <v>633800</v>
+        <v>575200</v>
       </c>
       <c r="G8" s="3">
-        <v>603500</v>
+        <v>634000</v>
       </c>
       <c r="H8" s="3">
-        <v>551800</v>
+        <v>586700</v>
       </c>
       <c r="I8" s="3">
-        <v>507400</v>
+        <v>539700</v>
       </c>
       <c r="J8" s="3">
+        <v>524000</v>
+      </c>
+      <c r="K8" s="3">
         <v>550800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>572500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>581500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>596500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>609300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>655700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>574700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>501000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>464600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>545700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>492200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>502100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>369700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>403000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>347400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>306900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>444600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>89900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>62300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>86000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>64400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>52500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>101800</v>
+        <v>199100</v>
       </c>
       <c r="E9" s="3">
-        <v>103800</v>
+        <v>248100</v>
       </c>
       <c r="F9" s="3">
-        <v>103200</v>
+        <v>254700</v>
       </c>
       <c r="G9" s="3">
-        <v>90200</v>
+        <v>237000</v>
       </c>
       <c r="H9" s="3">
-        <v>91400</v>
+        <v>191300</v>
       </c>
       <c r="I9" s="3">
-        <v>90300</v>
+        <v>190100</v>
       </c>
       <c r="J9" s="3">
+        <v>201900</v>
+      </c>
+      <c r="K9" s="3">
         <v>82600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>85300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>77200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>84900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>81200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>89200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>80100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>66500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>61900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>60200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>58900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>54800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>27200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>58400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>47400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>34800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>32800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>24500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>32900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>14300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>8800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>11400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>484700</v>
+        <v>423900</v>
       </c>
       <c r="E10" s="3">
-        <v>481800</v>
+        <v>324300</v>
       </c>
       <c r="F10" s="3">
-        <v>530600</v>
+        <v>320500</v>
       </c>
       <c r="G10" s="3">
-        <v>513300</v>
+        <v>396900</v>
       </c>
       <c r="H10" s="3">
-        <v>460500</v>
+        <v>395400</v>
       </c>
       <c r="I10" s="3">
-        <v>417100</v>
+        <v>349600</v>
       </c>
       <c r="J10" s="3">
+        <v>322000</v>
+      </c>
+      <c r="K10" s="3">
         <v>468200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>487300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>504300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>511600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>528100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>566600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>494600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>434500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>402700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>485500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>433300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>447300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>342400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>344600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>300000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>272100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>411900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>65500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>29500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>71700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>55600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>41100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1112,8 +1125,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1207,8 +1221,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,31 +1319,34 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>4200</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1397,31 +1417,34 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>2600</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>2600</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>2600</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>2600</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1453,8 +1476,8 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>8</v>
+      <c r="U15" s="3">
+        <v>0</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>8</v>
@@ -1471,29 +1494,32 @@
       <c r="Z15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AA15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB15" s="3">
         <v>100</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD15" s="3">
-        <v>100</v>
+      <c r="AD15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE15" s="3">
         <v>100</v>
       </c>
-      <c r="AF15" s="3" t="s">
-        <v>8</v>
+      <c r="AF15" s="3">
+        <v>100</v>
       </c>
       <c r="AG15" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,198 +1550,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>306600</v>
+        <v>287600</v>
       </c>
       <c r="E17" s="3">
-        <v>393200</v>
+        <v>328700</v>
       </c>
       <c r="F17" s="3">
-        <v>453400</v>
+        <v>342400</v>
       </c>
       <c r="G17" s="3">
-        <v>407700</v>
+        <v>342900</v>
       </c>
       <c r="H17" s="3">
-        <v>385300</v>
+        <v>282400</v>
       </c>
       <c r="I17" s="3">
-        <v>365400</v>
+        <v>272400</v>
       </c>
       <c r="J17" s="3">
+        <v>278300</v>
+      </c>
+      <c r="K17" s="3">
         <v>417700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>412500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>441000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>408800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>405100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>386500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>308600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>284200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>291800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>343700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>345800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>473100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>329300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>256000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>218000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>175600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>139100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>68400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>141500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>55400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>36100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>49600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>9900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>279800</v>
+        <v>335400</v>
       </c>
       <c r="E18" s="3">
-        <v>192300</v>
+        <v>243800</v>
       </c>
       <c r="F18" s="3">
-        <v>180400</v>
+        <v>232800</v>
       </c>
       <c r="G18" s="3">
-        <v>195800</v>
+        <v>291100</v>
       </c>
       <c r="H18" s="3">
-        <v>166600</v>
+        <v>304300</v>
       </c>
       <c r="I18" s="3">
-        <v>142000</v>
+        <v>267400</v>
       </c>
       <c r="J18" s="3">
+        <v>245600</v>
+      </c>
+      <c r="K18" s="3">
         <v>133100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>160000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>140500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>187700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>204100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>269200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>266100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>216800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>172800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>202100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>146400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>29100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>40400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>147000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>129400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>131300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>305500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>21500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-79200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>30600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>28400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-8200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-5600</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,126 +1782,130 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-35600</v>
+      </c>
+      <c r="F20" s="3">
+        <v>28300</v>
+      </c>
+      <c r="G20" s="3">
+        <v>110000</v>
+      </c>
+      <c r="H20" s="3">
+        <v>108600</v>
+      </c>
+      <c r="I20" s="3">
+        <v>82500</v>
+      </c>
+      <c r="J20" s="3">
+        <v>94600</v>
+      </c>
+      <c r="K20" s="3">
+        <v>11400</v>
+      </c>
+      <c r="L20" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M20" s="3">
+        <v>20100</v>
+      </c>
+      <c r="N20" s="3">
+        <v>4400</v>
+      </c>
+      <c r="O20" s="3">
+        <v>8300</v>
+      </c>
+      <c r="P20" s="3">
+        <v>4100</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>14400</v>
+      </c>
+      <c r="R20" s="3">
+        <v>6600</v>
+      </c>
+      <c r="S20" s="3">
+        <v>15400</v>
+      </c>
+      <c r="T20" s="3">
         <v>12900</v>
       </c>
-      <c r="E20" s="3">
-        <v>22900</v>
-      </c>
-      <c r="F20" s="3">
-        <v>7200</v>
-      </c>
-      <c r="G20" s="3">
-        <v>12600</v>
-      </c>
-      <c r="H20" s="3">
-        <v>26100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>13400</v>
-      </c>
-      <c r="J20" s="3">
-        <v>11400</v>
-      </c>
-      <c r="K20" s="3">
-        <v>1800</v>
-      </c>
-      <c r="L20" s="3">
-        <v>20100</v>
-      </c>
-      <c r="M20" s="3">
-        <v>4400</v>
-      </c>
-      <c r="N20" s="3">
-        <v>8300</v>
-      </c>
-      <c r="O20" s="3">
-        <v>4100</v>
-      </c>
-      <c r="P20" s="3">
-        <v>14400</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>6600</v>
-      </c>
-      <c r="R20" s="3">
-        <v>15400</v>
-      </c>
-      <c r="S20" s="3">
-        <v>12900</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>7300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>6900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>13600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>8800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>800</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>400</v>
       </c>
       <c r="AC20" s="3">
         <v>400</v>
       </c>
       <c r="AD20" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AE20" s="3">
         <v>200</v>
       </c>
       <c r="AF20" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG20" s="3">
         <v>100</v>
       </c>
-      <c r="AG20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>8</v>
+      <c r="D21" s="3">
+        <v>329200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>282000</v>
+      </c>
+      <c r="F21" s="3">
+        <v>207000</v>
+      </c>
+      <c r="G21" s="3">
+        <v>183700</v>
+      </c>
+      <c r="H21" s="3">
+        <v>198400</v>
+      </c>
+      <c r="I21" s="3">
+        <v>187500</v>
+      </c>
+      <c r="J21" s="3">
+        <v>153800</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>8</v>
@@ -1915,55 +1952,58 @@
       <c r="Y21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA21" s="3">
         <v>306600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>22700</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF21" s="3">
         <v>3200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-8000</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1980,8 +2020,8 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>8</v>
+      <c r="P22" s="3">
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>8</v>
@@ -1998,18 +2038,18 @@
       <c r="U22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V22" s="3">
+      <c r="V22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W22" s="3">
         <v>2200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>4000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>800</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z22" s="3" t="s">
         <v>8</v>
       </c>
@@ -2022,8 +2062,8 @@
       <c r="AC22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD22" s="3">
-        <v>0</v>
+      <c r="AD22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE22" s="3">
         <v>0</v>
@@ -2034,198 +2074,207 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>292800</v>
+        <v>336000</v>
       </c>
       <c r="E23" s="3">
-        <v>215200</v>
+        <v>285800</v>
       </c>
       <c r="F23" s="3">
-        <v>187600</v>
+        <v>211400</v>
       </c>
       <c r="G23" s="3">
-        <v>208400</v>
+        <v>187700</v>
       </c>
       <c r="H23" s="3">
-        <v>192600</v>
+        <v>202600</v>
       </c>
       <c r="I23" s="3">
-        <v>155400</v>
+        <v>188400</v>
       </c>
       <c r="J23" s="3">
+        <v>160400</v>
+      </c>
+      <c r="K23" s="3">
         <v>144500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>161900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>160600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>192000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>212400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>273300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>280500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>223500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>188200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>215000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>153700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>36000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>51800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>143900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>123400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>140100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>306100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>22300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-78800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>31000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>28500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-8000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-5600</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>98700</v>
+        <v>79600</v>
       </c>
       <c r="E24" s="3">
-        <v>51600</v>
+        <v>96300</v>
       </c>
       <c r="F24" s="3">
+        <v>50700</v>
+      </c>
+      <c r="G24" s="3">
         <v>31500</v>
       </c>
-      <c r="G24" s="3">
-        <v>48000</v>
-      </c>
       <c r="H24" s="3">
-        <v>38500</v>
+        <v>46700</v>
       </c>
       <c r="I24" s="3">
-        <v>24300</v>
+        <v>37600</v>
       </c>
       <c r="J24" s="3">
+        <v>25100</v>
+      </c>
+      <c r="K24" s="3">
         <v>22100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>25300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>25100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>29900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>32500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>51000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>58200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>35900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>20500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>33500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>24500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>7100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-14300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>29500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>27000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>30100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>64600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>7900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-4600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>7500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>6400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-2100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,198 +2368,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>194100</v>
+        <v>256400</v>
       </c>
       <c r="E26" s="3">
-        <v>163600</v>
+        <v>189400</v>
       </c>
       <c r="F26" s="3">
+        <v>160700</v>
+      </c>
+      <c r="G26" s="3">
         <v>156200</v>
       </c>
-      <c r="G26" s="3">
-        <v>160400</v>
-      </c>
       <c r="H26" s="3">
-        <v>154100</v>
+        <v>155900</v>
       </c>
       <c r="I26" s="3">
-        <v>131100</v>
+        <v>150800</v>
       </c>
       <c r="J26" s="3">
+        <v>135400</v>
+      </c>
+      <c r="K26" s="3">
         <v>122400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>136600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>135500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>162200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>179800</v>
-      </c>
-      <c r="O26" s="3">
-        <v>222300</v>
       </c>
       <c r="P26" s="3">
         <v>222300</v>
       </c>
       <c r="Q26" s="3">
+        <v>222300</v>
+      </c>
+      <c r="R26" s="3">
         <v>187500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>167600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>181500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>129200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>28900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>66200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>114400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>96400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>110000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>241500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>14400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-74200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>23500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>22100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-5900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>194600</v>
+        <v>257000</v>
       </c>
       <c r="E27" s="3">
-        <v>164100</v>
+        <v>190000</v>
       </c>
       <c r="F27" s="3">
-        <v>156700</v>
+        <v>161200</v>
       </c>
       <c r="G27" s="3">
-        <v>161000</v>
+        <v>156800</v>
       </c>
       <c r="H27" s="3">
-        <v>154700</v>
+        <v>156500</v>
       </c>
       <c r="I27" s="3">
-        <v>131700</v>
+        <v>151300</v>
       </c>
       <c r="J27" s="3">
+        <v>136000</v>
+      </c>
+      <c r="K27" s="3">
         <v>122900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>137200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>136200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>162900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>182200</v>
-      </c>
-      <c r="O27" s="3">
-        <v>222300</v>
       </c>
       <c r="P27" s="3">
         <v>222300</v>
       </c>
       <c r="Q27" s="3">
+        <v>222300</v>
+      </c>
+      <c r="R27" s="3">
         <v>187600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>167700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>181500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>129200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>28900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>66200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>114400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>96400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>110000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>241500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-419200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-74200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>23500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>22100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-5900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2662,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2699,8 +2760,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2858,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,198 +2956,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E32" s="3">
+        <v>35600</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-28300</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-110000</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-108600</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-82500</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-94600</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="O32" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="P32" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="R32" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="S32" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="T32" s="3">
         <v>-12900</v>
       </c>
-      <c r="E32" s="3">
-        <v>-22900</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-7200</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-12600</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-26100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-13400</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-11400</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-20100</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-4400</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-8300</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-14400</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-15400</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-12900</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-7300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-6900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-13600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>5200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-8800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-800</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-400</v>
       </c>
       <c r="AC32" s="3">
         <v>-400</v>
       </c>
       <c r="AD32" s="3">
-        <v>-200</v>
+        <v>-400</v>
       </c>
       <c r="AE32" s="3">
         <v>-200</v>
       </c>
       <c r="AF32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-100</v>
       </c>
-      <c r="AG32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>194600</v>
+        <v>257000</v>
       </c>
       <c r="E33" s="3">
-        <v>164100</v>
+        <v>190000</v>
       </c>
       <c r="F33" s="3">
-        <v>156700</v>
+        <v>161200</v>
       </c>
       <c r="G33" s="3">
-        <v>161000</v>
+        <v>156800</v>
       </c>
       <c r="H33" s="3">
-        <v>154700</v>
+        <v>156500</v>
       </c>
       <c r="I33" s="3">
-        <v>131700</v>
+        <v>151300</v>
       </c>
       <c r="J33" s="3">
+        <v>136000</v>
+      </c>
+      <c r="K33" s="3">
         <v>122900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>137200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>136200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>162900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>182200</v>
-      </c>
-      <c r="O33" s="3">
-        <v>222300</v>
       </c>
       <c r="P33" s="3">
         <v>222300</v>
       </c>
       <c r="Q33" s="3">
+        <v>222300</v>
+      </c>
+      <c r="R33" s="3">
         <v>187600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>167700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>181500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>129200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>28900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>66200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>114400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>96400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>110000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>241500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-419200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-74200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>23500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>22100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-5900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3250,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>194600</v>
+        <v>257000</v>
       </c>
       <c r="E35" s="3">
-        <v>164100</v>
+        <v>190000</v>
       </c>
       <c r="F35" s="3">
-        <v>156700</v>
+        <v>161200</v>
       </c>
       <c r="G35" s="3">
-        <v>161000</v>
+        <v>156800</v>
       </c>
       <c r="H35" s="3">
-        <v>154700</v>
+        <v>156500</v>
       </c>
       <c r="I35" s="3">
-        <v>131700</v>
+        <v>151300</v>
       </c>
       <c r="J35" s="3">
+        <v>136000</v>
+      </c>
+      <c r="K35" s="3">
         <v>122900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>137200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>136200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>162900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>182200</v>
-      </c>
-      <c r="O35" s="3">
-        <v>222300</v>
       </c>
       <c r="P35" s="3">
         <v>222300</v>
       </c>
       <c r="Q35" s="3">
+        <v>222300</v>
+      </c>
+      <c r="R35" s="3">
         <v>187600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>167700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>181500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>129200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>28900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>66200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>114400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>96400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>110000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>241500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-419200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-74200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>23500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>22100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-5900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3489,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,89 +3525,90 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>893400</v>
+        <v>611400</v>
       </c>
       <c r="E41" s="3">
-        <v>747400</v>
+        <v>872100</v>
       </c>
       <c r="F41" s="3">
-        <v>589000</v>
+        <v>734200</v>
       </c>
       <c r="G41" s="3">
-        <v>696200</v>
+        <v>589200</v>
       </c>
       <c r="H41" s="3">
-        <v>741000</v>
+        <v>676800</v>
       </c>
       <c r="I41" s="3">
-        <v>723000</v>
+        <v>724800</v>
       </c>
       <c r="J41" s="3">
+        <v>746600</v>
+      </c>
+      <c r="K41" s="3">
         <v>1010200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>997500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>968300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>852800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>842700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>600500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>745700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>831600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>615000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>710400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>563400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>570500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>324600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>287700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>285100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>195700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>210000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>281100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>65600</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3534,38 +3621,41 @@
       <c r="AG41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>41000</v>
+        <v>444800</v>
       </c>
       <c r="E42" s="3">
-        <v>2100</v>
+        <v>40100</v>
       </c>
       <c r="F42" s="3">
         <v>2100</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="H42" s="3">
-        <v>34900</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>33300</v>
+        <v>34100</v>
       </c>
       <c r="J42" s="3">
+        <v>34400</v>
+      </c>
+      <c r="K42" s="3">
         <v>8000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4100</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>8</v>
       </c>
@@ -3578,8 +3668,8 @@
       <c r="P42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="Q42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -3629,89 +3719,92 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4533100</v>
+        <v>4065500</v>
       </c>
       <c r="E43" s="3">
-        <v>4648500</v>
+        <v>3970900</v>
       </c>
       <c r="F43" s="3">
-        <v>4467000</v>
+        <v>4136000</v>
       </c>
       <c r="G43" s="3">
-        <v>4336500</v>
+        <v>3886500</v>
       </c>
       <c r="H43" s="3">
-        <v>3997700</v>
+        <v>3615300</v>
       </c>
       <c r="I43" s="3">
-        <v>3579700</v>
+        <v>3368100</v>
       </c>
       <c r="J43" s="3">
+        <v>3146800</v>
+      </c>
+      <c r="K43" s="3">
         <v>3207600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3030500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2643400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2653400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2444000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2516000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2232800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1947600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1918900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2034700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2097200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2153800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2168400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2094600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1663200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1050200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>642500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>177700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>272300</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3724,31 +3817,34 @@
       <c r="AG43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3819,89 +3915,92 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>371300</v>
+        <v>326700</v>
       </c>
       <c r="E45" s="3">
-        <v>497300</v>
+        <v>469600</v>
       </c>
       <c r="F45" s="3">
-        <v>552400</v>
+        <v>453600</v>
       </c>
       <c r="G45" s="3">
-        <v>607800</v>
+        <v>611100</v>
       </c>
       <c r="H45" s="3">
-        <v>521300</v>
+        <v>626700</v>
       </c>
       <c r="I45" s="3">
-        <v>601000</v>
+        <v>570900</v>
       </c>
       <c r="J45" s="3">
+        <v>589900</v>
+      </c>
+      <c r="K45" s="3">
         <v>581200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>565600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>671200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>555600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>537700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>521500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>563400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>511100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>511200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>517600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>606800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>597700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>510200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>498200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>427100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>354900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>213900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>156100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>102600</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3914,89 +4013,92 @@
       <c r="AG45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>5838800</v>
+        <v>5938900</v>
       </c>
       <c r="E46" s="3">
-        <v>5895300</v>
+        <v>5699200</v>
       </c>
       <c r="F46" s="3">
-        <v>5610400</v>
+        <v>5791300</v>
       </c>
       <c r="G46" s="3">
-        <v>5640600</v>
+        <v>5612300</v>
       </c>
       <c r="H46" s="3">
-        <v>5294900</v>
+        <v>5483300</v>
       </c>
       <c r="I46" s="3">
-        <v>4936900</v>
+        <v>5178700</v>
       </c>
       <c r="J46" s="3">
+        <v>5097900</v>
+      </c>
+      <c r="K46" s="3">
         <v>4807100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4597700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4282900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4061900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3824400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3638000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3541900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3290300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3045100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3262700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3267400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3322000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3003100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2880600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2375500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1600800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1066300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>615000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>440500</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD46" s="3" t="s">
         <v>8</v>
       </c>
@@ -4009,77 +4111,80 @@
       <c r="AG46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>443300</v>
-      </c>
-      <c r="E47" s="3">
-        <v>446100</v>
-      </c>
-      <c r="F47" s="3">
-        <v>514000</v>
-      </c>
-      <c r="G47" s="3">
-        <v>508800</v>
-      </c>
-      <c r="H47" s="3">
-        <v>505900</v>
-      </c>
-      <c r="I47" s="3">
-        <v>507000</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K47" s="3">
         <v>580900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>610100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>651700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>607100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>526500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>579600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>358000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>201600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>144900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>127700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>99300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>55100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>12100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>4700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>100</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z47" s="3" t="s">
         <v>8</v>
       </c>
@@ -4092,8 +4197,8 @@
       <c r="AC47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD47" s="3">
-        <v>0</v>
+      <c r="AD47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE47" s="3">
         <v>0</v>
@@ -4104,76 +4209,79 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>49600</v>
+        <v>47200</v>
       </c>
       <c r="E48" s="3">
-        <v>44200</v>
+        <v>41200</v>
       </c>
       <c r="F48" s="3">
-        <v>39100</v>
+        <v>35600</v>
       </c>
       <c r="G48" s="3">
-        <v>28400</v>
+        <v>39000</v>
       </c>
       <c r="H48" s="3">
-        <v>23400</v>
+        <v>20300</v>
       </c>
       <c r="I48" s="3">
-        <v>19900</v>
+        <v>14700</v>
       </c>
       <c r="J48" s="3">
+        <v>11100</v>
+      </c>
+      <c r="K48" s="3">
         <v>14600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>12400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>9500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>11100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>12200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>11600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>11200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2200</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>1000</v>
       </c>
       <c r="Z48" s="3">
         <v>1000</v>
@@ -4184,8 +4292,8 @@
       <c r="AB48" s="3">
         <v>1000</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>8</v>
+      <c r="AC48" s="3">
+        <v>1000</v>
       </c>
       <c r="AD48" s="3" t="s">
         <v>8</v>
@@ -4199,31 +4307,34 @@
       <c r="AG48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>7500</v>
+        <v>144900</v>
       </c>
       <c r="E49" s="3">
-        <v>7600</v>
+        <v>140400</v>
       </c>
       <c r="F49" s="3">
-        <v>7700</v>
+        <v>142100</v>
       </c>
       <c r="G49" s="3">
-        <v>7700</v>
+        <v>145600</v>
       </c>
       <c r="H49" s="3">
-        <v>700</v>
+        <v>142200</v>
       </c>
       <c r="I49" s="3">
-        <v>700</v>
+        <v>136900</v>
       </c>
       <c r="J49" s="3">
-        <v>700</v>
+        <v>145300</v>
       </c>
       <c r="K49" s="3">
         <v>700</v>
@@ -4232,19 +4343,19 @@
         <v>700</v>
       </c>
       <c r="M49" s="3">
+        <v>700</v>
+      </c>
+      <c r="N49" s="3">
         <v>800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>141100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>700</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>500</v>
       </c>
       <c r="R49" s="3">
         <v>500</v>
@@ -4253,22 +4364,22 @@
         <v>500</v>
       </c>
       <c r="T49" s="3">
+        <v>500</v>
+      </c>
+      <c r="U49" s="3">
         <v>400</v>
-      </c>
-      <c r="U49" s="3">
-        <v>500</v>
       </c>
       <c r="V49" s="3">
         <v>500</v>
       </c>
       <c r="W49" s="3">
+        <v>500</v>
+      </c>
+      <c r="X49" s="3">
         <v>600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>300</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>100</v>
       </c>
       <c r="Z49" s="3">
         <v>100</v>
@@ -4279,8 +4390,8 @@
       <c r="AB49" s="3">
         <v>100</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>8</v>
+      <c r="AC49" s="3">
+        <v>100</v>
       </c>
       <c r="AD49" s="3" t="s">
         <v>8</v>
@@ -4294,8 +4405,11 @@
       <c r="AG49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4503,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,89 +4601,92 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>34100</v>
+      </c>
+      <c r="E52" s="3">
+        <v>39200</v>
+      </c>
+      <c r="F52" s="3">
+        <v>62000</v>
+      </c>
+      <c r="G52" s="3">
+        <v>84200</v>
+      </c>
+      <c r="H52" s="3">
+        <v>85400</v>
+      </c>
+      <c r="I52" s="3">
+        <v>80200</v>
+      </c>
+      <c r="J52" s="3">
+        <v>95800</v>
+      </c>
+      <c r="K52" s="3">
         <v>284400</v>
       </c>
-      <c r="E52" s="3">
-        <v>293000</v>
-      </c>
-      <c r="F52" s="3">
-        <v>288300</v>
-      </c>
-      <c r="G52" s="3">
-        <v>305100</v>
-      </c>
-      <c r="H52" s="3">
-        <v>294000</v>
-      </c>
-      <c r="I52" s="3">
-        <v>298600</v>
-      </c>
-      <c r="J52" s="3">
-        <v>284400</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>300400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>287600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>267100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>115000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>164800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>147500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>207100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>194700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>169500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>154500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>212000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>107400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>25500</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z52" s="3">
-        <v>0</v>
+      <c r="Z52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="3">
         <v>86800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>67400</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4579,8 +4699,11 @@
       <c r="AG52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,89 +4797,92 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>6623700</v>
+        <v>6698800</v>
       </c>
       <c r="E54" s="3">
-        <v>6686200</v>
+        <v>6465300</v>
       </c>
       <c r="F54" s="3">
-        <v>6459500</v>
+        <v>6568300</v>
       </c>
       <c r="G54" s="3">
-        <v>6490600</v>
+        <v>6461600</v>
       </c>
       <c r="H54" s="3">
-        <v>6118800</v>
+        <v>6309700</v>
       </c>
       <c r="I54" s="3">
-        <v>5763200</v>
+        <v>5984600</v>
       </c>
       <c r="J54" s="3">
+        <v>5951100</v>
+      </c>
+      <c r="K54" s="3">
         <v>5687600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5521200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5236300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4950100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4616300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4390300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4056700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3707600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3394700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3571600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3533800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3601200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3134400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2913900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2378000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1601900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1067400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>702900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>509000</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD54" s="3" t="s">
         <v>8</v>
       </c>
@@ -4769,8 +4895,11 @@
       <c r="AG54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +4933,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,31 +4969,32 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>0</v>
-      </c>
-      <c r="E57" s="3">
-        <v>0</v>
-      </c>
-      <c r="F57" s="3">
-        <v>0</v>
-      </c>
-      <c r="G57" s="3">
-        <v>0</v>
-      </c>
-      <c r="H57" s="3">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3">
-        <v>0</v>
+      <c r="D57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -4934,77 +5065,80 @@
       <c r="AG57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>149200</v>
+        <v>148700</v>
       </c>
       <c r="E58" s="3">
-        <v>96400</v>
+        <v>145700</v>
       </c>
       <c r="F58" s="3">
-        <v>112600</v>
+        <v>94700</v>
       </c>
       <c r="G58" s="3">
-        <v>106600</v>
+        <v>116700</v>
       </c>
       <c r="H58" s="3">
-        <v>36700</v>
+        <v>103600</v>
       </c>
       <c r="I58" s="3">
+        <v>35900</v>
+      </c>
+      <c r="J58" s="3">
+        <v>21800</v>
+      </c>
+      <c r="K58" s="3">
         <v>21100</v>
       </c>
-      <c r="J58" s="3">
-        <v>21100</v>
-      </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>88400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>85000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>81000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>54800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>47700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>48300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>32300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>26000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>27200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>27700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>68600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>30800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>239500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>223900</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z58" s="3" t="s">
         <v>8</v>
       </c>
@@ -5017,8 +5151,8 @@
       <c r="AC58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD58" s="3">
-        <v>0</v>
+      <c r="AD58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE58" s="3">
         <v>0</v>
@@ -5029,89 +5163,92 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2231000</v>
+        <v>1774000</v>
       </c>
       <c r="E59" s="3">
-        <v>2690200</v>
+        <v>1868000</v>
       </c>
       <c r="F59" s="3">
-        <v>2692900</v>
+        <v>2271200</v>
       </c>
       <c r="G59" s="3">
-        <v>2571400</v>
+        <v>2499300</v>
       </c>
       <c r="H59" s="3">
-        <v>2245300</v>
+        <v>2115500</v>
       </c>
       <c r="I59" s="3">
-        <v>2541400</v>
+        <v>1934000</v>
       </c>
       <c r="J59" s="3">
+        <v>2344000</v>
+      </c>
+      <c r="K59" s="3">
         <v>2340300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2390600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2253800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1939500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1893900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1870500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1877300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1841500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1837100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1863800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1930800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2084600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1457800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1280000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1109500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>754700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>420300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>413100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>452200</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD59" s="3" t="s">
         <v>8</v>
       </c>
@@ -5124,89 +5261,92 @@
       <c r="AG59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2380300</v>
+        <v>2318000</v>
       </c>
       <c r="E60" s="3">
-        <v>2786600</v>
+        <v>2323400</v>
       </c>
       <c r="F60" s="3">
-        <v>2805400</v>
+        <v>2737400</v>
       </c>
       <c r="G60" s="3">
-        <v>2678100</v>
+        <v>2806400</v>
       </c>
       <c r="H60" s="3">
-        <v>2281900</v>
+        <v>2603400</v>
       </c>
       <c r="I60" s="3">
-        <v>2562600</v>
+        <v>2231900</v>
       </c>
       <c r="J60" s="3">
+        <v>2646100</v>
+      </c>
+      <c r="K60" s="3">
         <v>2361400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2479000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2338800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2020400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1948600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1918300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1925600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1873800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1863100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1891000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1958600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2153300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1488600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1519500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1333300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>754700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>420300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>413100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>452200</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD60" s="3" t="s">
         <v>8</v>
       </c>
@@ -5219,31 +5359,34 @@
       <c r="AG60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>33100</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>23500</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>23700</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>14500</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>13500</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>8500</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>6700</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -5314,83 +5457,86 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1052600</v>
+        <v>1011300</v>
       </c>
       <c r="E62" s="3">
-        <v>778200</v>
+        <v>941500</v>
       </c>
       <c r="F62" s="3">
-        <v>551100</v>
+        <v>713900</v>
       </c>
       <c r="G62" s="3">
-        <v>833700</v>
+        <v>505100</v>
       </c>
       <c r="H62" s="3">
-        <v>892400</v>
+        <v>780900</v>
       </c>
       <c r="I62" s="3">
-        <v>419500</v>
+        <v>847500</v>
       </c>
       <c r="J62" s="3">
+        <v>409700</v>
+      </c>
+      <c r="K62" s="3">
         <v>657200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>556800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>531300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>695500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>571100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>465300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>337600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>317300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>211800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>467700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>542400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>490300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>534900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>342300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>121400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>54400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2300</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5409,8 +5555,11 @@
       <c r="AG62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5653,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5751,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,89 +5849,92 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3441900</v>
+        <v>3434200</v>
       </c>
       <c r="E66" s="3">
-        <v>3574300</v>
+        <v>3350800</v>
       </c>
       <c r="F66" s="3">
-        <v>3366800</v>
+        <v>3501900</v>
       </c>
       <c r="G66" s="3">
-        <v>3522500</v>
+        <v>3357600</v>
       </c>
       <c r="H66" s="3">
-        <v>3185100</v>
+        <v>3413800</v>
       </c>
       <c r="I66" s="3">
-        <v>2993300</v>
+        <v>3104700</v>
       </c>
       <c r="J66" s="3">
+        <v>3079300</v>
+      </c>
+      <c r="K66" s="3">
         <v>3030500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3048000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2870500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2717000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2521500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2383600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2263300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2191200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2075000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2358900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2501200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2643700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2023600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1862000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1454700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>809100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>422600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>413100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>452200</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD66" s="3" t="s">
         <v>8</v>
       </c>
@@ -5789,8 +5947,11 @@
       <c r="AG66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +5985,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6081,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6179,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6089,11 +6257,11 @@
         <v>0</v>
       </c>
       <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="3">
         <v>628600</v>
       </c>
-      <c r="AB70" s="3">
-        <v>0</v>
-      </c>
       <c r="AC70" s="3">
         <v>0</v>
       </c>
@@ -6109,8 +6277,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,8 +6375,11 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6215,11 +6389,11 @@
       <c r="E72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F72" s="3">
-        <v>2297600</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>8</v>
+      <c r="F72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G72" s="3">
+        <v>2298300</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>8</v>
@@ -6227,66 +6401,66 @@
       <c r="I72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K72" s="3">
         <v>1805100</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="M72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O72" s="3">
         <v>1328500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1222000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1010000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>763500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>575900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>432200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>250600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>130000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>318900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>256100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>141600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>44300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-62500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-339400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-109100</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD72" s="3" t="s">
         <v>8</v>
       </c>
@@ -6299,8 +6473,11 @@
       <c r="AG72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6571,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6669,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,89 +6767,92 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>3181700</v>
+        <v>3256000</v>
       </c>
       <c r="E76" s="3">
-        <v>3111800</v>
+        <v>3105700</v>
       </c>
       <c r="F76" s="3">
-        <v>3092700</v>
+        <v>3057000</v>
       </c>
       <c r="G76" s="3">
-        <v>2968100</v>
+        <v>3093800</v>
       </c>
       <c r="H76" s="3">
-        <v>2933800</v>
+        <v>2885300</v>
       </c>
       <c r="I76" s="3">
-        <v>2769900</v>
+        <v>2869400</v>
       </c>
       <c r="J76" s="3">
+        <v>2860200</v>
+      </c>
+      <c r="K76" s="3">
         <v>2657100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2473200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2365900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2233100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2094800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2006700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1793300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1516400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1319700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1212800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1032600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>957400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1110700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1051900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>923300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>792800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>644800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-338900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>56800</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD76" s="3" t="s">
         <v>8</v>
       </c>
@@ -6679,8 +6865,11 @@
       <c r="AG76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +6963,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>194600</v>
+        <v>257000</v>
       </c>
       <c r="E81" s="3">
-        <v>164100</v>
+        <v>190000</v>
       </c>
       <c r="F81" s="3">
-        <v>156700</v>
+        <v>161200</v>
       </c>
       <c r="G81" s="3">
-        <v>161000</v>
+        <v>156800</v>
       </c>
       <c r="H81" s="3">
-        <v>154700</v>
+        <v>156500</v>
       </c>
       <c r="I81" s="3">
-        <v>131700</v>
+        <v>151300</v>
       </c>
       <c r="J81" s="3">
+        <v>136000</v>
+      </c>
+      <c r="K81" s="3">
         <v>122900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>137200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>136200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>162900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>182200</v>
-      </c>
-      <c r="O81" s="3">
-        <v>222300</v>
       </c>
       <c r="P81" s="3">
         <v>222300</v>
       </c>
       <c r="Q81" s="3">
+        <v>222300</v>
+      </c>
+      <c r="R81" s="3">
         <v>187600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>167700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>181500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>129200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>28900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>66200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>114400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>96400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>110000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>241500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-419200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-74200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>23500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>22100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-5900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,31 +7202,32 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
+        <v>8200</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+        <v>5900</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -7081,8 +7280,8 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>8</v>
+      <c r="AB83" s="3">
+        <v>0</v>
       </c>
       <c r="AC83" s="3" t="s">
         <v>8</v>
@@ -7099,8 +7298,11 @@
       <c r="AG83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7396,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7494,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7592,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7690,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,56 +7788,59 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>276500</v>
+        <v>338100</v>
       </c>
       <c r="E89" s="3">
-        <v>276100</v>
+        <v>269900</v>
       </c>
       <c r="F89" s="3">
-        <v>331600</v>
+        <v>271200</v>
       </c>
       <c r="G89" s="3">
-        <v>175400</v>
+        <v>331700</v>
       </c>
       <c r="H89" s="3">
-        <v>248300</v>
+        <v>170500</v>
       </c>
       <c r="I89" s="3">
-        <v>248300</v>
+        <v>242900</v>
       </c>
       <c r="J89" s="3">
+        <v>256400</v>
+      </c>
+      <c r="K89" s="3">
         <v>252700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>220000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>352800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>196000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>132800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>252600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>186200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>244000</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>8</v>
       </c>
@@ -7636,8 +7853,8 @@
       <c r="V89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
+      <c r="W89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X89" s="3">
         <v>0</v>
@@ -7651,8 +7868,8 @@
       <c r="AA89" s="3">
         <v>0</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>8</v>
+      <c r="AB89" s="3">
+        <v>0</v>
       </c>
       <c r="AC89" s="3" t="s">
         <v>8</v>
@@ -7669,8 +7886,11 @@
       <c r="AG89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,31 +7924,32 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+        <v>-11900</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -7781,8 +8002,8 @@
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>8</v>
+      <c r="AB91" s="3">
+        <v>0</v>
       </c>
       <c r="AC91" s="3" t="s">
         <v>8</v>
@@ -7799,8 +8020,11 @@
       <c r="AG91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8118,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,56 +8216,59 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-138200</v>
+        <v>-417700</v>
       </c>
       <c r="E94" s="3">
-        <v>-442400</v>
+        <v>-134900</v>
       </c>
       <c r="F94" s="3">
-        <v>-265800</v>
+        <v>-434600</v>
       </c>
       <c r="G94" s="3">
-        <v>-318700</v>
+        <v>-265900</v>
       </c>
       <c r="H94" s="3">
-        <v>-484500</v>
+        <v>-309900</v>
       </c>
       <c r="I94" s="3">
-        <v>-502500</v>
+        <v>-473900</v>
       </c>
       <c r="J94" s="3">
+        <v>-518900</v>
+      </c>
+      <c r="K94" s="3">
         <v>-236900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-411900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-374600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-337100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>10100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-487700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-323400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-63400</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>8</v>
       </c>
@@ -8051,8 +8281,8 @@
       <c r="V94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
+      <c r="W94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X94" s="3">
         <v>0</v>
@@ -8066,8 +8296,8 @@
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>8</v>
+      <c r="AB94" s="3">
+        <v>0</v>
       </c>
       <c r="AC94" s="3" t="s">
         <v>8</v>
@@ -8084,8 +8314,11 @@
       <c r="AG94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,31 +8352,32 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+        <v>132800</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8214,8 +8448,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8546,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8644,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,56 +8742,59 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-108200</v>
+        <v>-178000</v>
       </c>
       <c r="E100" s="3">
-        <v>250300</v>
+        <v>-105600</v>
       </c>
       <c r="F100" s="3">
-        <v>-128500</v>
+        <v>245900</v>
       </c>
       <c r="G100" s="3">
-        <v>99100</v>
+        <v>-128600</v>
       </c>
       <c r="H100" s="3">
-        <v>174300</v>
+        <v>96300</v>
       </c>
       <c r="I100" s="3">
-        <v>5500</v>
+        <v>170500</v>
       </c>
       <c r="J100" s="3">
+        <v>5700</v>
+      </c>
+      <c r="K100" s="3">
         <v>27300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>121700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>296000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>148700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>149600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>64700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>77300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>25700</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>8</v>
       </c>
@@ -8561,8 +8807,8 @@
       <c r="V100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
+      <c r="W100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X100" s="3">
         <v>0</v>
@@ -8576,8 +8822,8 @@
       <c r="AA100" s="3">
         <v>0</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>8</v>
+      <c r="AB100" s="3">
+        <v>0</v>
       </c>
       <c r="AC100" s="3" t="s">
         <v>8</v>
@@ -8594,55 +8840,58 @@
       <c r="AG100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="E101" s="3">
-        <v>300</v>
+        <v>1200</v>
       </c>
       <c r="F101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="H101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I101" s="3">
+        <v>200</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="K101" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="L101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
-        <v>700</v>
-      </c>
-      <c r="H101" s="3">
-        <v>1200</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-400</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="K101" s="3">
-        <v>1000</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-300</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-500</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="Q101" s="3">
         <v>-200</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>8</v>
+      <c r="R101" s="3">
+        <v>-200</v>
       </c>
       <c r="S101" s="3" t="s">
         <v>8</v>
@@ -8656,8 +8905,8 @@
       <c r="V101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
+      <c r="W101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X101" s="3">
         <v>0</v>
@@ -8671,8 +8920,8 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>8</v>
+      <c r="AB101" s="3">
+        <v>0</v>
       </c>
       <c r="AC101" s="3" t="s">
         <v>8</v>
@@ -8689,56 +8938,59 @@
       <c r="AG101" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>30400</v>
+        <v>-261000</v>
       </c>
       <c r="E102" s="3">
-        <v>84200</v>
+        <v>29700</v>
       </c>
       <c r="F102" s="3">
-        <v>-62900</v>
+        <v>82800</v>
       </c>
       <c r="G102" s="3">
-        <v>-43600</v>
+        <v>-63000</v>
       </c>
       <c r="H102" s="3">
-        <v>-60700</v>
+        <v>-42400</v>
       </c>
       <c r="I102" s="3">
-        <v>-249100</v>
+        <v>-59400</v>
       </c>
       <c r="J102" s="3">
+        <v>-257200</v>
+      </c>
+      <c r="K102" s="3">
         <v>39900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-69200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>273900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>7100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>292400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-170400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-60100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>206100</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>8</v>
       </c>
@@ -8751,8 +9003,8 @@
       <c r="V102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
+      <c r="W102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X102" s="3">
         <v>0</v>
@@ -8766,8 +9018,8 @@
       <c r="AA102" s="3">
         <v>0</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>8</v>
+      <c r="AB102" s="3">
+        <v>0</v>
       </c>
       <c r="AC102" s="3" t="s">
         <v>8</v>
@@ -8782,6 +9034,9 @@
         <v>8</v>
       </c>
       <c r="AG102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/QFIN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QFIN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="92">
   <si>
     <t>QFIN</t>
   </si>
@@ -656,442 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>614100</v>
+      </c>
+      <c r="E8" s="3">
         <v>623000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>572500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>575200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>634000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>586700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>539700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>524000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>550800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>572500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>581500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>596500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>609300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>655700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>574700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>501000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>464600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>545700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>492200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>502100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>369700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>403000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>347400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>306900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>444600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>89900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>62300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>86000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>64400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>52500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>208700</v>
+      </c>
+      <c r="E9" s="3">
         <v>199100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>248100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>254700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>237000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>191300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>190100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>201900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>82600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>85300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>77200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>84900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>81200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>89200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>80100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>66500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>61900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>60200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>58900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>54800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>27200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>58400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>47400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>34800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>32800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>24500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>32900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>14300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>8800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>11400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>405400</v>
+      </c>
+      <c r="E10" s="3">
         <v>423900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>324300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>320500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>396900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>395400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>349600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>322000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>468200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>487300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>504300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>511600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>528100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>566600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>494600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>434500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>402700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>485500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>433300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>447300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>342400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>344600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>300000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>272100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>411900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>65500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>29500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>71700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>55600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>41100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1126,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1224,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1322,8 +1338,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1336,20 +1355,20 @@
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>4200</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1420,19 +1439,22 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E15" s="3">
         <v>2600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2500</v>
-      </c>
-      <c r="F15" s="3">
-        <v>2600</v>
       </c>
       <c r="G15" s="3">
         <v>2600</v>
@@ -1441,14 +1463,14 @@
         <v>2600</v>
       </c>
       <c r="I15" s="3">
+        <v>2600</v>
+      </c>
+      <c r="J15" s="3">
         <v>2700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2800</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1479,8 +1501,8 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>8</v>
+      <c r="V15" s="3">
+        <v>0</v>
       </c>
       <c r="W15" s="3" t="s">
         <v>8</v>
@@ -1497,29 +1519,32 @@
       <c r="AA15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AB15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC15" s="3">
         <v>100</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE15" s="3">
-        <v>100</v>
+      <c r="AE15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF15" s="3">
         <v>100</v>
       </c>
-      <c r="AG15" s="3" t="s">
-        <v>8</v>
+      <c r="AG15" s="3">
+        <v>100</v>
       </c>
       <c r="AH15" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1551,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>312400</v>
+      </c>
+      <c r="E17" s="3">
         <v>287600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>328700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>342400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>342900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>282400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>272400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>278300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>417700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>412500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>441000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>408800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>405100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>386500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>308600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>284200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>291800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>343700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>345800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>473100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>329300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>256000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>218000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>175600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>139100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>68400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>141500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>55400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>36100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>49600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>9900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>301600</v>
+      </c>
+      <c r="E18" s="3">
         <v>335400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>243800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>232800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>291100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>304300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>267400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>245600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>133100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>160000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>140500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>187700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>204100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>269200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>266100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>216800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>172800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>202100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>146400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>29100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>40400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>147000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>129400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>131300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>305500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>21500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-79200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>30600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>28400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-8200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-5600</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1783,133 +1815,137 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>47100</v>
+      </c>
+      <c r="E20" s="3">
         <v>8800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-35600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>28300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>110000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>108600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>82500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>94600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>11400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>20100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>4400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>8300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>4100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>14400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>6600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>15400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>12900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>7300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>6900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>13600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>8800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>800</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>400</v>
       </c>
       <c r="AD20" s="3">
         <v>400</v>
       </c>
       <c r="AE20" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AF20" s="3">
         <v>200</v>
       </c>
       <c r="AG20" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH20" s="3">
         <v>100</v>
       </c>
-      <c r="AH20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>257000</v>
+      </c>
+      <c r="E21" s="3">
         <v>329200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>282000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>207000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>183700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>198400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>187500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>153800</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1955,32 +1991,35 @@
       <c r="Z21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB21" s="3">
         <v>306600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>22700</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG21" s="3">
         <v>3200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-8000</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2005,8 +2044,8 @@
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2023,8 +2062,8 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>8</v>
+      <c r="Q22" s="3">
+        <v>0</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>8</v>
@@ -2041,18 +2080,18 @@
       <c r="V22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W22" s="3">
+      <c r="W22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X22" s="3">
         <v>2200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>4000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>800</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA22" s="3" t="s">
         <v>8</v>
       </c>
@@ -2065,8 +2104,8 @@
       <c r="AD22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE22" s="3">
-        <v>0</v>
+      <c r="AE22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF22" s="3">
         <v>0</v>
@@ -2077,204 +2116,213 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>264800</v>
+      </c>
+      <c r="E23" s="3">
         <v>336000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>285800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>211400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>187700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>202600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>188400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>160400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>144500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>161900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>160600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>192000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>212400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>273300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>280500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>223500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>188200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>215000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>153700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>36000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>51800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>143900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>123400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>140100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>306100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>22300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-78800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>31000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>28500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>3100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-8000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-5600</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E24" s="3">
         <v>79600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>96300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>50700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>31500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>46700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>37600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>25100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>22100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>25300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>25100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>29900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>32500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>51000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>58200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>35900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>20500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>33500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>24500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>7100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-14300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>29500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>27000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>30100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>64600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>7900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-4600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>7500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>6400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-2100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2371,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>262000</v>
+      </c>
+      <c r="E26" s="3">
         <v>256400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>189400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>160700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>156200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>155900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>150800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>135400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>122400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>136600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>135500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>162200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>179800</v>
-      </c>
-      <c r="P26" s="3">
-        <v>222300</v>
       </c>
       <c r="Q26" s="3">
         <v>222300</v>
       </c>
       <c r="R26" s="3">
+        <v>222300</v>
+      </c>
+      <c r="S26" s="3">
         <v>187500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>167600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>181500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>129200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>28900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>66200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>114400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>96400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>110000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>241500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>14400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-74200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>23500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>22100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-5900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>262600</v>
+      </c>
+      <c r="E27" s="3">
         <v>257000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>190000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>161200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>156800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>156500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>151300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>136000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>122900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>137200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>136200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>162900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>182200</v>
-      </c>
-      <c r="P27" s="3">
-        <v>222300</v>
       </c>
       <c r="Q27" s="3">
         <v>222300</v>
       </c>
       <c r="R27" s="3">
+        <v>222300</v>
+      </c>
+      <c r="S27" s="3">
         <v>187600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>167700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>181500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>129200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>28900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>66200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>114400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>96400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>110000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>241500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-419200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-74200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>23500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>22100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-5900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2665,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2763,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2861,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2959,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-47100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-8800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>35600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-28300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-110000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-108600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-82500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-94600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-11400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-20100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-4400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-8300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-14400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-6600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-15400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-12900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-7300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-6900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-13600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>5200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-8800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-800</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>-400</v>
       </c>
       <c r="AD32" s="3">
         <v>-400</v>
       </c>
       <c r="AE32" s="3">
-        <v>-200</v>
+        <v>-400</v>
       </c>
       <c r="AF32" s="3">
         <v>-200</v>
       </c>
       <c r="AG32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-100</v>
       </c>
-      <c r="AH32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>262600</v>
+      </c>
+      <c r="E33" s="3">
         <v>257000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>190000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>161200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>156800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>156500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>151300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>136000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>122900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>137200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>136200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>162900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>182200</v>
-      </c>
-      <c r="P33" s="3">
-        <v>222300</v>
       </c>
       <c r="Q33" s="3">
         <v>222300</v>
       </c>
       <c r="R33" s="3">
+        <v>222300</v>
+      </c>
+      <c r="S33" s="3">
         <v>187600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>167700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>181500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>129200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>28900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>66200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>114400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>96400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>110000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>241500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-419200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-74200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>23500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>22100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-5900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3253,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>262600</v>
+      </c>
+      <c r="E35" s="3">
         <v>257000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>190000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>161200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>156800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>156500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>151300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>136000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>122900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>137200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>136200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>162900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>182200</v>
-      </c>
-      <c r="P35" s="3">
-        <v>222300</v>
       </c>
       <c r="Q35" s="3">
         <v>222300</v>
       </c>
       <c r="R35" s="3">
+        <v>222300</v>
+      </c>
+      <c r="S35" s="3">
         <v>187600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>167700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>181500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>129200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>28900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>66200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>114400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>96400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>110000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>241500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-419200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-74200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>23500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>22100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-5900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3490,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3526,92 +3611,93 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>610000</v>
+      </c>
+      <c r="E41" s="3">
         <v>611400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>872100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>734200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>589200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>676800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>724800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>746600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1010200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>997500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>968300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>852800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>842700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>600500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>745700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>831600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>615000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>710400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>563400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>570500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>324600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>287700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>285100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>195700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>210000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>281100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>65600</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3624,41 +3710,44 @@
       <c r="AH41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>465000</v>
+      </c>
+      <c r="E42" s="3">
         <v>444800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>40100</v>
-      </c>
-      <c r="F42" s="3">
-        <v>2100</v>
       </c>
       <c r="G42" s="3">
         <v>2100</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>34100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>34400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>8000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4100</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>8</v>
       </c>
@@ -3671,8 +3760,8 @@
       <c r="Q42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -3722,92 +3811,95 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3964500</v>
+      </c>
+      <c r="E43" s="3">
         <v>4065500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3970900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4136000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3886500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3615300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3368100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3146800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3207600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3030500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2643400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2653400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2444000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2516000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2232800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1947600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1918900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2034700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2097200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2153800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2168400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2094600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1663200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1050200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>642500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>177700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>272300</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3820,8 +3912,11 @@
       <c r="AH43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3846,8 +3941,8 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3918,92 +4013,95 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>298500</v>
+      </c>
+      <c r="E45" s="3">
         <v>326700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>469600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>453600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>611100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>626700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>570900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>589900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>581200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>565600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>671200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>555600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>537700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>521500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>563400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>511100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>511200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>517600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>606800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>597700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>510200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>498200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>427100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>354900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>213900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>156100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>102600</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4016,92 +4114,95 @@
       <c r="AH45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5861100</v>
+      </c>
+      <c r="E46" s="3">
         <v>5938900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5699200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5791300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5612300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5483300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5178700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5097900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4807100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4597700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4282900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4061900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3824400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3638000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3541900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3290300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3045100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3262700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3267400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3322000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3003100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2880600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2375500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1600800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1066300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>615000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>440500</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE46" s="3" t="s">
         <v>8</v>
       </c>
@@ -4114,8 +4215,11 @@
       <c r="AH46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4140,54 +4244,54 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="3">
         <v>580900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>610100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>651700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>607100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>526500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>579600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>358000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>201600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>144900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>127700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>99300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>55100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>12100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>4700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>100</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA47" s="3" t="s">
         <v>8</v>
       </c>
@@ -4200,8 +4304,8 @@
       <c r="AD47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE47" s="3">
-        <v>0</v>
+      <c r="AE47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF47" s="3">
         <v>0</v>
@@ -4212,79 +4316,82 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>49700</v>
+      </c>
+      <c r="E48" s="3">
         <v>47200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>41200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>35600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>39000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>20300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>14700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>11100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>12400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>13100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>9500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>11100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>12200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>11600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>11200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2200</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>1000</v>
       </c>
       <c r="AA48" s="3">
         <v>1000</v>
@@ -4295,8 +4402,8 @@
       <c r="AC48" s="3">
         <v>1000</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>8</v>
+      <c r="AD48" s="3">
+        <v>1000</v>
       </c>
       <c r="AE48" s="3" t="s">
         <v>8</v>
@@ -4310,34 +4417,37 @@
       <c r="AH48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>138500</v>
+      </c>
+      <c r="E49" s="3">
         <v>144900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>140400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>142100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>145600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>142200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>136900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>145300</v>
-      </c>
-      <c r="K49" s="3">
-        <v>700</v>
       </c>
       <c r="L49" s="3">
         <v>700</v>
@@ -4346,19 +4456,19 @@
         <v>700</v>
       </c>
       <c r="N49" s="3">
+        <v>700</v>
+      </c>
+      <c r="O49" s="3">
         <v>800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>141100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>700</v>
-      </c>
-      <c r="R49" s="3">
-        <v>500</v>
       </c>
       <c r="S49" s="3">
         <v>500</v>
@@ -4367,22 +4477,22 @@
         <v>500</v>
       </c>
       <c r="U49" s="3">
+        <v>500</v>
+      </c>
+      <c r="V49" s="3">
         <v>400</v>
-      </c>
-      <c r="V49" s="3">
-        <v>500</v>
       </c>
       <c r="W49" s="3">
         <v>500</v>
       </c>
       <c r="X49" s="3">
+        <v>500</v>
+      </c>
+      <c r="Y49" s="3">
         <v>600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>300</v>
-      </c>
-      <c r="Z49" s="3">
-        <v>100</v>
       </c>
       <c r="AA49" s="3">
         <v>100</v>
@@ -4393,8 +4503,8 @@
       <c r="AC49" s="3">
         <v>100</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>8</v>
+      <c r="AD49" s="3">
+        <v>100</v>
       </c>
       <c r="AE49" s="3" t="s">
         <v>8</v>
@@ -4408,8 +4518,11 @@
       <c r="AH49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4506,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4604,92 +4720,95 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E52" s="3">
         <v>34100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>39200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>62000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>84200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>85400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>80200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>95800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>284400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>300400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>287600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>267100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>115000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>164800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>147500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>207100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>194700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>169500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>154500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>212000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>107400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>25500</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA52" s="3">
-        <v>0</v>
+      <c r="AA52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="3">
         <v>86800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>67400</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4702,8 +4821,11 @@
       <c r="AH52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4800,92 +4922,95 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6594300</v>
+      </c>
+      <c r="E54" s="3">
         <v>6698800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6465300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6568300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6461600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6309700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5984600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5951100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5687600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5521200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5236300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4950100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4616300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4390300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4056700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3707600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3394700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3571600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3533800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3601200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3134400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2913900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2378000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1601900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1067400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>702900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>509000</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE54" s="3" t="s">
         <v>8</v>
       </c>
@@ -4898,8 +5023,11 @@
       <c r="AH54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4934,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4970,8 +5099,9 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4996,8 +5126,8 @@
       <c r="J57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
+      <c r="K57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L57" s="3">
         <v>0</v>
@@ -5068,80 +5198,83 @@
       <c r="AH57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>187700</v>
+      </c>
+      <c r="E58" s="3">
         <v>148700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>145700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>94700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>116700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>103600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>35900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>21800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>21100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>88400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>85000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>81000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>54800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>47700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>48300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>32300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>26000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>27200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>27700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>68600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>30800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>239500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>223900</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA58" s="3" t="s">
         <v>8</v>
       </c>
@@ -5154,8 +5287,8 @@
       <c r="AD58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE58" s="3">
-        <v>0</v>
+      <c r="AE58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF58" s="3">
         <v>0</v>
@@ -5166,92 +5299,95 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1849600</v>
+      </c>
+      <c r="E59" s="3">
         <v>1774000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1868000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2271200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2499300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2115500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1934000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2344000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2340300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2390600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2253800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1939500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1893900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1870500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1877300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1841500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1837100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1863800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1930800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2084600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1457800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1280000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1109500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>754700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>420300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>413100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>452200</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE59" s="3" t="s">
         <v>8</v>
       </c>
@@ -5264,92 +5400,95 @@
       <c r="AH59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2393700</v>
+      </c>
+      <c r="E60" s="3">
         <v>2318000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2323400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2737400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2806400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2603400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2231900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2646100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2361400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2479000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2338800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2020400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1948600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1918300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1925600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1873800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1863100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1891000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1958600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2153300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1488600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1519500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1333300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>754700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>420300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>413100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>452200</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE60" s="3" t="s">
         <v>8</v>
       </c>
@@ -5362,35 +5501,38 @@
       <c r="AH60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E61" s="3">
         <v>33100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>23500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>23700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>14500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>13500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6700</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -5460,86 +5602,89 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>783600</v>
+      </c>
+      <c r="E62" s="3">
         <v>1011300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>941500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>713900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>505100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>780900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>847500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>409700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>657200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>556800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>531300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>695500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>571100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>465300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>337600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>317300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>211800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>467700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>542400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>490300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>534900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>342300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>121400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>54400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2300</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5558,8 +5703,11 @@
       <c r="AH62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5656,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5754,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5852,92 +6006,95 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3272500</v>
+      </c>
+      <c r="E66" s="3">
         <v>3434200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3350800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3501900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3357600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3413800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3104700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3079300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3030500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3048000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2870500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2717000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2521500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2383600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2263300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2191200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2075000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2358900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2501200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2643700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2023600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1862000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1454700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>809100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>422600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>413100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>452200</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE66" s="3" t="s">
         <v>8</v>
       </c>
@@ -5950,8 +6107,11 @@
       <c r="AH66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5986,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6084,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6182,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6260,11 +6427,11 @@
         <v>0</v>
       </c>
       <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
         <v>628600</v>
       </c>
-      <c r="AC70" s="3">
-        <v>0</v>
-      </c>
       <c r="AD70" s="3">
         <v>0</v>
       </c>
@@ -6280,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6378,8 +6548,11 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6392,78 +6565,78 @@
       <c r="F72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H72" s="3">
         <v>2298300</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L72" s="3">
         <v>1805100</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P72" s="3">
         <v>1328500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1222000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1010000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>763500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>575900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>432200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>250600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>130000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>318900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>256100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>141600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>44300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-62500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-339400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-109100</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE72" s="3" t="s">
         <v>8</v>
       </c>
@@ -6476,8 +6649,11 @@
       <c r="AH72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6574,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6672,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6770,92 +6952,95 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3314100</v>
+      </c>
+      <c r="E76" s="3">
         <v>3256000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3105700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3057000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3093800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2885300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2869400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2860200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2657100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2473200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2365900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2233100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2094800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2006700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1793300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1516400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1319700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1212800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1032600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>957400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1110700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1051900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>923300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>792800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>644800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-338900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>56800</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE76" s="3" t="s">
         <v>8</v>
       </c>
@@ -6868,8 +7053,11 @@
       <c r="AH76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6966,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>262600</v>
+      </c>
+      <c r="E81" s="3">
         <v>257000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>190000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>161200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>156800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>156500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>151300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>136000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>122900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>137200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>136200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>162900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>182200</v>
-      </c>
-      <c r="P81" s="3">
-        <v>222300</v>
       </c>
       <c r="Q81" s="3">
         <v>222300</v>
       </c>
       <c r="R81" s="3">
+        <v>222300</v>
+      </c>
+      <c r="S81" s="3">
         <v>187600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>167700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>181500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>129200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>28900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>66200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>114400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>96400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>110000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>241500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-419200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-74200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>23500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>22100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-5900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7203,13 +7400,14 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>8</v>
+      <c r="D83" s="3">
+        <v>7500</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>8</v>
@@ -7217,20 +7415,20 @@
       <c r="F83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G83" s="3">
+      <c r="G83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H83" s="3">
         <v>8200</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J83" s="3">
         <v>5900</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -7283,8 +7481,8 @@
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>8</v>
+      <c r="AC83" s="3">
+        <v>0</v>
       </c>
       <c r="AD83" s="3" t="s">
         <v>8</v>
@@ -7301,8 +7499,11 @@
       <c r="AH83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7399,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7497,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7595,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7693,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7791,59 +8004,62 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>418100</v>
+      </c>
+      <c r="E89" s="3">
         <v>338100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>269900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>271200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>331700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>170500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>242900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>256400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>252700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>220000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>352800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>196000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>132800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>252600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>186200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>244000</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>8</v>
       </c>
@@ -7856,8 +8072,8 @@
       <c r="W89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
+      <c r="X89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y89" s="3">
         <v>0</v>
@@ -7871,8 +8087,8 @@
       <c r="AB89" s="3">
         <v>0</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>8</v>
+      <c r="AC89" s="3">
+        <v>0</v>
       </c>
       <c r="AD89" s="3" t="s">
         <v>8</v>
@@ -7889,8 +8105,11 @@
       <c r="AH89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7925,8 +8144,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7939,20 +8159,20 @@
       <c r="F91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G91" s="3">
+      <c r="G91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="3">
         <v>-11900</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -8005,8 +8225,8 @@
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>8</v>
+      <c r="AC91" s="3">
+        <v>0</v>
       </c>
       <c r="AD91" s="3" t="s">
         <v>8</v>
@@ -8023,8 +8243,11 @@
       <c r="AH91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8121,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8219,59 +8445,62 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-129600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-417700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-134900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-434600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-265900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-309900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-473900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-518900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-236900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-411900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-374600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-337100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>10100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-487700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-323400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-63400</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>8</v>
       </c>
@@ -8284,8 +8513,8 @@
       <c r="W94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
+      <c r="X94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y94" s="3">
         <v>0</v>
@@ -8299,8 +8528,8 @@
       <c r="AB94" s="3">
         <v>0</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>8</v>
+      <c r="AC94" s="3">
+        <v>0</v>
       </c>
       <c r="AD94" s="3" t="s">
         <v>8</v>
@@ -8317,8 +8546,11 @@
       <c r="AH94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8353,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8367,20 +8600,20 @@
       <c r="F96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G96" s="3">
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3">
         <v>132800</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I96" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8451,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8549,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8647,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8745,59 +8987,62 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-256700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-178000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-105600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>245900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-128600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>96300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>170500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>5700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>27300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>121700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>296000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>148700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>149600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>64700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>77300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>25700</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>8</v>
       </c>
@@ -8810,8 +9055,8 @@
       <c r="W100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
+      <c r="X100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y100" s="3">
         <v>0</v>
@@ -8825,8 +9070,8 @@
       <c r="AB100" s="3">
         <v>0</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>8</v>
+      <c r="AC100" s="3">
+        <v>0</v>
       </c>
       <c r="AD100" s="3" t="s">
         <v>8</v>
@@ -8843,58 +9088,61 @@
       <c r="AH100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
         <v>700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-3300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-3200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="R101" s="3">
         <v>-200</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>8</v>
+      <c r="S101" s="3">
+        <v>-200</v>
       </c>
       <c r="T101" s="3" t="s">
         <v>8</v>
@@ -8908,8 +9156,8 @@
       <c r="W101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
+      <c r="X101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y101" s="3">
         <v>0</v>
@@ -8923,8 +9171,8 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-      <c r="AC101" s="3" t="s">
-        <v>8</v>
+      <c r="AC101" s="3">
+        <v>0</v>
       </c>
       <c r="AD101" s="3" t="s">
         <v>8</v>
@@ -8941,59 +9189,62 @@
       <c r="AH101" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>36200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-261000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>29700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>82800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-63000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-42400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-59400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-257200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>39900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-69200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>273900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>7100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>292400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-170400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-60100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>206100</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>8</v>
       </c>
@@ -9006,8 +9257,8 @@
       <c r="W102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
+      <c r="X102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y102" s="3">
         <v>0</v>
@@ -9021,8 +9272,8 @@
       <c r="AB102" s="3">
         <v>0</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>8</v>
+      <c r="AC102" s="3">
+        <v>0</v>
       </c>
       <c r="AD102" s="3" t="s">
         <v>8</v>
@@ -9037,6 +9288,9 @@
         <v>8</v>
       </c>
       <c r="AH102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/QFIN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QFIN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="92">
   <si>
     <t>QFIN</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>646400</v>
+      </c>
+      <c r="E8" s="3">
         <v>614100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>623000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>572500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>575200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>634000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>586700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>539700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>524000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>550800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>572500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>581500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>596500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>609300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>655700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>574700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>501000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>464600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>545700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>492200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>502100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>369700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>403000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>347400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>306900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>444600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>89900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>62300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>86000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>64400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>52500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>234300</v>
+      </c>
+      <c r="E9" s="3">
         <v>208700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>199100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>248100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>254700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>237000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>191300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>190100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>201900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>82600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>85300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>77200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>84900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>81200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>89200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>80100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>66500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>61900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>60200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>58900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>54800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>27200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>58400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>47400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>34800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>32800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>24500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>32900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>14300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>8800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>11400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>412100</v>
+      </c>
+      <c r="E10" s="3">
         <v>405400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>423900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>324300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>320500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>396900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>395400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>349600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>322000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>468200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>487300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>504300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>511600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>528100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>566600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>494600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>434500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>402700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>485500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>433300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>447300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>342400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>344600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>300000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>272100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>411900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>65500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>29500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>71700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>55600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>41100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,8 +1358,11 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1358,20 +1378,20 @@
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>4200</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1442,22 +1462,25 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="E15" s="3">
         <v>2600</v>
       </c>
       <c r="F15" s="3">
+        <v>2600</v>
+      </c>
+      <c r="G15" s="3">
         <v>2500</v>
-      </c>
-      <c r="G15" s="3">
-        <v>2600</v>
       </c>
       <c r="H15" s="3">
         <v>2600</v>
@@ -1466,14 +1489,14 @@
         <v>2600</v>
       </c>
       <c r="J15" s="3">
+        <v>2600</v>
+      </c>
+      <c r="K15" s="3">
         <v>2700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2800</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1504,8 +1527,8 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>8</v>
+      <c r="W15" s="3">
+        <v>0</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>8</v>
@@ -1522,29 +1545,32 @@
       <c r="AB15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AC15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD15" s="3">
         <v>100</v>
       </c>
-      <c r="AD15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF15" s="3">
-        <v>100</v>
+      <c r="AF15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG15" s="3">
         <v>100</v>
       </c>
-      <c r="AH15" s="3" t="s">
-        <v>8</v>
+      <c r="AH15" s="3">
+        <v>100</v>
       </c>
       <c r="AI15" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ15" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>352300</v>
+      </c>
+      <c r="E17" s="3">
         <v>312400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>287600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>328700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>342400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>342900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>282400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>272400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>278300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>417700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>412500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>441000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>408800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>405100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>386500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>308600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>284200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>291800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>343700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>345800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>473100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>329300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>256000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>218000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>175600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>139100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>68400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>141500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>55400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>36100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>49600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>9900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>294100</v>
+      </c>
+      <c r="E18" s="3">
         <v>301600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>335400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>243800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>232800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>291100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>304300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>267400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>245600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>133100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>160000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>140500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>187700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>204100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>269200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>266100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>216800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>172800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>202100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>146400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>29100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>40400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>147000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>129400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>131300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>305500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>21500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-79200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>30600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>28400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-8200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-5600</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,139 +1849,143 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E20" s="3">
         <v>47100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>8800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-35600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>28300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>110000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>108600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>82500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>94600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>11400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>20100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>4400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>8300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>4100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>14400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>6600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>15400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>12900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>7300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>6900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>13600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>8800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>800</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>400</v>
       </c>
       <c r="AE20" s="3">
         <v>400</v>
       </c>
       <c r="AF20" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AG20" s="3">
         <v>200</v>
       </c>
       <c r="AH20" s="3">
+        <v>200</v>
+      </c>
+      <c r="AI20" s="3">
         <v>100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>257000</v>
+        <v>299200</v>
       </c>
       <c r="E21" s="3">
+        <v>257100</v>
+      </c>
+      <c r="F21" s="3">
         <v>329200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>282000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>207000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>183700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>198400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>187500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>153800</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1994,32 +2031,35 @@
       <c r="AA21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC21" s="3">
         <v>306600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>22700</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH21" s="3">
         <v>3200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-8000</v>
       </c>
-      <c r="AI21" s="3" t="s">
+      <c r="AJ21" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2047,8 +2087,8 @@
       <c r="K22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -2065,8 +2105,8 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>8</v>
+      <c r="R22" s="3">
+        <v>0</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>8</v>
@@ -2083,18 +2123,18 @@
       <c r="W22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X22" s="3">
+      <c r="X22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y22" s="3">
         <v>2200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>4000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>800</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB22" s="3" t="s">
         <v>8</v>
       </c>
@@ -2107,8 +2147,8 @@
       <c r="AE22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF22" s="3">
-        <v>0</v>
+      <c r="AF22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG22" s="3">
         <v>0</v>
@@ -2119,210 +2159,219 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>306000</v>
+      </c>
+      <c r="E23" s="3">
         <v>264800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>336000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>285800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>211400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>187700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>202600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>188400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>160400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>144500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>161900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>160600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>192000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>212400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>273300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>280500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>223500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>188200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>215000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>153700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>36000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>51800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>143900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>123400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>140100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>306100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>22300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-78800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>31000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>28500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>3100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-8000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-5600</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>58400</v>
+      </c>
+      <c r="E24" s="3">
         <v>2700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>79600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>96300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>50700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>31500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>46700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>37600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>25100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>22100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>25300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>25100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>29900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>32500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>51000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>58200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>35900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>20500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>33500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>24500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>7100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-14300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>29500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>27000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>30100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>64600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>7900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-4600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>7500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>6400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-2100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>247600</v>
+      </c>
+      <c r="E26" s="3">
         <v>262000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>256400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>189400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>160700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>156200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>155900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>150800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>135400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>122400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>136600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>135500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>162200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>179800</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>222300</v>
       </c>
       <c r="R26" s="3">
         <v>222300</v>
       </c>
       <c r="S26" s="3">
+        <v>222300</v>
+      </c>
+      <c r="T26" s="3">
         <v>187500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>167600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>181500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>129200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>28900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>66200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>114400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>96400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>110000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>241500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>14400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-74200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>23500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>22100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-5900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>248100</v>
+      </c>
+      <c r="E27" s="3">
         <v>262600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>257000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>190000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>161200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>156800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>156500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>151300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>136000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>122900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>137200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>136200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>162900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>182200</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>222300</v>
       </c>
       <c r="R27" s="3">
         <v>222300</v>
       </c>
       <c r="S27" s="3">
+        <v>222300</v>
+      </c>
+      <c r="T27" s="3">
         <v>187600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>167700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>181500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>129200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>28900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>66200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>114400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>96400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>110000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>241500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-419200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-74200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>23500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>22100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-5900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-47100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-8800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>35600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-28300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-110000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-108600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-82500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-94600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-11400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-20100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-4400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-4100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-14400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-6600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-15400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-12900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-7300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-6900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-13600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>5200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-8800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-800</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>-400</v>
       </c>
       <c r="AE32" s="3">
         <v>-400</v>
       </c>
       <c r="AF32" s="3">
-        <v>-200</v>
+        <v>-400</v>
       </c>
       <c r="AG32" s="3">
         <v>-200</v>
       </c>
       <c r="AH32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AI32" s="3">
         <v>-100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>248100</v>
+      </c>
+      <c r="E33" s="3">
         <v>262600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>257000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>190000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>161200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>156800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>156500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>151300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>136000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>122900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>137200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>136200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>162900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>182200</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>222300</v>
       </c>
       <c r="R33" s="3">
         <v>222300</v>
       </c>
       <c r="S33" s="3">
+        <v>222300</v>
+      </c>
+      <c r="T33" s="3">
         <v>187600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>167700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>181500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>129200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>28900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>66200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>114400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>96400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>110000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>241500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-419200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-74200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>23500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>22100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-5900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>248100</v>
+      </c>
+      <c r="E35" s="3">
         <v>262600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>257000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>190000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>161200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>156800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>156500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>151300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>136000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>122900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>137200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>136200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>162900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>182200</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>222300</v>
       </c>
       <c r="R35" s="3">
         <v>222300</v>
       </c>
       <c r="S35" s="3">
+        <v>222300</v>
+      </c>
+      <c r="T35" s="3">
         <v>187600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>167700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>181500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>129200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>28900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>66200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>114400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>96400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>110000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>241500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-419200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-74200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>23500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>22100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-5900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,95 +3698,96 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1182200</v>
+      </c>
+      <c r="E41" s="3">
         <v>610000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>611400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>872100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>734200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>589200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>676800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>724800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>746600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1010200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>997500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>968300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>852800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>842700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>600500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>745700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>831600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>615000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>710400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>563400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>570500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>324600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>287700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>285100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>195700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>210000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>281100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>65600</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3713,44 +3800,47 @@
       <c r="AI41" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ41" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>281200</v>
+      </c>
+      <c r="E42" s="3">
         <v>465000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>444800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>40100</v>
-      </c>
-      <c r="G42" s="3">
-        <v>2100</v>
       </c>
       <c r="H42" s="3">
         <v>2100</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>34100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>34400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>8000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4100</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>8</v>
       </c>
@@ -3763,8 +3853,8 @@
       <c r="R42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
@@ -3814,95 +3904,98 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4547000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3964500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4065500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3970900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4136000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3886500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3615300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3368100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3146800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3207600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3030500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2643400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2653400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2444000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2516000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2232800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1947600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1918900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2034700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2097200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2153800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2168400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2094600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1663200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1050200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>642500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>177700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>272300</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3915,8 +4008,11 @@
       <c r="AI43" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ43" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3944,8 +4040,8 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4016,95 +4112,98 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>282600</v>
+      </c>
+      <c r="E45" s="3">
         <v>298500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>326700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>469600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>453600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>611100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>626700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>570900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>589900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>581200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>565600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>671200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>555600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>537700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>521500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>563400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>511100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>511200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>517600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>606800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>597700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>510200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>498200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>427100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>354900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>213900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>156100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>102600</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4117,95 +4216,98 @@
       <c r="AI45" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ45" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6947300</v>
+      </c>
+      <c r="E46" s="3">
         <v>5861100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5938900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5699200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5791300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5612300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5483300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5178700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5097900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4807100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4597700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4282900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4061900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3824400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3638000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3541900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3290300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3045100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3262700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3267400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3322000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3003100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2880600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2375500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1600800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1066300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>615000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>440500</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF46" s="3" t="s">
         <v>8</v>
       </c>
@@ -4218,8 +4320,11 @@
       <c r="AI46" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ46" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4247,54 +4352,54 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="3">
         <v>580900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>610100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>651700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>607100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>526500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>579600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>358000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>201600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>144900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>127700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>99300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>55100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>12100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>4700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>100</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB47" s="3" t="s">
         <v>8</v>
       </c>
@@ -4307,8 +4412,8 @@
       <c r="AE47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF47" s="3">
-        <v>0</v>
+      <c r="AF47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG47" s="3">
         <v>0</v>
@@ -4319,82 +4424,85 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>49700</v>
+        <v>55900</v>
       </c>
       <c r="E48" s="3">
+        <v>54600</v>
+      </c>
+      <c r="F48" s="3">
         <v>47200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>41200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>35600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>39000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>20300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>14700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>11100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>14600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>12400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>13400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>13100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>9500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>11100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>12200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>11600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>11200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2200</v>
-      </c>
-      <c r="AA48" s="3">
-        <v>1000</v>
       </c>
       <c r="AB48" s="3">
         <v>1000</v>
@@ -4405,8 +4513,8 @@
       <c r="AD48" s="3">
         <v>1000</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>8</v>
+      <c r="AE48" s="3">
+        <v>1000</v>
       </c>
       <c r="AF48" s="3" t="s">
         <v>8</v>
@@ -4420,8 +4528,11 @@
       <c r="AI48" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ48" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4429,28 +4540,28 @@
         <v>138500</v>
       </c>
       <c r="E49" s="3">
+        <v>138500</v>
+      </c>
+      <c r="F49" s="3">
         <v>144900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>140400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>142100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>145600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>142200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>136900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>145300</v>
-      </c>
-      <c r="L49" s="3">
-        <v>700</v>
       </c>
       <c r="M49" s="3">
         <v>700</v>
@@ -4459,19 +4570,19 @@
         <v>700</v>
       </c>
       <c r="O49" s="3">
+        <v>700</v>
+      </c>
+      <c r="P49" s="3">
         <v>800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>141100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>700</v>
-      </c>
-      <c r="S49" s="3">
-        <v>500</v>
       </c>
       <c r="T49" s="3">
         <v>500</v>
@@ -4480,22 +4591,22 @@
         <v>500</v>
       </c>
       <c r="V49" s="3">
+        <v>500</v>
+      </c>
+      <c r="W49" s="3">
         <v>400</v>
-      </c>
-      <c r="W49" s="3">
-        <v>500</v>
       </c>
       <c r="X49" s="3">
         <v>500</v>
       </c>
       <c r="Y49" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z49" s="3">
         <v>600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>300</v>
-      </c>
-      <c r="AA49" s="3">
-        <v>100</v>
       </c>
       <c r="AB49" s="3">
         <v>100</v>
@@ -4506,8 +4617,8 @@
       <c r="AD49" s="3">
         <v>100</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>8</v>
+      <c r="AE49" s="3">
+        <v>100</v>
       </c>
       <c r="AF49" s="3" t="s">
         <v>8</v>
@@ -4521,8 +4632,11 @@
       <c r="AI49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,95 +4840,98 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>28400</v>
+        <v>30800</v>
       </c>
       <c r="E52" s="3">
+        <v>23500</v>
+      </c>
+      <c r="F52" s="3">
         <v>34100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>39200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>62000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>84200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>85400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>80200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>95800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>284400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>300400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>287600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>267100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>115000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>164800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>147500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>207100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>194700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>169500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>154500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>212000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>107400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>25500</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB52" s="3">
-        <v>0</v>
+      <c r="AB52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="3">
         <v>86800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>67400</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4824,8 +4944,11 @@
       <c r="AI52" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ52" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,95 +5048,98 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7665800</v>
+      </c>
+      <c r="E54" s="3">
         <v>6594300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6698800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6465300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6568300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6461600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6309700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5984600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5951100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5687600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5521200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5236300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4950100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4616300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4390300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4056700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3707600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3394700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3571600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3533800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3601200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3134400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2913900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2378000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1601900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1067400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>702900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>509000</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF54" s="3" t="s">
         <v>8</v>
       </c>
@@ -5026,8 +5152,11 @@
       <c r="AI54" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ54" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,8 +5230,9 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5129,8 +5260,8 @@
       <c r="K57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
+      <c r="L57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M57" s="3">
         <v>0</v>
@@ -5201,83 +5332,86 @@
       <c r="AI57" s="3">
         <v>0</v>
       </c>
+      <c r="AJ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>187700</v>
+        <v>168000</v>
       </c>
       <c r="E58" s="3">
+        <v>191400</v>
+      </c>
+      <c r="F58" s="3">
         <v>148700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>145700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>94700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>116700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>103600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>35900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>21800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>21100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>88400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>85000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>81000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>54800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>47700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>48300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>32300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>26000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>27200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>27700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>68600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>30800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>239500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>223900</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB58" s="3" t="s">
         <v>8</v>
       </c>
@@ -5290,8 +5424,8 @@
       <c r="AE58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF58" s="3">
-        <v>0</v>
+      <c r="AF58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG58" s="3">
         <v>0</v>
@@ -5302,95 +5436,98 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1849600</v>
+        <v>1628400</v>
       </c>
       <c r="E59" s="3">
+        <v>2015200</v>
+      </c>
+      <c r="F59" s="3">
         <v>1774000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1868000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2271200</v>
       </c>
-      <c r="H59" s="3">
-        <v>2499300</v>
-      </c>
       <c r="I59" s="3">
+        <v>2499600</v>
+      </c>
+      <c r="J59" s="3">
         <v>2115500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1934000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2344000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2340300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2390600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2253800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1939500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1893900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1870500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1877300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1841500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1837100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1863800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1930800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2084600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1457800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1280000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1109500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>754700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>420300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>413100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>452200</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF59" s="3" t="s">
         <v>8</v>
       </c>
@@ -5403,95 +5540,98 @@
       <c r="AI59" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ59" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2256900</v>
+      </c>
+      <c r="E60" s="3">
         <v>2393700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2318000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2323400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2737400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2806400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2603400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2231900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2646100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2361400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2479000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2338800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2020400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1948600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1918300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1925600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1873800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1863100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1891000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1958600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2153300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1488600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1519500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1333300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>754700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>420300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>413100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>452200</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF60" s="3" t="s">
         <v>8</v>
       </c>
@@ -5504,38 +5644,41 @@
       <c r="AI60" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ60" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>677000</v>
+      </c>
+      <c r="E61" s="3">
         <v>35000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>33100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>23500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>23700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>14500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>13500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6700</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -5605,89 +5748,92 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1467900</v>
+      </c>
+      <c r="E62" s="3">
         <v>783600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1011300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>941500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>713900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>505100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>780900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>847500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>409700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>657200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>556800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>531300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>695500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>571100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>465300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>337600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>317300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>211800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>467700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>542400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>490300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>534900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>342300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>121400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>54400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2300</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5706,8 +5852,11 @@
       <c r="AI62" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ62" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,95 +6164,98 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4480300</v>
+      </c>
+      <c r="E66" s="3">
         <v>3272500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3434200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3350800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3501900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3357600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3413800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3104700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3079300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3030500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3048000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2870500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2717000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2521500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2383600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2263300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2191200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2075000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2358900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2501200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2643700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2023600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1862000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1454700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>809100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>422600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>413100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>452200</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF66" s="3" t="s">
         <v>8</v>
       </c>
@@ -6110,8 +6268,11 @@
       <c r="AI66" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ66" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6430,11 +6598,11 @@
         <v>0</v>
       </c>
       <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD70" s="3">
         <v>628600</v>
       </c>
-      <c r="AD70" s="3">
-        <v>0</v>
-      </c>
       <c r="AE70" s="3">
         <v>0</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,16 +6722,19 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>8</v>
+      <c r="E72" s="3">
+        <v>2870500</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>8</v>
@@ -6568,78 +6742,78 @@
       <c r="G72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I72" s="3">
         <v>2298300</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M72" s="3">
         <v>1805100</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P72" s="3">
+      <c r="P72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q72" s="3">
         <v>1328500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1222000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1010000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>763500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>575900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>432200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>250600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>130000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>318900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>256100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>141600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>44300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-62500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-339400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-109100</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF72" s="3" t="s">
         <v>8</v>
       </c>
@@ -6652,8 +6826,11 @@
       <c r="AI72" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ72" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,95 +7138,98 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3178300</v>
+      </c>
+      <c r="E76" s="3">
         <v>3314100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3256000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3105700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3057000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3093800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2885300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2869400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2860200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2657100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2473200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2365900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2233100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2094800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2006700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1793300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1516400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1319700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1212800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1032600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>957400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1110700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1051900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>923300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>792800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>644800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-338900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>56800</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF76" s="3" t="s">
         <v>8</v>
       </c>
@@ -7056,8 +7242,11 @@
       <c r="AI76" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ76" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>248100</v>
+      </c>
+      <c r="E81" s="3">
         <v>262600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>257000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>190000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>161200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>156800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>156500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>151300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>136000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>122900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>137200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>136200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>162900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>182200</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>222300</v>
       </c>
       <c r="R81" s="3">
         <v>222300</v>
       </c>
       <c r="S81" s="3">
+        <v>222300</v>
+      </c>
+      <c r="T81" s="3">
         <v>187600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>167700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>181500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>129200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>28900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>66200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>114400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>96400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>110000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>241500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-419200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-74200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>23500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>22100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-5900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,37 +7599,38 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3">
         <v>7500</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F83" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I83" s="3">
         <v>8200</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K83" s="3">
         <v>5900</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -7484,8 +7683,8 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>8</v>
+      <c r="AD83" s="3">
+        <v>0</v>
       </c>
       <c r="AE83" s="3" t="s">
         <v>8</v>
@@ -7502,8 +7701,11 @@
       <c r="AI83" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ83" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,62 +8221,65 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3">
         <v>418100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>338100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>269900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>271200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>331700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>170500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>242900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>256400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>252700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>220000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>352800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>196000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>132800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>252600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>186200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>244000</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>8</v>
       </c>
@@ -8075,8 +8292,8 @@
       <c r="X89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
+      <c r="Y89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z89" s="3">
         <v>0</v>
@@ -8090,8 +8307,8 @@
       <c r="AC89" s="3">
         <v>0</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>8</v>
+      <c r="AD89" s="3">
+        <v>0</v>
       </c>
       <c r="AE89" s="3" t="s">
         <v>8</v>
@@ -8108,8 +8325,11 @@
       <c r="AI89" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ89" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,16 +8365,17 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>8</v>
+      <c r="E91" s="3">
+        <v>-21000</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>8</v>
@@ -8162,20 +8383,20 @@
       <c r="G91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3">
         <v>-11900</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -8228,8 +8449,8 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>8</v>
+      <c r="AD91" s="3">
+        <v>0</v>
       </c>
       <c r="AE91" s="3" t="s">
         <v>8</v>
@@ -8246,8 +8467,11 @@
       <c r="AI91" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ91" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,62 +8675,65 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3">
         <v>-129600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-417700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-134900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-434600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-265900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-309900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-473900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-518900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-236900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-411900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-374600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-337100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>10100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-487700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-323400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-63400</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>8</v>
       </c>
@@ -8516,8 +8746,8 @@
       <c r="X94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
+      <c r="Y94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z94" s="3">
         <v>0</v>
@@ -8531,8 +8761,8 @@
       <c r="AC94" s="3">
         <v>0</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>8</v>
+      <c r="AD94" s="3">
+        <v>0</v>
       </c>
       <c r="AE94" s="3" t="s">
         <v>8</v>
@@ -8549,8 +8779,11 @@
       <c r="AI94" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ94" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,16 +8819,17 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>8</v>
+      <c r="E96" s="3">
+        <v>173000</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>8</v>
@@ -8603,20 +8837,20 @@
       <c r="G96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3">
         <v>132800</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,62 +9233,65 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3">
         <v>-256700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-178000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-105600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>245900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-128600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>96300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>170500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>5700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>27300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>121700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>296000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>148700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>149600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>64700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>77300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>25700</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>8</v>
       </c>
@@ -9058,8 +9304,8 @@
       <c r="X100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
+      <c r="Y100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z100" s="3">
         <v>0</v>
@@ -9073,8 +9319,8 @@
       <c r="AC100" s="3">
         <v>0</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>8</v>
+      <c r="AD100" s="3">
+        <v>0</v>
       </c>
       <c r="AE100" s="3" t="s">
         <v>8</v>
@@ -9091,61 +9337,64 @@
       <c r="AI100" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ100" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-3300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="S101" s="3">
         <v>-200</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>8</v>
+      <c r="T101" s="3">
+        <v>-200</v>
       </c>
       <c r="U101" s="3" t="s">
         <v>8</v>
@@ -9159,8 +9408,8 @@
       <c r="X101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
+      <c r="Y101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z101" s="3">
         <v>0</v>
@@ -9174,8 +9423,8 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-      <c r="AD101" s="3" t="s">
-        <v>8</v>
+      <c r="AD101" s="3">
+        <v>0</v>
       </c>
       <c r="AE101" s="3" t="s">
         <v>8</v>
@@ -9192,62 +9441,65 @@
       <c r="AI101" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ101" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>36200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-261000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>29700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>82800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-63000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-42400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-59400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-257200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>39900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-69200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>273900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>7100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>292400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-170400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-60100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>206100</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>8</v>
       </c>
@@ -9260,8 +9512,8 @@
       <c r="X102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
+      <c r="Y102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z102" s="3">
         <v>0</v>
@@ -9275,8 +9527,8 @@
       <c r="AC102" s="3">
         <v>0</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>8</v>
+      <c r="AD102" s="3">
+        <v>0</v>
       </c>
       <c r="AE102" s="3" t="s">
         <v>8</v>
@@ -9291,6 +9543,9 @@
         <v>8</v>
       </c>
       <c r="AI102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/QFIN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QFIN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="92">
   <si>
     <t>QFIN</t>
   </si>
@@ -656,467 +656,480 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>728100</v>
+      </c>
+      <c r="E8" s="3">
         <v>646400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>614100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>623000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>572500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>575200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>634000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>586700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>539700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>524000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>550800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>572500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>581500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>596500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>609300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>655700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>574700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>501000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>464600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>545700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>492200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>502100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>369700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>403000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>347400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>306900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>444600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>89900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>62300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>86000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>64400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>52500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>246200</v>
+      </c>
+      <c r="E9" s="3">
         <v>234300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>208700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>199100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>248100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>254700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>237000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>191300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>190100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>201900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>82600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>85300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>77200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>84900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>81200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>89200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>80100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>66500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>61900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>60200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>58900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>54800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>27200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>58400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>47400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>34800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>32800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>24500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>32900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>14300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>8800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>11400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>481900</v>
+      </c>
+      <c r="E10" s="3">
         <v>412100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>405400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>423900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>324300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>320500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>396900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>395400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>349600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>322000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>468200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>487300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>504300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>511600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>528100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>566600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>494600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>434500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>402700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>485500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>433300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>447300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>342400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>344600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>300000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>272100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>411900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>65500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>29500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>71700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>55600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>41100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>-1100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,8 +1166,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1257,8 +1271,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,8 +1378,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1381,20 +1401,20 @@
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>4200</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1465,8 +1485,11 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1480,10 +1503,10 @@
         <v>2600</v>
       </c>
       <c r="G15" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H15" s="3">
         <v>2500</v>
-      </c>
-      <c r="H15" s="3">
-        <v>2600</v>
       </c>
       <c r="I15" s="3">
         <v>2600</v>
@@ -1492,14 +1515,14 @@
         <v>2600</v>
       </c>
       <c r="K15" s="3">
+        <v>2600</v>
+      </c>
+      <c r="L15" s="3">
         <v>2700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2800</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1530,8 +1553,8 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>8</v>
+      <c r="X15" s="3">
+        <v>0</v>
       </c>
       <c r="Y15" s="3" t="s">
         <v>8</v>
@@ -1548,29 +1571,32 @@
       <c r="AC15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AD15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE15" s="3">
         <v>100</v>
       </c>
-      <c r="AE15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG15" s="3">
-        <v>100</v>
+      <c r="AG15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH15" s="3">
         <v>100</v>
       </c>
-      <c r="AI15" s="3" t="s">
-        <v>8</v>
+      <c r="AI15" s="3">
+        <v>100</v>
       </c>
       <c r="AJ15" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK15" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1630,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>374400</v>
+      </c>
+      <c r="E17" s="3">
         <v>352300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>312400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>287600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>328700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>342400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>342900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>282400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>272400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>278300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>417700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>412500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>441000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>408800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>405100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>386500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>308600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>284200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>291800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>343700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>345800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>473100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>329300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>256000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>218000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>175600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>139100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>68400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>141500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>55400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>36100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>49600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>9900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>353700</v>
+      </c>
+      <c r="E18" s="3">
         <v>294100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>301600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>335400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>243800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>232800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>291100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>304300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>267400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>245600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>133100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>160000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>140500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>187700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>204100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>269200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>266100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>216800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>172800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>202100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>146400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>29100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>40400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>147000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>129400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>131300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>305500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>21500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-79200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>30600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>28400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-8200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-5600</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,145 +1883,149 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>60700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>47100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>8800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-35600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>28300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>110000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>108600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>82500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>94600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>11400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>20100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>4400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>8300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>4100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>14400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>6600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>15400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>12900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>7300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>6900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>13600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-5200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>8800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>800</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>400</v>
       </c>
       <c r="AF20" s="3">
         <v>400</v>
       </c>
       <c r="AG20" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AH20" s="3">
         <v>200</v>
       </c>
       <c r="AI20" s="3">
+        <v>200</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>295600</v>
+      </c>
+      <c r="E21" s="3">
         <v>299200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>257100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>329200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>282000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>207000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>183700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>198400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>187500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>153800</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2034,32 +2071,35 @@
       <c r="AB21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD21" s="3">
         <v>306600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>22700</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AH21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI21" s="3">
         <v>3200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-8000</v>
       </c>
-      <c r="AJ21" s="3" t="s">
+      <c r="AK21" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2090,8 +2130,8 @@
       <c r="L22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -2108,8 +2148,8 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>8</v>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>8</v>
@@ -2126,18 +2166,18 @@
       <c r="X22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Y22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z22" s="3">
         <v>2200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>4000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>800</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC22" s="3" t="s">
         <v>8</v>
       </c>
@@ -2150,8 +2190,8 @@
       <c r="AF22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG22" s="3">
-        <v>0</v>
+      <c r="AG22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH22" s="3">
         <v>0</v>
@@ -2162,216 +2202,225 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>303200</v>
+      </c>
+      <c r="E23" s="3">
         <v>306000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>264800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>336000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>285800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>211400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>187700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>202600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>188400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>160400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>144500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>161900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>160600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>192000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>212400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>273300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>280500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>223500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>188200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>215000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>153700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>36000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>51800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>143900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>123400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>140100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>306100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>22300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-78800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>31000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>28500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>3100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-8000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-5600</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>61600</v>
+      </c>
+      <c r="E24" s="3">
         <v>58400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>79600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>96300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>50700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>31500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>46700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>37600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>25100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>22100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>25300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>25100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>29900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>32500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>51000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>58200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>35900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>20500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>33500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>24500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>7100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-14300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>29500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>27000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>30100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>64600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>7900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-4600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>7500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>6400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-2100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2523,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>241600</v>
+      </c>
+      <c r="E26" s="3">
         <v>247600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>262000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>256400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>189400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>160700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>156200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>155900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>150800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>135400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>122400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>136600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>135500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>162200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>179800</v>
-      </c>
-      <c r="R26" s="3">
-        <v>222300</v>
       </c>
       <c r="S26" s="3">
         <v>222300</v>
       </c>
       <c r="T26" s="3">
+        <v>222300</v>
+      </c>
+      <c r="U26" s="3">
         <v>187500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>167600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>181500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>129200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>28900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>66200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>114400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>96400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>110000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>241500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>14400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-74200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>23500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>22100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-5900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>242000</v>
+      </c>
+      <c r="E27" s="3">
         <v>248100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>262600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>257000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>190000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>161200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>156800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>156500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>151300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>136000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>122900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>137200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>136200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>162900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>182200</v>
-      </c>
-      <c r="R27" s="3">
-        <v>222300</v>
       </c>
       <c r="S27" s="3">
         <v>222300</v>
       </c>
       <c r="T27" s="3">
+        <v>222300</v>
+      </c>
+      <c r="U27" s="3">
         <v>187600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>167700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>181500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>129200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>28900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>66200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>114400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>96400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>110000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>241500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-419200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-74200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>23500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>22100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>2400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-5900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2844,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2890,8 +2951,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3058,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,216 +3165,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-60700</v>
+      </c>
+      <c r="E32" s="3">
         <v>2500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-47100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-8800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>35600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-28300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-110000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-108600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-82500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-94600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-11400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-20100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-8300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-4100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-14400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-6600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-15400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-12900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-7300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-13600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>5200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-8800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-800</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>-400</v>
       </c>
       <c r="AF32" s="3">
         <v>-400</v>
       </c>
       <c r="AG32" s="3">
-        <v>-200</v>
+        <v>-400</v>
       </c>
       <c r="AH32" s="3">
         <v>-200</v>
       </c>
       <c r="AI32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>242000</v>
+      </c>
+      <c r="E33" s="3">
         <v>248100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>262600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>257000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>190000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>161200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>156800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>156500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>151300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>136000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>122900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>137200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>136200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>162900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>182200</v>
-      </c>
-      <c r="R33" s="3">
-        <v>222300</v>
       </c>
       <c r="S33" s="3">
         <v>222300</v>
       </c>
       <c r="T33" s="3">
+        <v>222300</v>
+      </c>
+      <c r="U33" s="3">
         <v>187600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>167700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>181500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>129200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>28900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>66200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>114400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>96400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>110000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>241500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-419200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-74200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>23500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>22100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>2400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-5900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3486,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>242000</v>
+      </c>
+      <c r="E35" s="3">
         <v>248100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>262600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>257000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>190000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>161200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>156800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>156500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>151300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>136000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>122900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>137200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>136200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>162900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>182200</v>
-      </c>
-      <c r="R35" s="3">
-        <v>222300</v>
       </c>
       <c r="S35" s="3">
         <v>222300</v>
       </c>
       <c r="T35" s="3">
+        <v>222300</v>
+      </c>
+      <c r="U35" s="3">
         <v>187600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>167700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>181500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>129200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>28900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>66200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>114400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>96400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>110000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>241500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-419200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-74200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>23500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>22100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>2400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-5900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3746,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,98 +3785,99 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>738100</v>
+      </c>
+      <c r="E41" s="3">
         <v>1182200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>610000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>611400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>872100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>734200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>589200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>676800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>724800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>746600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1010200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>997500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>968300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>852800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>842700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>600500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>745700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>831600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>615000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>710400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>563400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>570500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>324600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>287700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>285100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>195700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>210000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>281100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>65600</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3803,47 +3890,50 @@
       <c r="AJ41" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK41" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>684600</v>
+      </c>
+      <c r="E42" s="3">
         <v>281200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>465000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>444800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>40100</v>
-      </c>
-      <c r="H42" s="3">
-        <v>2100</v>
       </c>
       <c r="I42" s="3">
         <v>2100</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>34100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>34400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>8000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>4100</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>8</v>
       </c>
@@ -3856,8 +3946,8 @@
       <c r="S42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -3907,98 +3997,101 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5199600</v>
+      </c>
+      <c r="E43" s="3">
         <v>4547000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3964500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4065500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3970900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4136000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3886500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3615300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3368100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3146800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3207600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3030500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2643400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2653400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2444000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2516000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2232800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1947600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1918900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2034700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2097200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2153800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2168400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2094600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1663200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1050200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>642500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>177700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>272300</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG43" s="3" t="s">
         <v>8</v>
       </c>
@@ -4011,8 +4104,11 @@
       <c r="AJ43" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK43" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4043,8 +4139,8 @@
       <c r="L44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4115,98 +4211,101 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>308100</v>
+      </c>
+      <c r="E45" s="3">
         <v>282600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>298500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>326700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>469600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>453600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>611100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>626700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>570900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>589900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>581200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>565600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>671200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>555600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>537700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>521500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>563400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>511100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>511200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>517600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>606800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>597700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>510200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>498200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>427100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>354900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>213900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>156100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>102600</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4219,98 +4318,101 @@
       <c r="AJ45" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK45" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7556700</v>
+      </c>
+      <c r="E46" s="3">
         <v>6947300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5861100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5938900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5699200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5791300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5612300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5483300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5178700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5097900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4807100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4597700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4282900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4061900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3824400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3638000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3541900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3290300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3045100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3262700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3267400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3322000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3003100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2880600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2375500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1600800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1066300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>615000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>440500</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG46" s="3" t="s">
         <v>8</v>
       </c>
@@ -4323,8 +4425,11 @@
       <c r="AJ46" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK46" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4355,54 +4460,54 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N47" s="3">
         <v>580900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>610100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>651700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>607100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>526500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>579600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>358000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>201600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>144900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>127700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>99300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>55100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>12100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>4700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>100</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC47" s="3" t="s">
         <v>8</v>
       </c>
@@ -4415,8 +4520,8 @@
       <c r="AF47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG47" s="3">
-        <v>0</v>
+      <c r="AG47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH47" s="3">
         <v>0</v>
@@ -4427,85 +4532,88 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>69400</v>
+      </c>
+      <c r="E48" s="3">
         <v>55900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>54600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>47200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>41200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>35600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>39000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>20300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>11100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>14600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>12400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>13400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>13100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>8200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>9500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>11100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>12200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>11600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>11200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2200</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>1000</v>
       </c>
       <c r="AC48" s="3">
         <v>1000</v>
@@ -4516,8 +4624,8 @@
       <c r="AE48" s="3">
         <v>1000</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>8</v>
+      <c r="AF48" s="3">
+        <v>1000</v>
       </c>
       <c r="AG48" s="3" t="s">
         <v>8</v>
@@ -4531,40 +4639,43 @@
       <c r="AJ48" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK48" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>138500</v>
+        <v>139600</v>
       </c>
       <c r="E49" s="3">
         <v>138500</v>
       </c>
       <c r="F49" s="3">
+        <v>138500</v>
+      </c>
+      <c r="G49" s="3">
         <v>144900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>140400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>142100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>145600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>142200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>136900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>145300</v>
-      </c>
-      <c r="M49" s="3">
-        <v>700</v>
       </c>
       <c r="N49" s="3">
         <v>700</v>
@@ -4573,19 +4684,19 @@
         <v>700</v>
       </c>
       <c r="P49" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q49" s="3">
         <v>800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>141100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>700</v>
-      </c>
-      <c r="T49" s="3">
-        <v>500</v>
       </c>
       <c r="U49" s="3">
         <v>500</v>
@@ -4594,22 +4705,22 @@
         <v>500</v>
       </c>
       <c r="W49" s="3">
+        <v>500</v>
+      </c>
+      <c r="X49" s="3">
         <v>400</v>
-      </c>
-      <c r="X49" s="3">
-        <v>500</v>
       </c>
       <c r="Y49" s="3">
         <v>500</v>
       </c>
       <c r="Z49" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA49" s="3">
         <v>600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>300</v>
-      </c>
-      <c r="AB49" s="3">
-        <v>100</v>
       </c>
       <c r="AC49" s="3">
         <v>100</v>
@@ -4620,8 +4731,8 @@
       <c r="AE49" s="3">
         <v>100</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>8</v>
+      <c r="AF49" s="3">
+        <v>100</v>
       </c>
       <c r="AG49" s="3" t="s">
         <v>8</v>
@@ -4635,8 +4746,11 @@
       <c r="AJ49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4853,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,98 +4960,101 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>43400</v>
+      </c>
+      <c r="E52" s="3">
         <v>30800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>23500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>34100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>39200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>62000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>84200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>85400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>80200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>95800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>284400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>300400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>287600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>267100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>115000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>164800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>147500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>207100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>194700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>169500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>154500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>212000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>107400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>25500</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC52" s="3">
-        <v>0</v>
+      <c r="AC52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="3">
         <v>86800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>67400</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4947,8 +5067,11 @@
       <c r="AJ52" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK52" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,98 +5174,101 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8341200</v>
+      </c>
+      <c r="E54" s="3">
         <v>7665800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6594300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6698800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6465300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6568300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6461600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6309700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5984600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5951100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5687600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5521200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5236300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4950100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4616300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4390300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4056700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3707600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3394700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3571600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3533800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3601200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3134400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2913900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2378000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1601900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1067400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>702900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>509000</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG54" s="3" t="s">
         <v>8</v>
       </c>
@@ -5155,8 +5281,11 @@
       <c r="AJ54" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK54" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5322,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,8 +5361,9 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5263,8 +5394,8 @@
       <c r="L57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
+      <c r="M57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N57" s="3">
         <v>0</v>
@@ -5335,86 +5466,89 @@
       <c r="AJ57" s="3">
         <v>0</v>
       </c>
+      <c r="AK57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>204300</v>
+      </c>
+      <c r="E58" s="3">
         <v>168000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>191400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>148700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>145700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>94700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>116700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>103600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>35900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>21800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>21100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>88400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>85000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>81000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>54800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>47700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>48300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>32300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>26000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>27200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>27700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>68600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>30800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>239500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>223900</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC58" s="3" t="s">
         <v>8</v>
       </c>
@@ -5427,8 +5561,8 @@
       <c r="AF58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG58" s="3">
-        <v>0</v>
+      <c r="AG58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH58" s="3">
         <v>0</v>
@@ -5439,98 +5573,101 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1570300</v>
+      </c>
+      <c r="E59" s="3">
         <v>1628400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2015200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1774000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1868000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2271200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2499600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2115500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1934000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2344000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2340300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2390600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2253800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1939500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1893900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1870500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1877300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1841500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1837100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1863800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1930800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2084600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1457800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1280000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1109500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>754700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>420300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>413100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>452200</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG59" s="3" t="s">
         <v>8</v>
       </c>
@@ -5543,98 +5680,101 @@
       <c r="AJ59" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK59" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2173200</v>
+      </c>
+      <c r="E60" s="3">
         <v>2256900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2393700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2318000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2323400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2737400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2806400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2603400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2231900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2646100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2361400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2479000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2338800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2020400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1948600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1918300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1925600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1873800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1863100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1891000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1958600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2153300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1488600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1519500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1333300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>754700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>420300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>413100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>452200</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG60" s="3" t="s">
         <v>8</v>
       </c>
@@ -5647,41 +5787,44 @@
       <c r="AJ60" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK60" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>677000</v>
+        <v>751600</v>
       </c>
       <c r="E61" s="3">
+        <v>718000</v>
+      </c>
+      <c r="F61" s="3">
         <v>35000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>33100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>23500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>23700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>14500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>13500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6700</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -5751,92 +5894,95 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1467900</v>
+        <v>1969100</v>
       </c>
       <c r="E62" s="3">
+        <v>1426900</v>
+      </c>
+      <c r="F62" s="3">
         <v>783600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1011300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>941500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>713900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>505100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>780900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>847500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>409700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>657200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>556800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>531300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>695500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>571100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>465300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>337600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>317300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>211800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>467700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>542400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>490300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>534900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>342300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>121400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>54400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2300</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5855,8 +6001,11 @@
       <c r="AJ62" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK62" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6108,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6215,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,98 +6322,101 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4976100</v>
+      </c>
+      <c r="E66" s="3">
         <v>4480300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3272500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3434200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3350800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3501900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3357600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3413800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3104700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3079300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3030500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3048000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2870500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2717000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2521500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2383600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2263300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2191200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2075000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2358900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2501200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2643700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2023600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1862000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1454700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>809100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>422600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>413100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>452200</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG66" s="3" t="s">
         <v>8</v>
       </c>
@@ -6271,8 +6429,11 @@
       <c r="AJ66" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK66" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6470,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6575,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6682,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6601,11 +6769,11 @@
         <v>0</v>
       </c>
       <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
         <v>628600</v>
       </c>
-      <c r="AE70" s="3">
-        <v>0</v>
-      </c>
       <c r="AF70" s="3">
         <v>0</v>
       </c>
@@ -6621,8 +6789,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,98 +6896,101 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E72" s="3">
+      <c r="E72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F72" s="3">
         <v>2870500</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J72" s="3">
         <v>2298300</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N72" s="3">
         <v>1805100</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R72" s="3">
         <v>1328500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1222000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1010000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>763500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>575900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>432200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>250600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>130000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>318900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>256100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>141600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>44300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-62500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-339400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-109100</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG72" s="3" t="s">
         <v>8</v>
       </c>
@@ -6829,8 +7003,11 @@
       <c r="AJ72" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK72" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7110,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7217,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,98 +7324,101 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3358300</v>
+      </c>
+      <c r="E76" s="3">
         <v>3178300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3314100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3256000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3105700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3057000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3093800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2885300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2869400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2860200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2657100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2473200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2365900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2233100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2094800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2006700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1793300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1516400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1319700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1212800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1032600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>957400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1110700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1051900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>923300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>792800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>644800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-338900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>56800</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG76" s="3" t="s">
         <v>8</v>
       </c>
@@ -7245,8 +7431,11 @@
       <c r="AJ76" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK76" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7538,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>242000</v>
+      </c>
+      <c r="E81" s="3">
         <v>248100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>262600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>257000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>190000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>161200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>156800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>156500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>151300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>136000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>122900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>137200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>136200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>162900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>182200</v>
-      </c>
-      <c r="R81" s="3">
-        <v>222300</v>
       </c>
       <c r="S81" s="3">
         <v>222300</v>
       </c>
       <c r="T81" s="3">
+        <v>222300</v>
+      </c>
+      <c r="U81" s="3">
         <v>187600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>167700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>181500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>129200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>28900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>66200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>114400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>96400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>110000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>241500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-419200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-74200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>23500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>22100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>2400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-5900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,40 +7798,41 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E83" s="3">
+      <c r="E83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F83" s="3">
         <v>7500</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G83" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J83" s="3">
         <v>8200</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="K83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L83" s="3">
         <v>5900</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -7686,8 +7885,8 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>8</v>
+      <c r="AE83" s="3">
+        <v>0</v>
       </c>
       <c r="AF83" s="3" t="s">
         <v>8</v>
@@ -7704,8 +7903,11 @@
       <c r="AJ83" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK83" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8010,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8117,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8224,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8331,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,65 +8438,68 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>8</v>
+      <c r="D89" s="3">
+        <v>366000</v>
       </c>
       <c r="E89" s="3">
+        <v>386600</v>
+      </c>
+      <c r="F89" s="3">
         <v>418100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>338100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>269900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>271200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>331700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>170500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>242900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>256400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>252700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>220000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>352800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>196000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>132800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>252600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>186200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>244000</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>8</v>
       </c>
@@ -8295,8 +8512,8 @@
       <c r="Y89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z89" s="3">
-        <v>0</v>
+      <c r="Z89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA89" s="3">
         <v>0</v>
@@ -8310,8 +8527,8 @@
       <c r="AD89" s="3">
         <v>0</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>8</v>
+      <c r="AE89" s="3">
+        <v>0</v>
       </c>
       <c r="AF89" s="3" t="s">
         <v>8</v>
@@ -8328,8 +8545,11 @@
       <c r="AJ89" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK89" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,40 +8586,41 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E91" s="3">
+      <c r="E91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="3">
         <v>-21000</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I91" s="3">
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3">
         <v>-11900</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -8452,8 +8673,8 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>8</v>
+      <c r="AE91" s="3">
+        <v>0</v>
       </c>
       <c r="AF91" s="3" t="s">
         <v>8</v>
@@ -8470,8 +8691,11 @@
       <c r="AJ91" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK91" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8798,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,65 +8905,68 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>8</v>
+      <c r="D94" s="3">
+        <v>-1143400</v>
       </c>
       <c r="E94" s="3">
+        <v>-446500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-129600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-417700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-134900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-434600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-265900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-309900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-473900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-518900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-236900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-411900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-374600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-337100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>10100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-487700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-323400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-63400</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>8</v>
       </c>
@@ -8749,8 +8979,8 @@
       <c r="Y94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
+      <c r="Z94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA94" s="3">
         <v>0</v>
@@ -8764,8 +8994,8 @@
       <c r="AD94" s="3">
         <v>0</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>8</v>
+      <c r="AE94" s="3">
+        <v>0</v>
       </c>
       <c r="AF94" s="3" t="s">
         <v>8</v>
@@ -8782,8 +9012,11 @@
       <c r="AJ94" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK94" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,40 +9053,41 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E96" s="3">
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3">
         <v>173000</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G96" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I96" s="3">
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3">
         <v>132800</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -8924,8 +9158,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9265,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9372,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,65 +9479,68 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>8</v>
+      <c r="D100" s="3">
+        <v>278600</v>
       </c>
       <c r="E100" s="3">
+        <v>750900</v>
+      </c>
+      <c r="F100" s="3">
         <v>-256700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-178000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-105600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>245900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-128600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>96300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>170500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>5700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>27300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>121700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>296000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>148700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>149600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>64700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>77300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>25700</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>8</v>
       </c>
@@ -9307,8 +9553,8 @@
       <c r="Y100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
+      <c r="Z100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA100" s="3">
         <v>0</v>
@@ -9322,8 +9568,8 @@
       <c r="AD100" s="3">
         <v>0</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>8</v>
+      <c r="AE100" s="3">
+        <v>0</v>
       </c>
       <c r="AF100" s="3" t="s">
         <v>8</v>
@@ -9340,8 +9586,11 @@
       <c r="AJ100" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK100" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9349,55 +9598,55 @@
         <v>300</v>
       </c>
       <c r="E101" s="3">
+        <v>300</v>
+      </c>
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-3300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-3200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="T101" s="3">
         <v>-200</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>8</v>
+      <c r="U101" s="3">
+        <v>-200</v>
       </c>
       <c r="V101" s="3" t="s">
         <v>8</v>
@@ -9411,8 +9660,8 @@
       <c r="Y101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
+      <c r="Z101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA101" s="3">
         <v>0</v>
@@ -9426,8 +9675,8 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-      <c r="AE101" s="3" t="s">
-        <v>8</v>
+      <c r="AE101" s="3">
+        <v>0</v>
       </c>
       <c r="AF101" s="3" t="s">
         <v>8</v>
@@ -9444,65 +9693,68 @@
       <c r="AJ101" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK101" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-502900</v>
       </c>
       <c r="E102" s="3">
+        <v>690300</v>
+      </c>
+      <c r="F102" s="3">
         <v>36200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-261000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>29700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>82800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-63000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-42400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-59400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-257200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>39900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-69200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>273900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>7100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>292400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-170400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-60100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>206100</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>8</v>
       </c>
@@ -9515,8 +9767,8 @@
       <c r="Y102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z102" s="3">
-        <v>0</v>
+      <c r="Z102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA102" s="3">
         <v>0</v>
@@ -9530,8 +9782,8 @@
       <c r="AD102" s="3">
         <v>0</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>8</v>
+      <c r="AE102" s="3">
+        <v>0</v>
       </c>
       <c r="AF102" s="3" t="s">
         <v>8</v>
@@ -9546,6 +9798,9 @@
         <v>8</v>
       </c>
       <c r="AJ102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/QFIN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QFIN_QTR_FIN.xlsx
@@ -5939,7 +5939,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>679100</v>
+        <v>763000</v>
       </c>
       <c r="E61" s="3">
         <v>751600</v>
@@ -6049,7 +6049,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1776400</v>
+        <v>1692600</v>
       </c>
       <c r="E62" s="3">
         <v>1969100</v>

--- a/AAII_Financials/Quarterly/QFIN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QFIN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="92">
   <si>
     <t>QFIN</t>
   </si>
@@ -656,493 +656,518 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AN102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>566800</v>
+      </c>
+      <c r="E8" s="3">
+        <v>585100</v>
+      </c>
+      <c r="F8" s="3">
         <v>731200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>728100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>646400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>614100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>623000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>572500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>575200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>634000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>586700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>539700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>524000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>550800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>572500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>581500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>596500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>609300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>655700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>574700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>501000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>464600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>545700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>492200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>502100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>369700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>403000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>347400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>306900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>444600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>89900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>62300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>86000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>64400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>52500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>1800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>319100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>303700</v>
+      </c>
+      <c r="F9" s="3">
         <v>256100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>246200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>234300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>208700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>199100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>248100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>254700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>237000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>191300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>190100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>201900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>82600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>85300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>77200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>84900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>81200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>89200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>80100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>66500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>61900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>60200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>58900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>54800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>27200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>58400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>47400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>34800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>32800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>24500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>32900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>14300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>8800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>11400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>2900</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>247700</v>
+      </c>
+      <c r="E10" s="3">
+        <v>281500</v>
+      </c>
+      <c r="F10" s="3">
         <v>475100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>481900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>412100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>405400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>423900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>324300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>320500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>396900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>395400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>349600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>322000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>468200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>487300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>504300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>511600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>528100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>566600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>494600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>434500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>402700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>485500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>433300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>447300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>342400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>344600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>300000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>272100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>411900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>65500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>29500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>71700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>55600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>41100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>-1100</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1181,8 +1206,10 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1291,8 +1318,14 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1401,16 +1434,22 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-38600</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
@@ -1427,23 +1466,23 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
         <v>4200</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1511,16 +1550,22 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2600</v>
+        <v>2500</v>
       </c>
       <c r="E15" s="3">
-        <v>2600</v>
+        <v>2400</v>
       </c>
       <c r="F15" s="3">
         <v>2600</v>
@@ -1532,29 +1577,29 @@
         <v>2600</v>
       </c>
       <c r="I15" s="3">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="J15" s="3">
         <v>2600</v>
       </c>
       <c r="K15" s="3">
-        <v>2600</v>
+        <v>2500</v>
       </c>
       <c r="L15" s="3">
         <v>2600</v>
       </c>
       <c r="M15" s="3">
+        <v>2600</v>
+      </c>
+      <c r="N15" s="3">
+        <v>2600</v>
+      </c>
+      <c r="O15" s="3">
         <v>2700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>2800</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1582,11 +1627,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA15" s="3" t="s">
-        <v>8</v>
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>0</v>
       </c>
       <c r="AB15" s="3" t="s">
         <v>8</v>
@@ -1600,29 +1645,35 @@
       <c r="AE15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AF15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH15" s="3">
         <v>100</v>
       </c>
-      <c r="AG15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI15" s="3">
+      <c r="AI15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK15" s="3">
         <v>100</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AL15" s="3">
         <v>100</v>
       </c>
-      <c r="AK15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AL15" s="3" t="s">
+      <c r="AM15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN15" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1658,228 +1709,242 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>411200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>412800</v>
+      </c>
+      <c r="F17" s="3">
         <v>383800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>374400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>352300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>312400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>287600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>328700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>342400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>342900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>282400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>272400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>278300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>417700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>412500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>441000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>408800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>405100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>386500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>308600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>284200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>291800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>343700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>345800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>473100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>329300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>256000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>218000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>175600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>139100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>68400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>141500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>55400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>36100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>49600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>9900</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>155600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>172300</v>
+      </c>
+      <c r="F18" s="3">
         <v>347400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>353700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>294100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>301600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>335400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>243800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>232800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>291100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>304300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>267400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>245600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>133100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>160000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>140500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>187700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>204100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>269200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>266100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>216800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>172800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>202100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>146400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>29100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>40400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>147000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>129400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>131300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>305500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>21500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-79200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>30600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>28400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>2900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>-8200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>-5600</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1918,160 +1983,168 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E20" s="3">
+        <v>54000</v>
+      </c>
+      <c r="F20" s="3">
         <v>101800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>60700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-2500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>47100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>8800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-35600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>28300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>110000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>108600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>82500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>94600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>11400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>1800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>20100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>4400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>8300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>4100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>14400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>6600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>15400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>12900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>7300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>6900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>13600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>8800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>100</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>146200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>120700</v>
+      </c>
+      <c r="F21" s="3">
         <v>248300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>295600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>299200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>257100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>329200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>282000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>207000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>183700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>198400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>187500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>153800</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2114,32 +2187,38 @@
       <c r="AD21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG21" s="3">
         <v>306600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>22700</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AJ21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL21" s="3">
         <v>3200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>-8000</v>
       </c>
-      <c r="AL21" s="3" t="s">
+      <c r="AN21" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2176,11 +2255,11 @@
       <c r="N22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -2194,11 +2273,11 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V22" s="3" t="s">
-        <v>8</v>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
+        <v>0</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>8</v>
@@ -2212,21 +2291,21 @@
       <c r="Z22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AA22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC22" s="3">
         <v>2200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>4000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>800</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF22" s="3" t="s">
         <v>8</v>
       </c>
@@ -2236,11 +2315,11 @@
       <c r="AH22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ22" s="3">
-        <v>0</v>
+      <c r="AI22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK22" s="3">
         <v>0</v>
@@ -2248,228 +2327,246 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>165400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>164800</v>
+      </c>
+      <c r="F23" s="3">
         <v>257200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>303200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>306000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>264800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>336000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>285800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>211400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>187700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>202600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>188400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>160400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>144500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>161900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>160600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>192000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>212400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>273300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>280500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>223500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>188200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>215000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>153700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>36000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>51800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>143900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>123400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>140100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>306100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>22300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>-78800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>31000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>28500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>3100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>-8000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>-5600</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>37800</v>
+      </c>
+      <c r="E24" s="3">
+        <v>19500</v>
+      </c>
+      <c r="F24" s="3">
         <v>56000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>61600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>58400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>2700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>79600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>96300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>50700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>31500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>46700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>37600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>25100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>22100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>25300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>25100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>29900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>32500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>51000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>58200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>35900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>20500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>33500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>24500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>7100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-14300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>29500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>27000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>30100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>64600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>7900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>-4600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>7500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>6400</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>-2100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2578,228 +2675,246 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>127600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>145300</v>
+      </c>
+      <c r="F26" s="3">
         <v>201200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>241600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>247600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>262000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>256400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>189400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>160700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>156200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>155900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>150800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>135400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>122400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>136600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>135500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>162200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>179800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>222300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>222300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>187500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>167600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>181500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>129200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>28900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>66200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>114400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>96400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>110000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>241500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>14400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>-74200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>23500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>22100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>2400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>-5900</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>128100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>145800</v>
+      </c>
+      <c r="F27" s="3">
         <v>201700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>242000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>248100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>262600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>257000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>190000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>161200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>156800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>156500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>151300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>136000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>122900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>137200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>136200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>162900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>182200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>222300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>222300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>187600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>167700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>181500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>129200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>28900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>66200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>114400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>96400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>110000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>241500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-419200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>-74200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>23500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>22100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>2400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>-5900</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2908,8 +3023,14 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3018,8 +3139,14 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3128,8 +3255,14 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3238,228 +3371,246 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-54000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-101800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-60700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>2500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-47100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-8800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>35600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-28300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-110000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-108600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-82500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-94600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-11400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-20100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-4400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-8300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-4100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-14400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-6600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-15400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-12900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-7300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-6900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-13600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>5200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-8800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>-200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>-100</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>128100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>145800</v>
+      </c>
+      <c r="F33" s="3">
         <v>201700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>242000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>248100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>262600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>257000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>190000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>161200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>156800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>156500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>151300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>136000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>122900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>137200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>136200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>162900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>182200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>222300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>222300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>187600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>167700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>181500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>129200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>28900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>66200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>114400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>96400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>110000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>241500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-419200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>-74200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>23500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>22100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>2400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>-5900</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3568,233 +3719,251 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>128100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>145800</v>
+      </c>
+      <c r="F35" s="3">
         <v>201700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>242000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>248100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>262600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>257000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>190000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>161200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>156800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>156500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>151300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>136000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>122900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>137200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>136200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>162900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>182200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>222300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>222300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>187600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>167700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>181500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>129200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>28900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>66200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>114400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>96400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>110000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>241500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-419200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>-74200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>23500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>22100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>2400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>-5900</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3833,8 +4002,10 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3873,107 +4044,109 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>821800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>671500</v>
+      </c>
+      <c r="F41" s="3">
         <v>916300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>738100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1182200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>610000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>611400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>872100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>734200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>589200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>676800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>724800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>746600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1010200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>997500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>968300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>852800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>842700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>600500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>745700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>831600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>615000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>710400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>563400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>570500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>324600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>287700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>285100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>195700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>210000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>281100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>65600</v>
       </c>
-      <c r="AH41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3983,56 +4156,62 @@
       <c r="AL41" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN41" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>127500</v>
+      </c>
+      <c r="E42" s="3">
+        <v>407800</v>
+      </c>
+      <c r="F42" s="3">
         <v>617900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>684600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>281200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>465000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>444800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>40100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>2100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>2100</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>34100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>34400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>8000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>4100</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>8</v>
       </c>
@@ -4042,11 +4221,11 @@
       <c r="U42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
-      </c>
-      <c r="W42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X42" s="3">
         <v>0</v>
@@ -4093,107 +4272,113 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4570100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>5094200</v>
+      </c>
+      <c r="F43" s="3">
         <v>5217800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>5199600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>4547000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>3964500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>4065500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>3970900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>4136000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>3886500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>3615300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>3368100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>3146800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>3207600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>3030500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>2643400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>2653400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>2444000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>2516000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>2232800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>1947600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>1918900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>2034700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>2097200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>2153800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>2168400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>2094600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>1663200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>1050200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>642500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>177700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>272300</v>
       </c>
-      <c r="AH43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ43" s="3" t="s">
         <v>8</v>
       </c>
@@ -4203,8 +4388,14 @@
       <c r="AL43" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN43" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4241,11 +4432,11 @@
       <c r="N44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4313,107 +4504,113 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>223800</v>
+      </c>
+      <c r="E45" s="3">
+        <v>383700</v>
+      </c>
+      <c r="F45" s="3">
         <v>380200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>308100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>282600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>298500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>326700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>469600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>453600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>611100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>626700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>570900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>589900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>581200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>565600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>671200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>555600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>537700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>521500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>563400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>511100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>511200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>517600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>606800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>597700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>510200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>498200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>427100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>354900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>213900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>156100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>102600</v>
       </c>
-      <c r="AH45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4423,107 +4620,113 @@
       <c r="AL45" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN45" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6498000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>7074400</v>
+      </c>
+      <c r="F46" s="3">
         <v>7802400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>7556700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>6947300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>5861100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>5938900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>5699200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>5791300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>5612300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>5483300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>5178700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>5097900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>4807100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>4597700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>4282900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>4061900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>3824400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>3638000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>3541900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>3290300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>3045100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>3262700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>3267400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>3322000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>3003100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>2880600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>2375500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>1600800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>1066300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>615000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>440500</v>
       </c>
-      <c r="AH46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ46" s="3" t="s">
         <v>8</v>
       </c>
@@ -4533,8 +4736,14 @@
       <c r="AL46" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN46" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4571,57 +4780,57 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q47" s="3">
         <v>580900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>610100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>651700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>607100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>526500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>579600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>358000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>201600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>144900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>127700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>99300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>55100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>12100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>4700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>100</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF47" s="3" t="s">
         <v>8</v>
       </c>
@@ -4631,11 +4840,11 @@
       <c r="AH47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ47" s="3">
-        <v>0</v>
+      <c r="AI47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK47" s="3">
         <v>0</v>
@@ -4643,94 +4852,100 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>93900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>96200</v>
+      </c>
+      <c r="F48" s="3">
         <v>80900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>69400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>55900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>54600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>47200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>41200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>35600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>39000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>20300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>14700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>11100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>14600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>12400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>13400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>13100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>9300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>7400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>8600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>8200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>9500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>11100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>12200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>11600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>11200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>2600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>2200</v>
-      </c>
-      <c r="AD48" s="3">
-        <v>1000</v>
-      </c>
-      <c r="AE48" s="3">
-        <v>1000</v>
       </c>
       <c r="AF48" s="3">
         <v>1000</v>
@@ -4738,11 +4953,11 @@
       <c r="AG48" s="3">
         <v>1000</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI48" s="3" t="s">
-        <v>8</v>
+      <c r="AH48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AI48" s="3">
+        <v>1000</v>
       </c>
       <c r="AJ48" s="3" t="s">
         <v>8</v>
@@ -4753,94 +4968,100 @@
       <c r="AL48" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN48" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>147400</v>
+      </c>
+      <c r="E49" s="3">
+        <v>146200</v>
+      </c>
+      <c r="F49" s="3">
         <v>144300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>139600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>138500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>138500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>144900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>140400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>142100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>145600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>142200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>136900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>145300</v>
-      </c>
-      <c r="O49" s="3">
-        <v>700</v>
-      </c>
-      <c r="P49" s="3">
-        <v>700</v>
       </c>
       <c r="Q49" s="3">
         <v>700</v>
       </c>
       <c r="R49" s="3">
+        <v>700</v>
+      </c>
+      <c r="S49" s="3">
+        <v>700</v>
+      </c>
+      <c r="T49" s="3">
         <v>800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>141100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>700</v>
-      </c>
-      <c r="V49" s="3">
-        <v>500</v>
-      </c>
-      <c r="W49" s="3">
-        <v>500</v>
       </c>
       <c r="X49" s="3">
         <v>500</v>
       </c>
       <c r="Y49" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="Z49" s="3">
         <v>500</v>
       </c>
       <c r="AA49" s="3">
+        <v>400</v>
+      </c>
+      <c r="AB49" s="3">
         <v>500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD49" s="3">
         <v>600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>300</v>
-      </c>
-      <c r="AD49" s="3">
-        <v>100</v>
-      </c>
-      <c r="AE49" s="3">
-        <v>100</v>
       </c>
       <c r="AF49" s="3">
         <v>100</v>
@@ -4848,11 +5069,11 @@
       <c r="AG49" s="3">
         <v>100</v>
       </c>
-      <c r="AH49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI49" s="3" t="s">
-        <v>8</v>
+      <c r="AH49" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI49" s="3">
+        <v>100</v>
       </c>
       <c r="AJ49" s="3" t="s">
         <v>8</v>
@@ -4863,8 +5084,14 @@
       <c r="AL49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4973,8 +5200,14 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5083,107 +5316,113 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>58200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>52800</v>
+      </c>
+      <c r="F52" s="3">
         <v>57900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>43400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>30800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>23500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>34100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>39200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>62000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>84200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>85400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>80200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>95800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>284400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>300400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>287600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>267100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>115000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>164800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>147500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>207100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>194700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>169500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>154500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>212000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>107400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>25500</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF52" s="3">
+      <c r="AE52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="3">
         <v>86800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>67400</v>
       </c>
-      <c r="AH52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ52" s="3" t="s">
         <v>8</v>
       </c>
@@ -5193,8 +5432,14 @@
       <c r="AL52" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN52" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5303,107 +5548,113 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7847900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>8142200</v>
+      </c>
+      <c r="F54" s="3">
         <v>8631500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>8341200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>7665800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>6594300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>6698800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>6465300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>6568300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>6461600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>6309700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>5984600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>5951100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>5687600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>5521200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>5236300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>4950100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>4616300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>4390300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>4056700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>3707600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>3394700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>3571600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>3533800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>3601200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>3134400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>2913900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>2378000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>1601900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>1067400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>702900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>509000</v>
       </c>
-      <c r="AH54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ54" s="3" t="s">
         <v>8</v>
       </c>
@@ -5413,8 +5664,14 @@
       <c r="AL54" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN54" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5453,8 +5710,10 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5493,8 +5752,10 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5531,11 +5792,11 @@
       <c r="N57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
-      <c r="P57" s="3">
-        <v>0</v>
+      <c r="O57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q57" s="3">
         <v>0</v>
@@ -5603,95 +5864,101 @@
       <c r="AL57" s="3">
         <v>0</v>
       </c>
+      <c r="AM57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>205400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>320300</v>
+      </c>
+      <c r="F58" s="3">
         <v>209500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>204300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>168000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>191400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>148700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>145700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>94700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>116700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>103600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>35900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>21800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>21100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>88400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>85000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>81000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>54800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>47700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>48300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>32300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>26000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>27200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>27700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>68600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>30800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>239500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>223900</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF58" s="3" t="s">
         <v>8</v>
       </c>
@@ -5701,11 +5968,11 @@
       <c r="AH58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ58" s="3">
-        <v>0</v>
+      <c r="AI58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK58" s="3">
         <v>0</v>
@@ -5713,107 +5980,113 @@
       <c r="AL58" s="3">
         <v>0</v>
       </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2211400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2400100</v>
+      </c>
+      <c r="F59" s="3">
         <v>2040500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1570300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1628400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2015200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1774000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1868000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2271200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2499600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>2115500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1934000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>2344000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>2340300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>2390600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>2253800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1939500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1893900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1870500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>1877300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>1841500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>1837100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>1863800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>1930800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>2084600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>1457800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>1280000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>1109500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>754700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>420300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>413100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>452200</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ59" s="3" t="s">
         <v>8</v>
       </c>
@@ -5823,107 +6096,113 @@
       <c r="AL59" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN59" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2930100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2910900</v>
+      </c>
+      <c r="F60" s="3">
         <v>2658200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>2173200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2256900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>2393700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>2318000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2323400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2737400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>2806400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>2603400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>2231900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>2646100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>2361400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>2479000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>2338800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>2020400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1948600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1918300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>1925600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>1873800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>1863100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>1891000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>1958600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>2153300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>1488600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>1519500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>1333300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>754700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>420300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>413100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>452200</v>
       </c>
-      <c r="AH60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ60" s="3" t="s">
         <v>8</v>
       </c>
@@ -5933,50 +6212,56 @@
       <c r="AL60" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN60" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>207700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>294600</v>
+      </c>
+      <c r="F61" s="3">
         <v>763000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>751600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>718000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>35000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>33100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>23500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>23700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>14500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>13500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>8500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>6700</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -6043,101 +6328,107 @@
       <c r="AL61" s="3">
         <v>0</v>
       </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1119800</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1437100</v>
+      </c>
+      <c r="F62" s="3">
         <v>1692600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>1969100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>1426900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>783600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>1011300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>941500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>713900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>505100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>780900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>847500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>409700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>657200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>556800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>531300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>695500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>571100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>465300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>337600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>317300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>211800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>467700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>542400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>490300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>534900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>342300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>121400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>54400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>2300</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH62" s="3" t="s">
         <v>8</v>
       </c>
@@ -6153,8 +6444,14 @@
       <c r="AL62" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN62" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6263,8 +6560,14 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6373,8 +6676,14 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6483,107 +6792,113 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4310900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>4688400</v>
+      </c>
+      <c r="F66" s="3">
         <v>5217800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>4976100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>4480300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>3272500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>3434200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>3350800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>3501900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>3357600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>3413800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>3104700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>3079300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>3030500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>3048000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>2870500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>2717000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>2521500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>2383600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>2263300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>2191200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>2075000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>2358900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>2501200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>2643700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>2023600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>1862000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>1454700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>809100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>422600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>413100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>452200</v>
       </c>
-      <c r="AH66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ66" s="3" t="s">
         <v>8</v>
       </c>
@@ -6593,8 +6908,14 @@
       <c r="AL66" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN66" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6633,8 +6954,10 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6743,8 +7066,14 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6853,8 +7182,14 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6943,14 +7278,14 @@
         <v>0</v>
       </c>
       <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
         <v>628600</v>
       </c>
-      <c r="AG70" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH70" s="3">
-        <v>0</v>
-      </c>
       <c r="AI70" s="3">
         <v>0</v>
       </c>
@@ -6963,8 +7298,14 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7073,107 +7414,113 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>8</v>
+      <c r="E72" s="3">
+        <v>3503100</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I72" s="3">
         <v>2870500</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M72" s="3">
         <v>2298300</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q72" s="3">
         <v>1805100</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S72" s="3">
+      <c r="S72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U72" s="3">
         <v>1328500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>1222000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>1010000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>763500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>575900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>432200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>250600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>130000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>318900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>256100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>141600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>44300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-62500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-339400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>-109100</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ72" s="3" t="s">
         <v>8</v>
       </c>
@@ -7183,8 +7530,14 @@
       <c r="AL72" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN72" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7293,8 +7646,14 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7403,8 +7762,14 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7513,107 +7878,113 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3531400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3447700</v>
+      </c>
+      <c r="F76" s="3">
         <v>3407200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>3358300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>3178300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>3314100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>3256000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>3105700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>3057000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>3093800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>2885300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>2869400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>2860200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>2657100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>2473200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>2365900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>2233100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>2094800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>2006700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>1793300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>1516400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>1319700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>1212800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>1032600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>957400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>1110700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>1051900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>923300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>792800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>644800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>-338900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>56800</v>
       </c>
-      <c r="AH76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ76" s="3" t="s">
         <v>8</v>
       </c>
@@ -7623,8 +7994,14 @@
       <c r="AL76" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN76" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7733,233 +8110,251 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>128100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>145800</v>
+      </c>
+      <c r="F81" s="3">
         <v>201700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>242000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>248100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>262600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>257000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>190000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>161200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>156800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>156500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>151300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>136000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>122900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>137200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>136200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>162900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>182200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>222300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>222300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>187600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>167700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>181500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>129200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>28900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>66200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>114400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>96400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>110000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>241500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-419200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>-74200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>23500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>22100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>2400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>-5900</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7998,49 +8393,51 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>8</v>
+      <c r="E83" s="3">
+        <v>7400</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G83" s="3">
+      <c r="G83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I83" s="3">
         <v>7500</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K83" s="3">
+      <c r="K83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M83" s="3">
         <v>8200</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O83" s="3">
         <v>5900</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3">
-        <v>0</v>
+      <c r="P83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
@@ -8090,11 +8487,11 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH83" s="3" t="s">
-        <v>8</v>
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="3">
+        <v>0</v>
       </c>
       <c r="AI83" s="3" t="s">
         <v>8</v>
@@ -8108,8 +8505,14 @@
       <c r="AL83" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN83" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8218,8 +8621,14 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8328,8 +8737,14 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8438,8 +8853,14 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8548,8 +8969,14 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8658,74 +9085,80 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>304100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>451000</v>
+      </c>
+      <c r="F89" s="3">
         <v>351400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>366000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>386600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>418100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>338100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>269900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>271200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>331700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>170500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>242900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>256400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>252700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>220000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>352800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>196000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>132800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>252600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>186200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>244000</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>8</v>
       </c>
@@ -8735,11 +9168,11 @@
       <c r="AA89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC89" s="3">
-        <v>0</v>
+      <c r="AB89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD89" s="3">
         <v>0</v>
@@ -8750,11 +9183,11 @@
       <c r="AF89" s="3">
         <v>0</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH89" s="3" t="s">
-        <v>8</v>
+      <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH89" s="3">
+        <v>0</v>
       </c>
       <c r="AI89" s="3" t="s">
         <v>8</v>
@@ -8768,8 +9201,14 @@
       <c r="AL89" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN89" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8808,49 +9247,51 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>8</v>
+      <c r="E91" s="3">
+        <v>-34400</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G91" s="3">
+      <c r="G91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3">
         <v>-21000</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K91" s="3">
+      <c r="K91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M91" s="3">
         <v>-11900</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -8900,11 +9341,11 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH91" s="3" t="s">
-        <v>8</v>
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>0</v>
       </c>
       <c r="AI91" s="3" t="s">
         <v>8</v>
@@ -8918,8 +9359,14 @@
       <c r="AL91" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN91" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9028,8 +9475,14 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9138,74 +9591,80 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>349000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-143700</v>
+      </c>
+      <c r="F94" s="3">
         <v>-90700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-1143400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-446500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-129600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-417700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-134900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-434600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-265900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-309900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-473900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-518900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-236900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-411900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-374600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-337100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>10100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-487700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-323400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-63400</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>8</v>
       </c>
@@ -9215,11 +9674,11 @@
       <c r="AA94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC94" s="3">
-        <v>0</v>
+      <c r="AB94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD94" s="3">
         <v>0</v>
@@ -9230,11 +9689,11 @@
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH94" s="3" t="s">
-        <v>8</v>
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
+        <v>0</v>
       </c>
       <c r="AI94" s="3" t="s">
         <v>8</v>
@@ -9248,8 +9707,14 @@
       <c r="AL94" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN94" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9288,49 +9753,51 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>8</v>
+      <c r="E96" s="3">
+        <v>197000</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G96" s="3">
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3">
         <v>173000</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M96" s="3">
         <v>132800</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -9398,8 +9865,14 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9508,8 +9981,14 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9618,8 +10097,14 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9728,74 +10213,80 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-352100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-602200</v>
+      </c>
+      <c r="F100" s="3">
         <v>-63000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>278600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>750900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-256700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-178000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-105600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>245900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-128600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>96300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>170500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>5700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>27300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>121700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>296000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>148700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>149600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>64700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>77300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>25700</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>8</v>
       </c>
@@ -9805,11 +10296,11 @@
       <c r="AA100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC100" s="3">
-        <v>0</v>
+      <c r="AB100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD100" s="3">
         <v>0</v>
@@ -9820,11 +10311,11 @@
       <c r="AF100" s="3">
         <v>0</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH100" s="3" t="s">
-        <v>8</v>
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
+        <v>0</v>
       </c>
       <c r="AI100" s="3" t="s">
         <v>8</v>
@@ -9838,74 +10329,80 @@
       <c r="AL100" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN100" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E101" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F101" s="3">
         <v>-3400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>1200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-3300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>1000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-3200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>1000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-100</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>-200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-200</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y101" s="3" t="s">
         <v>8</v>
       </c>
@@ -9915,11 +10412,11 @@
       <c r="AA101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>0</v>
+      <c r="AB101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD101" s="3">
         <v>0</v>
@@ -9930,11 +10427,11 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-      <c r="AG101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH101" s="3" t="s">
-        <v>8</v>
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
       </c>
       <c r="AI101" s="3" t="s">
         <v>8</v>
@@ -9948,74 +10445,80 @@
       <c r="AL101" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN101" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>299200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-298000</v>
+      </c>
+      <c r="F102" s="3">
         <v>198400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-502900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>690300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>36200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-261000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>29700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>82800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-63000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-42400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-59400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-257200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>39900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-69200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>273900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>7100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>292400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-170400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-60100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>206100</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>8</v>
       </c>
@@ -10025,11 +10528,11 @@
       <c r="AA102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC102" s="3">
-        <v>0</v>
+      <c r="AB102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD102" s="3">
         <v>0</v>
@@ -10040,11 +10543,11 @@
       <c r="AF102" s="3">
         <v>0</v>
       </c>
-      <c r="AG102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH102" s="3" t="s">
-        <v>8</v>
+      <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
+        <v>0</v>
       </c>
       <c r="AI102" s="3" t="s">
         <v>8</v>
@@ -10056,6 +10559,12 @@
         <v>8</v>
       </c>
       <c r="AL102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN102" s="3" t="s">
         <v>8</v>
       </c>
     </row>
